--- a/tools/push-challenges-template.xlsx
+++ b/tools/push-challenges-template.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Flags" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Solutions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Hints" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lists" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Bonus Tiers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Lists" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="ChallengeStates">'Lists'!$A$2:$A$4</definedName>
@@ -21,6 +22,8 @@
     <definedName name="FlagTypes">'Lists'!$D$2:$D$3</definedName>
     <definedName name="FlagMatching">'Lists'!$E$2:$E$3</definedName>
     <definedName name="SolutionStates">'Lists'!$F$2:$F$4</definedName>
+    <definedName name="ScoringFunctions">'Lists'!$G$2:$G$3</definedName>
+    <definedName name="BonusModes">'Lists'!$H$2:$H$4</definedName>
     <definedName name="ChallengeNames">OFFSET('Challenges'!$A$2,0,0,MAX(1,COUNTA('Challenges'!$A:$A)-1),1)</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -84,15 +87,6 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -166,9 +160,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChallengesTable" displayName="ChallengesTable" ref="A1:L501" headerRowCount="1">
-  <autoFilter ref="A1:L501"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChallengesTable" displayName="ChallengesTable" ref="A1:P501" headerRowCount="1">
+  <autoFilter ref="A1:P501"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Description"/>
     <tableColumn id="3" name="Value"/>
@@ -181,6 +175,10 @@
     <tableColumn id="10" name="Max Attempts"/>
     <tableColumn id="11" name="Attribution"/>
     <tableColumn id="12" name="Connection Info"/>
+    <tableColumn id="13" name="Scoring Function"/>
+    <tableColumn id="14" name="Minimum Value"/>
+    <tableColumn id="15" name="Decay"/>
+    <tableColumn id="16" name="Bonus Mode"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -220,6 +218,19 @@
     <tableColumn id="3" name="Hint"/>
     <tableColumn id="4" name="Cost"/>
     <tableColumn id="5" name="Required Hints"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="BonusTiersTable" displayName="BonusTiersTable" ref="A1:D501" headerRowCount="1">
+  <autoFilter ref="A1:D501"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Challenge"/>
+    <tableColumn id="2" name="Start Placement"/>
+    <tableColumn id="3" name="End Placement"/>
+    <tableColumn id="4" name="Amount"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -514,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -584,12 +595,48 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Limitations</t>
+          <t>Dynamic scoring</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Standard challenges are supported. Dynamic is reserved for future use and currently fails validation. Files remain manual.</t>
+          <t>Value is initial points. Select Linear or Logarithmic, enter Minimum Value and positive Decay. Standard rows leave these settings blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Bonus tiers</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Choose Absolute or Percentage in Bonus Mode, then add contiguous placement ranges starting at 1 on Bonus Tiers. Percentage truncates to 2 decimals; absolute uses whole points. Zero is allowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Preserve/disable</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Blank Bonus Mode preserves existing settings. Disabled preserves tiers and history but stops future awards. Both leave Bonus Tiers empty. Bonus changes require Monthly Game on the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Import skips</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Existing Standard/Dynamic type mismatches skip only that challenge. Review MANUAL ACTION REQUIRED at the end of every import. Change types manually in CTFd and rerun. Files remain manual.</t>
         </is>
       </c>
     </row>
@@ -604,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L501"/>
+  <dimension ref="A1:P501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -619,6 +666,10 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -680,6 +731,26 @@
       <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Connection Info</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Function</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Minimum Value</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Decay</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Bonus Mode</t>
         </is>
       </c>
     </row>
@@ -710,6 +781,10 @@
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -738,6 +813,10 @@
       </c>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -766,6 +845,10 @@
       </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -794,6 +877,10 @@
       </c>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -822,6 +909,10 @@
       </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -850,6 +941,10 @@
       </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -878,6 +973,10 @@
       </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -906,6 +1005,10 @@
       </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -934,6 +1037,10 @@
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -962,6 +1069,10 @@
       </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -990,6 +1101,10 @@
       </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1018,6 +1133,10 @@
       </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1046,6 +1165,10 @@
       </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1074,6 +1197,10 @@
       </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1102,6 +1229,10 @@
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1130,6 +1261,10 @@
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1158,6 +1293,10 @@
       </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1186,6 +1325,10 @@
       </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1214,6 +1357,10 @@
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1242,6 +1389,10 @@
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1270,6 +1421,10 @@
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1298,6 +1453,10 @@
       </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1326,6 +1485,10 @@
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1354,6 +1517,10 @@
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1382,6 +1549,10 @@
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1410,6 +1581,10 @@
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1438,6 +1613,10 @@
       </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1466,6 +1645,10 @@
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1494,6 +1677,10 @@
       </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1522,6 +1709,10 @@
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1550,6 +1741,10 @@
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1578,6 +1773,10 @@
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1606,6 +1805,10 @@
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1634,6 +1837,10 @@
       </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1662,6 +1869,10 @@
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1690,6 +1901,10 @@
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1718,6 +1933,10 @@
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1746,6 +1965,10 @@
       </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1774,6 +1997,10 @@
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -1802,6 +2029,10 @@
       </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1830,6 +2061,10 @@
       </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -1858,6 +2093,10 @@
       </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1886,6 +2125,10 @@
       </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1914,6 +2157,10 @@
       </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1942,6 +2189,10 @@
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -1970,6 +2221,10 @@
       </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1998,6 +2253,10 @@
       </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -2026,6 +2285,10 @@
       </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2054,6 +2317,10 @@
       </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -2082,6 +2349,10 @@
       </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2110,6 +2381,10 @@
       </c>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -2138,6 +2413,10 @@
       </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -2166,6 +2445,10 @@
       </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -2194,6 +2477,10 @@
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -2222,6 +2509,10 @@
       </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -2250,6 +2541,10 @@
       </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -2278,6 +2573,10 @@
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -2306,6 +2605,10 @@
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -2334,6 +2637,10 @@
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -2362,6 +2669,10 @@
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -2390,6 +2701,10 @@
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
+      <c r="P62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -2418,6 +2733,10 @@
       </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -2446,6 +2765,10 @@
       </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -2474,6 +2797,10 @@
       </c>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -2502,6 +2829,10 @@
       </c>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
+      <c r="P66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -2530,6 +2861,10 @@
       </c>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="n"/>
+      <c r="P67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -2558,6 +2893,10 @@
       </c>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
+      <c r="P68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -2586,6 +2925,10 @@
       </c>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -2614,6 +2957,10 @@
       </c>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -2642,6 +2989,10 @@
       </c>
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -2670,6 +3021,10 @@
       </c>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -2698,6 +3053,10 @@
       </c>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -2726,6 +3085,10 @@
       </c>
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
+      <c r="P74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -2754,6 +3117,10 @@
       </c>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -2782,6 +3149,10 @@
       </c>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="n"/>
+      <c r="P76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -2810,6 +3181,10 @@
       </c>
       <c r="K77" s="2" t="n"/>
       <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="n"/>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="2" t="n"/>
+      <c r="P77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -2838,6 +3213,10 @@
       </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
+      <c r="P78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -2866,6 +3245,10 @@
       </c>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="n"/>
+      <c r="P79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -2894,6 +3277,10 @@
       </c>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -2922,6 +3309,10 @@
       </c>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n"/>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -2950,6 +3341,10 @@
       </c>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
+      <c r="P82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -2978,6 +3373,10 @@
       </c>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="n"/>
+      <c r="P83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -3006,6 +3405,10 @@
       </c>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
+      <c r="P84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -3034,6 +3437,10 @@
       </c>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n"/>
+      <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="n"/>
+      <c r="P85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -3062,6 +3469,10 @@
       </c>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -3090,6 +3501,10 @@
       </c>
       <c r="K87" s="2" t="n"/>
       <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n"/>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
+      <c r="P87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -3118,6 +3533,10 @@
       </c>
       <c r="K88" s="2" t="n"/>
       <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -3146,6 +3565,10 @@
       </c>
       <c r="K89" s="2" t="n"/>
       <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
+      <c r="P89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -3174,6 +3597,10 @@
       </c>
       <c r="K90" s="2" t="n"/>
       <c r="L90" s="2" t="n"/>
+      <c r="M90" s="2" t="n"/>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
+      <c r="P90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -3202,6 +3629,10 @@
       </c>
       <c r="K91" s="2" t="n"/>
       <c r="L91" s="2" t="n"/>
+      <c r="M91" s="2" t="n"/>
+      <c r="N91" s="2" t="n"/>
+      <c r="O91" s="2" t="n"/>
+      <c r="P91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -3230,6 +3661,10 @@
       </c>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
+      <c r="P92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -3258,6 +3693,10 @@
       </c>
       <c r="K93" s="2" t="n"/>
       <c r="L93" s="2" t="n"/>
+      <c r="M93" s="2" t="n"/>
+      <c r="N93" s="2" t="n"/>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -3286,6 +3725,10 @@
       </c>
       <c r="K94" s="2" t="n"/>
       <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
+      <c r="P94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -3314,6 +3757,10 @@
       </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
+      <c r="M95" s="2" t="n"/>
+      <c r="N95" s="2" t="n"/>
+      <c r="O95" s="2" t="n"/>
+      <c r="P95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -3342,6 +3789,10 @@
       </c>
       <c r="K96" s="2" t="n"/>
       <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
+      <c r="P96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -3370,6 +3821,10 @@
       </c>
       <c r="K97" s="2" t="n"/>
       <c r="L97" s="2" t="n"/>
+      <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
+      <c r="O97" s="2" t="n"/>
+      <c r="P97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -3398,6 +3853,10 @@
       </c>
       <c r="K98" s="2" t="n"/>
       <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -3426,6 +3885,10 @@
       </c>
       <c r="K99" s="2" t="n"/>
       <c r="L99" s="2" t="n"/>
+      <c r="M99" s="2" t="n"/>
+      <c r="N99" s="2" t="n"/>
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -3454,6 +3917,10 @@
       </c>
       <c r="K100" s="2" t="n"/>
       <c r="L100" s="2" t="n"/>
+      <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -3482,6 +3949,10 @@
       </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
+      <c r="M101" s="2" t="n"/>
+      <c r="N101" s="2" t="n"/>
+      <c r="O101" s="2" t="n"/>
+      <c r="P101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -3510,6 +3981,10 @@
       </c>
       <c r="K102" s="2" t="n"/>
       <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
+      <c r="P102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -3538,6 +4013,10 @@
       </c>
       <c r="K103" s="2" t="n"/>
       <c r="L103" s="2" t="n"/>
+      <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="n"/>
+      <c r="O103" s="2" t="n"/>
+      <c r="P103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -3566,6 +4045,10 @@
       </c>
       <c r="K104" s="2" t="n"/>
       <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
+      <c r="P104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -3594,6 +4077,10 @@
       </c>
       <c r="K105" s="2" t="n"/>
       <c r="L105" s="2" t="n"/>
+      <c r="M105" s="2" t="n"/>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="2" t="n"/>
+      <c r="P105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -3622,6 +4109,10 @@
       </c>
       <c r="K106" s="2" t="n"/>
       <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
+      <c r="P106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -3650,6 +4141,10 @@
       </c>
       <c r="K107" s="2" t="n"/>
       <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -3678,6 +4173,10 @@
       </c>
       <c r="K108" s="2" t="n"/>
       <c r="L108" s="2" t="n"/>
+      <c r="M108" s="2" t="n"/>
+      <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
+      <c r="P108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -3706,6 +4205,10 @@
       </c>
       <c r="K109" s="2" t="n"/>
       <c r="L109" s="2" t="n"/>
+      <c r="M109" s="2" t="n"/>
+      <c r="N109" s="2" t="n"/>
+      <c r="O109" s="2" t="n"/>
+      <c r="P109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -3734,6 +4237,10 @@
       </c>
       <c r="K110" s="2" t="n"/>
       <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -3762,6 +4269,10 @@
       </c>
       <c r="K111" s="2" t="n"/>
       <c r="L111" s="2" t="n"/>
+      <c r="M111" s="2" t="n"/>
+      <c r="N111" s="2" t="n"/>
+      <c r="O111" s="2" t="n"/>
+      <c r="P111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -3790,6 +4301,10 @@
       </c>
       <c r="K112" s="2" t="n"/>
       <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -3818,6 +4333,10 @@
       </c>
       <c r="K113" s="2" t="n"/>
       <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -3846,6 +4365,10 @@
       </c>
       <c r="K114" s="2" t="n"/>
       <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -3874,6 +4397,10 @@
       </c>
       <c r="K115" s="2" t="n"/>
       <c r="L115" s="2" t="n"/>
+      <c r="M115" s="2" t="n"/>
+      <c r="N115" s="2" t="n"/>
+      <c r="O115" s="2" t="n"/>
+      <c r="P115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -3902,6 +4429,10 @@
       </c>
       <c r="K116" s="2" t="n"/>
       <c r="L116" s="2" t="n"/>
+      <c r="M116" s="2" t="n"/>
+      <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
+      <c r="P116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -3930,6 +4461,10 @@
       </c>
       <c r="K117" s="2" t="n"/>
       <c r="L117" s="2" t="n"/>
+      <c r="M117" s="2" t="n"/>
+      <c r="N117" s="2" t="n"/>
+      <c r="O117" s="2" t="n"/>
+      <c r="P117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -3958,6 +4493,10 @@
       </c>
       <c r="K118" s="2" t="n"/>
       <c r="L118" s="2" t="n"/>
+      <c r="M118" s="2" t="n"/>
+      <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
+      <c r="P118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -3986,6 +4525,10 @@
       </c>
       <c r="K119" s="2" t="n"/>
       <c r="L119" s="2" t="n"/>
+      <c r="M119" s="2" t="n"/>
+      <c r="N119" s="2" t="n"/>
+      <c r="O119" s="2" t="n"/>
+      <c r="P119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -4014,6 +4557,10 @@
       </c>
       <c r="K120" s="2" t="n"/>
       <c r="L120" s="2" t="n"/>
+      <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
+      <c r="P120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -4042,6 +4589,10 @@
       </c>
       <c r="K121" s="2" t="n"/>
       <c r="L121" s="2" t="n"/>
+      <c r="M121" s="2" t="n"/>
+      <c r="N121" s="2" t="n"/>
+      <c r="O121" s="2" t="n"/>
+      <c r="P121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -4070,6 +4621,10 @@
       </c>
       <c r="K122" s="2" t="n"/>
       <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
+      <c r="P122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -4098,6 +4653,10 @@
       </c>
       <c r="K123" s="2" t="n"/>
       <c r="L123" s="2" t="n"/>
+      <c r="M123" s="2" t="n"/>
+      <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
+      <c r="P123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -4126,6 +4685,10 @@
       </c>
       <c r="K124" s="2" t="n"/>
       <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -4154,6 +4717,10 @@
       </c>
       <c r="K125" s="2" t="n"/>
       <c r="L125" s="2" t="n"/>
+      <c r="M125" s="2" t="n"/>
+      <c r="N125" s="2" t="n"/>
+      <c r="O125" s="2" t="n"/>
+      <c r="P125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -4182,6 +4749,10 @@
       </c>
       <c r="K126" s="2" t="n"/>
       <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -4210,6 +4781,10 @@
       </c>
       <c r="K127" s="2" t="n"/>
       <c r="L127" s="2" t="n"/>
+      <c r="M127" s="2" t="n"/>
+      <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
+      <c r="P127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -4238,6 +4813,10 @@
       </c>
       <c r="K128" s="2" t="n"/>
       <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
+      <c r="P128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -4266,6 +4845,10 @@
       </c>
       <c r="K129" s="2" t="n"/>
       <c r="L129" s="2" t="n"/>
+      <c r="M129" s="2" t="n"/>
+      <c r="N129" s="2" t="n"/>
+      <c r="O129" s="2" t="n"/>
+      <c r="P129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -4294,6 +4877,10 @@
       </c>
       <c r="K130" s="2" t="n"/>
       <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -4322,6 +4909,10 @@
       </c>
       <c r="K131" s="2" t="n"/>
       <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -4350,6 +4941,10 @@
       </c>
       <c r="K132" s="2" t="n"/>
       <c r="L132" s="2" t="n"/>
+      <c r="M132" s="2" t="n"/>
+      <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
+      <c r="P132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -4378,6 +4973,10 @@
       </c>
       <c r="K133" s="2" t="n"/>
       <c r="L133" s="2" t="n"/>
+      <c r="M133" s="2" t="n"/>
+      <c r="N133" s="2" t="n"/>
+      <c r="O133" s="2" t="n"/>
+      <c r="P133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -4406,6 +5005,10 @@
       </c>
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
+      <c r="P134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -4434,6 +5037,10 @@
       </c>
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="2" t="n"/>
+      <c r="M135" s="2" t="n"/>
+      <c r="N135" s="2" t="n"/>
+      <c r="O135" s="2" t="n"/>
+      <c r="P135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -4462,6 +5069,10 @@
       </c>
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="2" t="n"/>
+      <c r="M136" s="2" t="n"/>
+      <c r="N136" s="2" t="n"/>
+      <c r="O136" s="2" t="n"/>
+      <c r="P136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -4490,6 +5101,10 @@
       </c>
       <c r="K137" s="2" t="n"/>
       <c r="L137" s="2" t="n"/>
+      <c r="M137" s="2" t="n"/>
+      <c r="N137" s="2" t="n"/>
+      <c r="O137" s="2" t="n"/>
+      <c r="P137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -4518,6 +5133,10 @@
       </c>
       <c r="K138" s="2" t="n"/>
       <c r="L138" s="2" t="n"/>
+      <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
+      <c r="P138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -4546,6 +5165,10 @@
       </c>
       <c r="K139" s="2" t="n"/>
       <c r="L139" s="2" t="n"/>
+      <c r="M139" s="2" t="n"/>
+      <c r="N139" s="2" t="n"/>
+      <c r="O139" s="2" t="n"/>
+      <c r="P139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -4574,6 +5197,10 @@
       </c>
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="2" t="n"/>
+      <c r="M140" s="2" t="n"/>
+      <c r="N140" s="2" t="n"/>
+      <c r="O140" s="2" t="n"/>
+      <c r="P140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -4602,6 +5229,10 @@
       </c>
       <c r="K141" s="2" t="n"/>
       <c r="L141" s="2" t="n"/>
+      <c r="M141" s="2" t="n"/>
+      <c r="N141" s="2" t="n"/>
+      <c r="O141" s="2" t="n"/>
+      <c r="P141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -4630,6 +5261,10 @@
       </c>
       <c r="K142" s="2" t="n"/>
       <c r="L142" s="2" t="n"/>
+      <c r="M142" s="2" t="n"/>
+      <c r="N142" s="2" t="n"/>
+      <c r="O142" s="2" t="n"/>
+      <c r="P142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -4658,6 +5293,10 @@
       </c>
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="2" t="n"/>
+      <c r="M143" s="2" t="n"/>
+      <c r="N143" s="2" t="n"/>
+      <c r="O143" s="2" t="n"/>
+      <c r="P143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -4686,6 +5325,10 @@
       </c>
       <c r="K144" s="2" t="n"/>
       <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n"/>
+      <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
+      <c r="P144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -4714,6 +5357,10 @@
       </c>
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="2" t="n"/>
+      <c r="M145" s="2" t="n"/>
+      <c r="N145" s="2" t="n"/>
+      <c r="O145" s="2" t="n"/>
+      <c r="P145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -4742,6 +5389,10 @@
       </c>
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="2" t="n"/>
+      <c r="M146" s="2" t="n"/>
+      <c r="N146" s="2" t="n"/>
+      <c r="O146" s="2" t="n"/>
+      <c r="P146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -4770,6 +5421,10 @@
       </c>
       <c r="K147" s="2" t="n"/>
       <c r="L147" s="2" t="n"/>
+      <c r="M147" s="2" t="n"/>
+      <c r="N147" s="2" t="n"/>
+      <c r="O147" s="2" t="n"/>
+      <c r="P147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -4798,6 +5453,10 @@
       </c>
       <c r="K148" s="2" t="n"/>
       <c r="L148" s="2" t="n"/>
+      <c r="M148" s="2" t="n"/>
+      <c r="N148" s="2" t="n"/>
+      <c r="O148" s="2" t="n"/>
+      <c r="P148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -4826,6 +5485,10 @@
       </c>
       <c r="K149" s="2" t="n"/>
       <c r="L149" s="2" t="n"/>
+      <c r="M149" s="2" t="n"/>
+      <c r="N149" s="2" t="n"/>
+      <c r="O149" s="2" t="n"/>
+      <c r="P149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -4854,6 +5517,10 @@
       </c>
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n"/>
+      <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
+      <c r="P150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -4882,6 +5549,10 @@
       </c>
       <c r="K151" s="2" t="n"/>
       <c r="L151" s="2" t="n"/>
+      <c r="M151" s="2" t="n"/>
+      <c r="N151" s="2" t="n"/>
+      <c r="O151" s="2" t="n"/>
+      <c r="P151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -4910,6 +5581,10 @@
       </c>
       <c r="K152" s="2" t="n"/>
       <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
+      <c r="P152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -4938,6 +5613,10 @@
       </c>
       <c r="K153" s="2" t="n"/>
       <c r="L153" s="2" t="n"/>
+      <c r="M153" s="2" t="n"/>
+      <c r="N153" s="2" t="n"/>
+      <c r="O153" s="2" t="n"/>
+      <c r="P153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -4966,6 +5645,10 @@
       </c>
       <c r="K154" s="2" t="n"/>
       <c r="L154" s="2" t="n"/>
+      <c r="M154" s="2" t="n"/>
+      <c r="N154" s="2" t="n"/>
+      <c r="O154" s="2" t="n"/>
+      <c r="P154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -4994,6 +5677,10 @@
       </c>
       <c r="K155" s="2" t="n"/>
       <c r="L155" s="2" t="n"/>
+      <c r="M155" s="2" t="n"/>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="2" t="n"/>
+      <c r="P155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -5022,6 +5709,10 @@
       </c>
       <c r="K156" s="2" t="n"/>
       <c r="L156" s="2" t="n"/>
+      <c r="M156" s="2" t="n"/>
+      <c r="N156" s="2" t="n"/>
+      <c r="O156" s="2" t="n"/>
+      <c r="P156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -5050,6 +5741,10 @@
       </c>
       <c r="K157" s="2" t="n"/>
       <c r="L157" s="2" t="n"/>
+      <c r="M157" s="2" t="n"/>
+      <c r="N157" s="2" t="n"/>
+      <c r="O157" s="2" t="n"/>
+      <c r="P157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -5078,6 +5773,10 @@
       </c>
       <c r="K158" s="2" t="n"/>
       <c r="L158" s="2" t="n"/>
+      <c r="M158" s="2" t="n"/>
+      <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n"/>
+      <c r="P158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -5106,6 +5805,10 @@
       </c>
       <c r="K159" s="2" t="n"/>
       <c r="L159" s="2" t="n"/>
+      <c r="M159" s="2" t="n"/>
+      <c r="N159" s="2" t="n"/>
+      <c r="O159" s="2" t="n"/>
+      <c r="P159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -5134,6 +5837,10 @@
       </c>
       <c r="K160" s="2" t="n"/>
       <c r="L160" s="2" t="n"/>
+      <c r="M160" s="2" t="n"/>
+      <c r="N160" s="2" t="n"/>
+      <c r="O160" s="2" t="n"/>
+      <c r="P160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -5162,6 +5869,10 @@
       </c>
       <c r="K161" s="2" t="n"/>
       <c r="L161" s="2" t="n"/>
+      <c r="M161" s="2" t="n"/>
+      <c r="N161" s="2" t="n"/>
+      <c r="O161" s="2" t="n"/>
+      <c r="P161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -5190,6 +5901,10 @@
       </c>
       <c r="K162" s="2" t="n"/>
       <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n"/>
+      <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
+      <c r="P162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -5218,6 +5933,10 @@
       </c>
       <c r="K163" s="2" t="n"/>
       <c r="L163" s="2" t="n"/>
+      <c r="M163" s="2" t="n"/>
+      <c r="N163" s="2" t="n"/>
+      <c r="O163" s="2" t="n"/>
+      <c r="P163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -5246,6 +5965,10 @@
       </c>
       <c r="K164" s="2" t="n"/>
       <c r="L164" s="2" t="n"/>
+      <c r="M164" s="2" t="n"/>
+      <c r="N164" s="2" t="n"/>
+      <c r="O164" s="2" t="n"/>
+      <c r="P164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -5274,6 +5997,10 @@
       </c>
       <c r="K165" s="2" t="n"/>
       <c r="L165" s="2" t="n"/>
+      <c r="M165" s="2" t="n"/>
+      <c r="N165" s="2" t="n"/>
+      <c r="O165" s="2" t="n"/>
+      <c r="P165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -5302,6 +6029,10 @@
       </c>
       <c r="K166" s="2" t="n"/>
       <c r="L166" s="2" t="n"/>
+      <c r="M166" s="2" t="n"/>
+      <c r="N166" s="2" t="n"/>
+      <c r="O166" s="2" t="n"/>
+      <c r="P166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -5330,6 +6061,10 @@
       </c>
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="2" t="n"/>
+      <c r="M167" s="2" t="n"/>
+      <c r="N167" s="2" t="n"/>
+      <c r="O167" s="2" t="n"/>
+      <c r="P167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -5358,6 +6093,10 @@
       </c>
       <c r="K168" s="2" t="n"/>
       <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n"/>
+      <c r="N168" s="2" t="n"/>
+      <c r="O168" s="2" t="n"/>
+      <c r="P168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -5386,6 +6125,10 @@
       </c>
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="2" t="n"/>
+      <c r="M169" s="2" t="n"/>
+      <c r="N169" s="2" t="n"/>
+      <c r="O169" s="2" t="n"/>
+      <c r="P169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -5414,6 +6157,10 @@
       </c>
       <c r="K170" s="2" t="n"/>
       <c r="L170" s="2" t="n"/>
+      <c r="M170" s="2" t="n"/>
+      <c r="N170" s="2" t="n"/>
+      <c r="O170" s="2" t="n"/>
+      <c r="P170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -5442,6 +6189,10 @@
       </c>
       <c r="K171" s="2" t="n"/>
       <c r="L171" s="2" t="n"/>
+      <c r="M171" s="2" t="n"/>
+      <c r="N171" s="2" t="n"/>
+      <c r="O171" s="2" t="n"/>
+      <c r="P171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -5470,6 +6221,10 @@
       </c>
       <c r="K172" s="2" t="n"/>
       <c r="L172" s="2" t="n"/>
+      <c r="M172" s="2" t="n"/>
+      <c r="N172" s="2" t="n"/>
+      <c r="O172" s="2" t="n"/>
+      <c r="P172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -5498,6 +6253,10 @@
       </c>
       <c r="K173" s="2" t="n"/>
       <c r="L173" s="2" t="n"/>
+      <c r="M173" s="2" t="n"/>
+      <c r="N173" s="2" t="n"/>
+      <c r="O173" s="2" t="n"/>
+      <c r="P173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -5526,6 +6285,10 @@
       </c>
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
+      <c r="M174" s="2" t="n"/>
+      <c r="N174" s="2" t="n"/>
+      <c r="O174" s="2" t="n"/>
+      <c r="P174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -5554,6 +6317,10 @@
       </c>
       <c r="K175" s="2" t="n"/>
       <c r="L175" s="2" t="n"/>
+      <c r="M175" s="2" t="n"/>
+      <c r="N175" s="2" t="n"/>
+      <c r="O175" s="2" t="n"/>
+      <c r="P175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -5582,6 +6349,10 @@
       </c>
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
+      <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
+      <c r="O176" s="2" t="n"/>
+      <c r="P176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -5610,6 +6381,10 @@
       </c>
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="2" t="n"/>
+      <c r="M177" s="2" t="n"/>
+      <c r="N177" s="2" t="n"/>
+      <c r="O177" s="2" t="n"/>
+      <c r="P177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -5638,6 +6413,10 @@
       </c>
       <c r="K178" s="2" t="n"/>
       <c r="L178" s="2" t="n"/>
+      <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
+      <c r="O178" s="2" t="n"/>
+      <c r="P178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -5666,6 +6445,10 @@
       </c>
       <c r="K179" s="2" t="n"/>
       <c r="L179" s="2" t="n"/>
+      <c r="M179" s="2" t="n"/>
+      <c r="N179" s="2" t="n"/>
+      <c r="O179" s="2" t="n"/>
+      <c r="P179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -5694,6 +6477,10 @@
       </c>
       <c r="K180" s="2" t="n"/>
       <c r="L180" s="2" t="n"/>
+      <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="n"/>
+      <c r="O180" s="2" t="n"/>
+      <c r="P180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -5722,6 +6509,10 @@
       </c>
       <c r="K181" s="2" t="n"/>
       <c r="L181" s="2" t="n"/>
+      <c r="M181" s="2" t="n"/>
+      <c r="N181" s="2" t="n"/>
+      <c r="O181" s="2" t="n"/>
+      <c r="P181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -5750,6 +6541,10 @@
       </c>
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="n"/>
+      <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="n"/>
+      <c r="O182" s="2" t="n"/>
+      <c r="P182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -5778,6 +6573,10 @@
       </c>
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="2" t="n"/>
+      <c r="M183" s="2" t="n"/>
+      <c r="N183" s="2" t="n"/>
+      <c r="O183" s="2" t="n"/>
+      <c r="P183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -5806,6 +6605,10 @@
       </c>
       <c r="K184" s="2" t="n"/>
       <c r="L184" s="2" t="n"/>
+      <c r="M184" s="2" t="n"/>
+      <c r="N184" s="2" t="n"/>
+      <c r="O184" s="2" t="n"/>
+      <c r="P184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -5834,6 +6637,10 @@
       </c>
       <c r="K185" s="2" t="n"/>
       <c r="L185" s="2" t="n"/>
+      <c r="M185" s="2" t="n"/>
+      <c r="N185" s="2" t="n"/>
+      <c r="O185" s="2" t="n"/>
+      <c r="P185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -5862,6 +6669,10 @@
       </c>
       <c r="K186" s="2" t="n"/>
       <c r="L186" s="2" t="n"/>
+      <c r="M186" s="2" t="n"/>
+      <c r="N186" s="2" t="n"/>
+      <c r="O186" s="2" t="n"/>
+      <c r="P186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -5890,6 +6701,10 @@
       </c>
       <c r="K187" s="2" t="n"/>
       <c r="L187" s="2" t="n"/>
+      <c r="M187" s="2" t="n"/>
+      <c r="N187" s="2" t="n"/>
+      <c r="O187" s="2" t="n"/>
+      <c r="P187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -5918,6 +6733,10 @@
       </c>
       <c r="K188" s="2" t="n"/>
       <c r="L188" s="2" t="n"/>
+      <c r="M188" s="2" t="n"/>
+      <c r="N188" s="2" t="n"/>
+      <c r="O188" s="2" t="n"/>
+      <c r="P188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -5946,6 +6765,10 @@
       </c>
       <c r="K189" s="2" t="n"/>
       <c r="L189" s="2" t="n"/>
+      <c r="M189" s="2" t="n"/>
+      <c r="N189" s="2" t="n"/>
+      <c r="O189" s="2" t="n"/>
+      <c r="P189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -5974,6 +6797,10 @@
       </c>
       <c r="K190" s="2" t="n"/>
       <c r="L190" s="2" t="n"/>
+      <c r="M190" s="2" t="n"/>
+      <c r="N190" s="2" t="n"/>
+      <c r="O190" s="2" t="n"/>
+      <c r="P190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -6002,6 +6829,10 @@
       </c>
       <c r="K191" s="2" t="n"/>
       <c r="L191" s="2" t="n"/>
+      <c r="M191" s="2" t="n"/>
+      <c r="N191" s="2" t="n"/>
+      <c r="O191" s="2" t="n"/>
+      <c r="P191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -6030,6 +6861,10 @@
       </c>
       <c r="K192" s="2" t="n"/>
       <c r="L192" s="2" t="n"/>
+      <c r="M192" s="2" t="n"/>
+      <c r="N192" s="2" t="n"/>
+      <c r="O192" s="2" t="n"/>
+      <c r="P192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -6058,6 +6893,10 @@
       </c>
       <c r="K193" s="2" t="n"/>
       <c r="L193" s="2" t="n"/>
+      <c r="M193" s="2" t="n"/>
+      <c r="N193" s="2" t="n"/>
+      <c r="O193" s="2" t="n"/>
+      <c r="P193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -6086,6 +6925,10 @@
       </c>
       <c r="K194" s="2" t="n"/>
       <c r="L194" s="2" t="n"/>
+      <c r="M194" s="2" t="n"/>
+      <c r="N194" s="2" t="n"/>
+      <c r="O194" s="2" t="n"/>
+      <c r="P194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -6114,6 +6957,10 @@
       </c>
       <c r="K195" s="2" t="n"/>
       <c r="L195" s="2" t="n"/>
+      <c r="M195" s="2" t="n"/>
+      <c r="N195" s="2" t="n"/>
+      <c r="O195" s="2" t="n"/>
+      <c r="P195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -6142,6 +6989,10 @@
       </c>
       <c r="K196" s="2" t="n"/>
       <c r="L196" s="2" t="n"/>
+      <c r="M196" s="2" t="n"/>
+      <c r="N196" s="2" t="n"/>
+      <c r="O196" s="2" t="n"/>
+      <c r="P196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -6170,6 +7021,10 @@
       </c>
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="2" t="n"/>
+      <c r="M197" s="2" t="n"/>
+      <c r="N197" s="2" t="n"/>
+      <c r="O197" s="2" t="n"/>
+      <c r="P197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -6198,6 +7053,10 @@
       </c>
       <c r="K198" s="2" t="n"/>
       <c r="L198" s="2" t="n"/>
+      <c r="M198" s="2" t="n"/>
+      <c r="N198" s="2" t="n"/>
+      <c r="O198" s="2" t="n"/>
+      <c r="P198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -6226,6 +7085,10 @@
       </c>
       <c r="K199" s="2" t="n"/>
       <c r="L199" s="2" t="n"/>
+      <c r="M199" s="2" t="n"/>
+      <c r="N199" s="2" t="n"/>
+      <c r="O199" s="2" t="n"/>
+      <c r="P199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -6254,6 +7117,10 @@
       </c>
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="2" t="n"/>
+      <c r="M200" s="2" t="n"/>
+      <c r="N200" s="2" t="n"/>
+      <c r="O200" s="2" t="n"/>
+      <c r="P200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -6282,6 +7149,10 @@
       </c>
       <c r="K201" s="2" t="n"/>
       <c r="L201" s="2" t="n"/>
+      <c r="M201" s="2" t="n"/>
+      <c r="N201" s="2" t="n"/>
+      <c r="O201" s="2" t="n"/>
+      <c r="P201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -6310,6 +7181,10 @@
       </c>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
+      <c r="M202" s="2" t="n"/>
+      <c r="N202" s="2" t="n"/>
+      <c r="O202" s="2" t="n"/>
+      <c r="P202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -6338,6 +7213,10 @@
       </c>
       <c r="K203" s="2" t="n"/>
       <c r="L203" s="2" t="n"/>
+      <c r="M203" s="2" t="n"/>
+      <c r="N203" s="2" t="n"/>
+      <c r="O203" s="2" t="n"/>
+      <c r="P203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -6366,6 +7245,10 @@
       </c>
       <c r="K204" s="2" t="n"/>
       <c r="L204" s="2" t="n"/>
+      <c r="M204" s="2" t="n"/>
+      <c r="N204" s="2" t="n"/>
+      <c r="O204" s="2" t="n"/>
+      <c r="P204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -6394,6 +7277,10 @@
       </c>
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="2" t="n"/>
+      <c r="M205" s="2" t="n"/>
+      <c r="N205" s="2" t="n"/>
+      <c r="O205" s="2" t="n"/>
+      <c r="P205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -6422,6 +7309,10 @@
       </c>
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
+      <c r="M206" s="2" t="n"/>
+      <c r="N206" s="2" t="n"/>
+      <c r="O206" s="2" t="n"/>
+      <c r="P206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -6450,6 +7341,10 @@
       </c>
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="n"/>
+      <c r="M207" s="2" t="n"/>
+      <c r="N207" s="2" t="n"/>
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -6478,6 +7373,10 @@
       </c>
       <c r="K208" s="2" t="n"/>
       <c r="L208" s="2" t="n"/>
+      <c r="M208" s="2" t="n"/>
+      <c r="N208" s="2" t="n"/>
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -6506,6 +7405,10 @@
       </c>
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="2" t="n"/>
+      <c r="M209" s="2" t="n"/>
+      <c r="N209" s="2" t="n"/>
+      <c r="O209" s="2" t="n"/>
+      <c r="P209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -6534,6 +7437,10 @@
       </c>
       <c r="K210" s="2" t="n"/>
       <c r="L210" s="2" t="n"/>
+      <c r="M210" s="2" t="n"/>
+      <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="n"/>
+      <c r="P210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -6562,6 +7469,10 @@
       </c>
       <c r="K211" s="2" t="n"/>
       <c r="L211" s="2" t="n"/>
+      <c r="M211" s="2" t="n"/>
+      <c r="N211" s="2" t="n"/>
+      <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -6590,6 +7501,10 @@
       </c>
       <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
+      <c r="M212" s="2" t="n"/>
+      <c r="N212" s="2" t="n"/>
+      <c r="O212" s="2" t="n"/>
+      <c r="P212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -6618,6 +7533,10 @@
       </c>
       <c r="K213" s="2" t="n"/>
       <c r="L213" s="2" t="n"/>
+      <c r="M213" s="2" t="n"/>
+      <c r="N213" s="2" t="n"/>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -6646,6 +7565,10 @@
       </c>
       <c r="K214" s="2" t="n"/>
       <c r="L214" s="2" t="n"/>
+      <c r="M214" s="2" t="n"/>
+      <c r="N214" s="2" t="n"/>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -6674,6 +7597,10 @@
       </c>
       <c r="K215" s="2" t="n"/>
       <c r="L215" s="2" t="n"/>
+      <c r="M215" s="2" t="n"/>
+      <c r="N215" s="2" t="n"/>
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -6702,6 +7629,10 @@
       </c>
       <c r="K216" s="2" t="n"/>
       <c r="L216" s="2" t="n"/>
+      <c r="M216" s="2" t="n"/>
+      <c r="N216" s="2" t="n"/>
+      <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -6730,6 +7661,10 @@
       </c>
       <c r="K217" s="2" t="n"/>
       <c r="L217" s="2" t="n"/>
+      <c r="M217" s="2" t="n"/>
+      <c r="N217" s="2" t="n"/>
+      <c r="O217" s="2" t="n"/>
+      <c r="P217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -6758,6 +7693,10 @@
       </c>
       <c r="K218" s="2" t="n"/>
       <c r="L218" s="2" t="n"/>
+      <c r="M218" s="2" t="n"/>
+      <c r="N218" s="2" t="n"/>
+      <c r="O218" s="2" t="n"/>
+      <c r="P218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -6786,6 +7725,10 @@
       </c>
       <c r="K219" s="2" t="n"/>
       <c r="L219" s="2" t="n"/>
+      <c r="M219" s="2" t="n"/>
+      <c r="N219" s="2" t="n"/>
+      <c r="O219" s="2" t="n"/>
+      <c r="P219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -6814,6 +7757,10 @@
       </c>
       <c r="K220" s="2" t="n"/>
       <c r="L220" s="2" t="n"/>
+      <c r="M220" s="2" t="n"/>
+      <c r="N220" s="2" t="n"/>
+      <c r="O220" s="2" t="n"/>
+      <c r="P220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -6842,6 +7789,10 @@
       </c>
       <c r="K221" s="2" t="n"/>
       <c r="L221" s="2" t="n"/>
+      <c r="M221" s="2" t="n"/>
+      <c r="N221" s="2" t="n"/>
+      <c r="O221" s="2" t="n"/>
+      <c r="P221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -6870,6 +7821,10 @@
       </c>
       <c r="K222" s="2" t="n"/>
       <c r="L222" s="2" t="n"/>
+      <c r="M222" s="2" t="n"/>
+      <c r="N222" s="2" t="n"/>
+      <c r="O222" s="2" t="n"/>
+      <c r="P222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -6898,6 +7853,10 @@
       </c>
       <c r="K223" s="2" t="n"/>
       <c r="L223" s="2" t="n"/>
+      <c r="M223" s="2" t="n"/>
+      <c r="N223" s="2" t="n"/>
+      <c r="O223" s="2" t="n"/>
+      <c r="P223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -6926,6 +7885,10 @@
       </c>
       <c r="K224" s="2" t="n"/>
       <c r="L224" s="2" t="n"/>
+      <c r="M224" s="2" t="n"/>
+      <c r="N224" s="2" t="n"/>
+      <c r="O224" s="2" t="n"/>
+      <c r="P224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -6954,6 +7917,10 @@
       </c>
       <c r="K225" s="2" t="n"/>
       <c r="L225" s="2" t="n"/>
+      <c r="M225" s="2" t="n"/>
+      <c r="N225" s="2" t="n"/>
+      <c r="O225" s="2" t="n"/>
+      <c r="P225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -6982,6 +7949,10 @@
       </c>
       <c r="K226" s="2" t="n"/>
       <c r="L226" s="2" t="n"/>
+      <c r="M226" s="2" t="n"/>
+      <c r="N226" s="2" t="n"/>
+      <c r="O226" s="2" t="n"/>
+      <c r="P226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -7010,6 +7981,10 @@
       </c>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="2" t="n"/>
+      <c r="M227" s="2" t="n"/>
+      <c r="N227" s="2" t="n"/>
+      <c r="O227" s="2" t="n"/>
+      <c r="P227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -7038,6 +8013,10 @@
       </c>
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="2" t="n"/>
+      <c r="M228" s="2" t="n"/>
+      <c r="N228" s="2" t="n"/>
+      <c r="O228" s="2" t="n"/>
+      <c r="P228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -7066,6 +8045,10 @@
       </c>
       <c r="K229" s="2" t="n"/>
       <c r="L229" s="2" t="n"/>
+      <c r="M229" s="2" t="n"/>
+      <c r="N229" s="2" t="n"/>
+      <c r="O229" s="2" t="n"/>
+      <c r="P229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -7094,6 +8077,10 @@
       </c>
       <c r="K230" s="2" t="n"/>
       <c r="L230" s="2" t="n"/>
+      <c r="M230" s="2" t="n"/>
+      <c r="N230" s="2" t="n"/>
+      <c r="O230" s="2" t="n"/>
+      <c r="P230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -7122,6 +8109,10 @@
       </c>
       <c r="K231" s="2" t="n"/>
       <c r="L231" s="2" t="n"/>
+      <c r="M231" s="2" t="n"/>
+      <c r="N231" s="2" t="n"/>
+      <c r="O231" s="2" t="n"/>
+      <c r="P231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -7150,6 +8141,10 @@
       </c>
       <c r="K232" s="2" t="n"/>
       <c r="L232" s="2" t="n"/>
+      <c r="M232" s="2" t="n"/>
+      <c r="N232" s="2" t="n"/>
+      <c r="O232" s="2" t="n"/>
+      <c r="P232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -7178,6 +8173,10 @@
       </c>
       <c r="K233" s="2" t="n"/>
       <c r="L233" s="2" t="n"/>
+      <c r="M233" s="2" t="n"/>
+      <c r="N233" s="2" t="n"/>
+      <c r="O233" s="2" t="n"/>
+      <c r="P233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -7206,6 +8205,10 @@
       </c>
       <c r="K234" s="2" t="n"/>
       <c r="L234" s="2" t="n"/>
+      <c r="M234" s="2" t="n"/>
+      <c r="N234" s="2" t="n"/>
+      <c r="O234" s="2" t="n"/>
+      <c r="P234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -7234,6 +8237,10 @@
       </c>
       <c r="K235" s="2" t="n"/>
       <c r="L235" s="2" t="n"/>
+      <c r="M235" s="2" t="n"/>
+      <c r="N235" s="2" t="n"/>
+      <c r="O235" s="2" t="n"/>
+      <c r="P235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -7262,6 +8269,10 @@
       </c>
       <c r="K236" s="2" t="n"/>
       <c r="L236" s="2" t="n"/>
+      <c r="M236" s="2" t="n"/>
+      <c r="N236" s="2" t="n"/>
+      <c r="O236" s="2" t="n"/>
+      <c r="P236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -7290,6 +8301,10 @@
       </c>
       <c r="K237" s="2" t="n"/>
       <c r="L237" s="2" t="n"/>
+      <c r="M237" s="2" t="n"/>
+      <c r="N237" s="2" t="n"/>
+      <c r="O237" s="2" t="n"/>
+      <c r="P237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -7318,6 +8333,10 @@
       </c>
       <c r="K238" s="2" t="n"/>
       <c r="L238" s="2" t="n"/>
+      <c r="M238" s="2" t="n"/>
+      <c r="N238" s="2" t="n"/>
+      <c r="O238" s="2" t="n"/>
+      <c r="P238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -7346,6 +8365,10 @@
       </c>
       <c r="K239" s="2" t="n"/>
       <c r="L239" s="2" t="n"/>
+      <c r="M239" s="2" t="n"/>
+      <c r="N239" s="2" t="n"/>
+      <c r="O239" s="2" t="n"/>
+      <c r="P239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -7374,6 +8397,10 @@
       </c>
       <c r="K240" s="2" t="n"/>
       <c r="L240" s="2" t="n"/>
+      <c r="M240" s="2" t="n"/>
+      <c r="N240" s="2" t="n"/>
+      <c r="O240" s="2" t="n"/>
+      <c r="P240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -7402,6 +8429,10 @@
       </c>
       <c r="K241" s="2" t="n"/>
       <c r="L241" s="2" t="n"/>
+      <c r="M241" s="2" t="n"/>
+      <c r="N241" s="2" t="n"/>
+      <c r="O241" s="2" t="n"/>
+      <c r="P241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -7430,6 +8461,10 @@
       </c>
       <c r="K242" s="2" t="n"/>
       <c r="L242" s="2" t="n"/>
+      <c r="M242" s="2" t="n"/>
+      <c r="N242" s="2" t="n"/>
+      <c r="O242" s="2" t="n"/>
+      <c r="P242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -7458,6 +8493,10 @@
       </c>
       <c r="K243" s="2" t="n"/>
       <c r="L243" s="2" t="n"/>
+      <c r="M243" s="2" t="n"/>
+      <c r="N243" s="2" t="n"/>
+      <c r="O243" s="2" t="n"/>
+      <c r="P243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -7486,6 +8525,10 @@
       </c>
       <c r="K244" s="2" t="n"/>
       <c r="L244" s="2" t="n"/>
+      <c r="M244" s="2" t="n"/>
+      <c r="N244" s="2" t="n"/>
+      <c r="O244" s="2" t="n"/>
+      <c r="P244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -7514,6 +8557,10 @@
       </c>
       <c r="K245" s="2" t="n"/>
       <c r="L245" s="2" t="n"/>
+      <c r="M245" s="2" t="n"/>
+      <c r="N245" s="2" t="n"/>
+      <c r="O245" s="2" t="n"/>
+      <c r="P245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -7542,6 +8589,10 @@
       </c>
       <c r="K246" s="2" t="n"/>
       <c r="L246" s="2" t="n"/>
+      <c r="M246" s="2" t="n"/>
+      <c r="N246" s="2" t="n"/>
+      <c r="O246" s="2" t="n"/>
+      <c r="P246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -7570,6 +8621,10 @@
       </c>
       <c r="K247" s="2" t="n"/>
       <c r="L247" s="2" t="n"/>
+      <c r="M247" s="2" t="n"/>
+      <c r="N247" s="2" t="n"/>
+      <c r="O247" s="2" t="n"/>
+      <c r="P247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -7598,6 +8653,10 @@
       </c>
       <c r="K248" s="2" t="n"/>
       <c r="L248" s="2" t="n"/>
+      <c r="M248" s="2" t="n"/>
+      <c r="N248" s="2" t="n"/>
+      <c r="O248" s="2" t="n"/>
+      <c r="P248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -7626,6 +8685,10 @@
       </c>
       <c r="K249" s="2" t="n"/>
       <c r="L249" s="2" t="n"/>
+      <c r="M249" s="2" t="n"/>
+      <c r="N249" s="2" t="n"/>
+      <c r="O249" s="2" t="n"/>
+      <c r="P249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -7654,6 +8717,10 @@
       </c>
       <c r="K250" s="2" t="n"/>
       <c r="L250" s="2" t="n"/>
+      <c r="M250" s="2" t="n"/>
+      <c r="N250" s="2" t="n"/>
+      <c r="O250" s="2" t="n"/>
+      <c r="P250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -7682,6 +8749,10 @@
       </c>
       <c r="K251" s="2" t="n"/>
       <c r="L251" s="2" t="n"/>
+      <c r="M251" s="2" t="n"/>
+      <c r="N251" s="2" t="n"/>
+      <c r="O251" s="2" t="n"/>
+      <c r="P251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -7710,6 +8781,10 @@
       </c>
       <c r="K252" s="2" t="n"/>
       <c r="L252" s="2" t="n"/>
+      <c r="M252" s="2" t="n"/>
+      <c r="N252" s="2" t="n"/>
+      <c r="O252" s="2" t="n"/>
+      <c r="P252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -7738,6 +8813,10 @@
       </c>
       <c r="K253" s="2" t="n"/>
       <c r="L253" s="2" t="n"/>
+      <c r="M253" s="2" t="n"/>
+      <c r="N253" s="2" t="n"/>
+      <c r="O253" s="2" t="n"/>
+      <c r="P253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -7766,6 +8845,10 @@
       </c>
       <c r="K254" s="2" t="n"/>
       <c r="L254" s="2" t="n"/>
+      <c r="M254" s="2" t="n"/>
+      <c r="N254" s="2" t="n"/>
+      <c r="O254" s="2" t="n"/>
+      <c r="P254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -7794,6 +8877,10 @@
       </c>
       <c r="K255" s="2" t="n"/>
       <c r="L255" s="2" t="n"/>
+      <c r="M255" s="2" t="n"/>
+      <c r="N255" s="2" t="n"/>
+      <c r="O255" s="2" t="n"/>
+      <c r="P255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -7822,6 +8909,10 @@
       </c>
       <c r="K256" s="2" t="n"/>
       <c r="L256" s="2" t="n"/>
+      <c r="M256" s="2" t="n"/>
+      <c r="N256" s="2" t="n"/>
+      <c r="O256" s="2" t="n"/>
+      <c r="P256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -7850,6 +8941,10 @@
       </c>
       <c r="K257" s="2" t="n"/>
       <c r="L257" s="2" t="n"/>
+      <c r="M257" s="2" t="n"/>
+      <c r="N257" s="2" t="n"/>
+      <c r="O257" s="2" t="n"/>
+      <c r="P257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -7878,6 +8973,10 @@
       </c>
       <c r="K258" s="2" t="n"/>
       <c r="L258" s="2" t="n"/>
+      <c r="M258" s="2" t="n"/>
+      <c r="N258" s="2" t="n"/>
+      <c r="O258" s="2" t="n"/>
+      <c r="P258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -7906,6 +9005,10 @@
       </c>
       <c r="K259" s="2" t="n"/>
       <c r="L259" s="2" t="n"/>
+      <c r="M259" s="2" t="n"/>
+      <c r="N259" s="2" t="n"/>
+      <c r="O259" s="2" t="n"/>
+      <c r="P259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -7934,6 +9037,10 @@
       </c>
       <c r="K260" s="2" t="n"/>
       <c r="L260" s="2" t="n"/>
+      <c r="M260" s="2" t="n"/>
+      <c r="N260" s="2" t="n"/>
+      <c r="O260" s="2" t="n"/>
+      <c r="P260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -7962,6 +9069,10 @@
       </c>
       <c r="K261" s="2" t="n"/>
       <c r="L261" s="2" t="n"/>
+      <c r="M261" s="2" t="n"/>
+      <c r="N261" s="2" t="n"/>
+      <c r="O261" s="2" t="n"/>
+      <c r="P261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -7990,6 +9101,10 @@
       </c>
       <c r="K262" s="2" t="n"/>
       <c r="L262" s="2" t="n"/>
+      <c r="M262" s="2" t="n"/>
+      <c r="N262" s="2" t="n"/>
+      <c r="O262" s="2" t="n"/>
+      <c r="P262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -8018,6 +9133,10 @@
       </c>
       <c r="K263" s="2" t="n"/>
       <c r="L263" s="2" t="n"/>
+      <c r="M263" s="2" t="n"/>
+      <c r="N263" s="2" t="n"/>
+      <c r="O263" s="2" t="n"/>
+      <c r="P263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -8046,6 +9165,10 @@
       </c>
       <c r="K264" s="2" t="n"/>
       <c r="L264" s="2" t="n"/>
+      <c r="M264" s="2" t="n"/>
+      <c r="N264" s="2" t="n"/>
+      <c r="O264" s="2" t="n"/>
+      <c r="P264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -8074,6 +9197,10 @@
       </c>
       <c r="K265" s="2" t="n"/>
       <c r="L265" s="2" t="n"/>
+      <c r="M265" s="2" t="n"/>
+      <c r="N265" s="2" t="n"/>
+      <c r="O265" s="2" t="n"/>
+      <c r="P265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -8102,6 +9229,10 @@
       </c>
       <c r="K266" s="2" t="n"/>
       <c r="L266" s="2" t="n"/>
+      <c r="M266" s="2" t="n"/>
+      <c r="N266" s="2" t="n"/>
+      <c r="O266" s="2" t="n"/>
+      <c r="P266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -8130,6 +9261,10 @@
       </c>
       <c r="K267" s="2" t="n"/>
       <c r="L267" s="2" t="n"/>
+      <c r="M267" s="2" t="n"/>
+      <c r="N267" s="2" t="n"/>
+      <c r="O267" s="2" t="n"/>
+      <c r="P267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -8158,6 +9293,10 @@
       </c>
       <c r="K268" s="2" t="n"/>
       <c r="L268" s="2" t="n"/>
+      <c r="M268" s="2" t="n"/>
+      <c r="N268" s="2" t="n"/>
+      <c r="O268" s="2" t="n"/>
+      <c r="P268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -8186,6 +9325,10 @@
       </c>
       <c r="K269" s="2" t="n"/>
       <c r="L269" s="2" t="n"/>
+      <c r="M269" s="2" t="n"/>
+      <c r="N269" s="2" t="n"/>
+      <c r="O269" s="2" t="n"/>
+      <c r="P269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -8214,6 +9357,10 @@
       </c>
       <c r="K270" s="2" t="n"/>
       <c r="L270" s="2" t="n"/>
+      <c r="M270" s="2" t="n"/>
+      <c r="N270" s="2" t="n"/>
+      <c r="O270" s="2" t="n"/>
+      <c r="P270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -8242,6 +9389,10 @@
       </c>
       <c r="K271" s="2" t="n"/>
       <c r="L271" s="2" t="n"/>
+      <c r="M271" s="2" t="n"/>
+      <c r="N271" s="2" t="n"/>
+      <c r="O271" s="2" t="n"/>
+      <c r="P271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -8270,6 +9421,10 @@
       </c>
       <c r="K272" s="2" t="n"/>
       <c r="L272" s="2" t="n"/>
+      <c r="M272" s="2" t="n"/>
+      <c r="N272" s="2" t="n"/>
+      <c r="O272" s="2" t="n"/>
+      <c r="P272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -8298,6 +9453,10 @@
       </c>
       <c r="K273" s="2" t="n"/>
       <c r="L273" s="2" t="n"/>
+      <c r="M273" s="2" t="n"/>
+      <c r="N273" s="2" t="n"/>
+      <c r="O273" s="2" t="n"/>
+      <c r="P273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -8326,6 +9485,10 @@
       </c>
       <c r="K274" s="2" t="n"/>
       <c r="L274" s="2" t="n"/>
+      <c r="M274" s="2" t="n"/>
+      <c r="N274" s="2" t="n"/>
+      <c r="O274" s="2" t="n"/>
+      <c r="P274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -8354,6 +9517,10 @@
       </c>
       <c r="K275" s="2" t="n"/>
       <c r="L275" s="2" t="n"/>
+      <c r="M275" s="2" t="n"/>
+      <c r="N275" s="2" t="n"/>
+      <c r="O275" s="2" t="n"/>
+      <c r="P275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -8382,6 +9549,10 @@
       </c>
       <c r="K276" s="2" t="n"/>
       <c r="L276" s="2" t="n"/>
+      <c r="M276" s="2" t="n"/>
+      <c r="N276" s="2" t="n"/>
+      <c r="O276" s="2" t="n"/>
+      <c r="P276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -8410,6 +9581,10 @@
       </c>
       <c r="K277" s="2" t="n"/>
       <c r="L277" s="2" t="n"/>
+      <c r="M277" s="2" t="n"/>
+      <c r="N277" s="2" t="n"/>
+      <c r="O277" s="2" t="n"/>
+      <c r="P277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -8438,6 +9613,10 @@
       </c>
       <c r="K278" s="2" t="n"/>
       <c r="L278" s="2" t="n"/>
+      <c r="M278" s="2" t="n"/>
+      <c r="N278" s="2" t="n"/>
+      <c r="O278" s="2" t="n"/>
+      <c r="P278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -8466,6 +9645,10 @@
       </c>
       <c r="K279" s="2" t="n"/>
       <c r="L279" s="2" t="n"/>
+      <c r="M279" s="2" t="n"/>
+      <c r="N279" s="2" t="n"/>
+      <c r="O279" s="2" t="n"/>
+      <c r="P279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -8494,6 +9677,10 @@
       </c>
       <c r="K280" s="2" t="n"/>
       <c r="L280" s="2" t="n"/>
+      <c r="M280" s="2" t="n"/>
+      <c r="N280" s="2" t="n"/>
+      <c r="O280" s="2" t="n"/>
+      <c r="P280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -8522,6 +9709,10 @@
       </c>
       <c r="K281" s="2" t="n"/>
       <c r="L281" s="2" t="n"/>
+      <c r="M281" s="2" t="n"/>
+      <c r="N281" s="2" t="n"/>
+      <c r="O281" s="2" t="n"/>
+      <c r="P281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -8550,6 +9741,10 @@
       </c>
       <c r="K282" s="2" t="n"/>
       <c r="L282" s="2" t="n"/>
+      <c r="M282" s="2" t="n"/>
+      <c r="N282" s="2" t="n"/>
+      <c r="O282" s="2" t="n"/>
+      <c r="P282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -8578,6 +9773,10 @@
       </c>
       <c r="K283" s="2" t="n"/>
       <c r="L283" s="2" t="n"/>
+      <c r="M283" s="2" t="n"/>
+      <c r="N283" s="2" t="n"/>
+      <c r="O283" s="2" t="n"/>
+      <c r="P283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -8606,6 +9805,10 @@
       </c>
       <c r="K284" s="2" t="n"/>
       <c r="L284" s="2" t="n"/>
+      <c r="M284" s="2" t="n"/>
+      <c r="N284" s="2" t="n"/>
+      <c r="O284" s="2" t="n"/>
+      <c r="P284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -8634,6 +9837,10 @@
       </c>
       <c r="K285" s="2" t="n"/>
       <c r="L285" s="2" t="n"/>
+      <c r="M285" s="2" t="n"/>
+      <c r="N285" s="2" t="n"/>
+      <c r="O285" s="2" t="n"/>
+      <c r="P285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -8662,6 +9869,10 @@
       </c>
       <c r="K286" s="2" t="n"/>
       <c r="L286" s="2" t="n"/>
+      <c r="M286" s="2" t="n"/>
+      <c r="N286" s="2" t="n"/>
+      <c r="O286" s="2" t="n"/>
+      <c r="P286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -8690,6 +9901,10 @@
       </c>
       <c r="K287" s="2" t="n"/>
       <c r="L287" s="2" t="n"/>
+      <c r="M287" s="2" t="n"/>
+      <c r="N287" s="2" t="n"/>
+      <c r="O287" s="2" t="n"/>
+      <c r="P287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -8718,6 +9933,10 @@
       </c>
       <c r="K288" s="2" t="n"/>
       <c r="L288" s="2" t="n"/>
+      <c r="M288" s="2" t="n"/>
+      <c r="N288" s="2" t="n"/>
+      <c r="O288" s="2" t="n"/>
+      <c r="P288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -8746,6 +9965,10 @@
       </c>
       <c r="K289" s="2" t="n"/>
       <c r="L289" s="2" t="n"/>
+      <c r="M289" s="2" t="n"/>
+      <c r="N289" s="2" t="n"/>
+      <c r="O289" s="2" t="n"/>
+      <c r="P289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -8774,6 +9997,10 @@
       </c>
       <c r="K290" s="2" t="n"/>
       <c r="L290" s="2" t="n"/>
+      <c r="M290" s="2" t="n"/>
+      <c r="N290" s="2" t="n"/>
+      <c r="O290" s="2" t="n"/>
+      <c r="P290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -8802,6 +10029,10 @@
       </c>
       <c r="K291" s="2" t="n"/>
       <c r="L291" s="2" t="n"/>
+      <c r="M291" s="2" t="n"/>
+      <c r="N291" s="2" t="n"/>
+      <c r="O291" s="2" t="n"/>
+      <c r="P291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -8830,6 +10061,10 @@
       </c>
       <c r="K292" s="2" t="n"/>
       <c r="L292" s="2" t="n"/>
+      <c r="M292" s="2" t="n"/>
+      <c r="N292" s="2" t="n"/>
+      <c r="O292" s="2" t="n"/>
+      <c r="P292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -8858,6 +10093,10 @@
       </c>
       <c r="K293" s="2" t="n"/>
       <c r="L293" s="2" t="n"/>
+      <c r="M293" s="2" t="n"/>
+      <c r="N293" s="2" t="n"/>
+      <c r="O293" s="2" t="n"/>
+      <c r="P293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -8886,6 +10125,10 @@
       </c>
       <c r="K294" s="2" t="n"/>
       <c r="L294" s="2" t="n"/>
+      <c r="M294" s="2" t="n"/>
+      <c r="N294" s="2" t="n"/>
+      <c r="O294" s="2" t="n"/>
+      <c r="P294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -8914,6 +10157,10 @@
       </c>
       <c r="K295" s="2" t="n"/>
       <c r="L295" s="2" t="n"/>
+      <c r="M295" s="2" t="n"/>
+      <c r="N295" s="2" t="n"/>
+      <c r="O295" s="2" t="n"/>
+      <c r="P295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -8942,6 +10189,10 @@
       </c>
       <c r="K296" s="2" t="n"/>
       <c r="L296" s="2" t="n"/>
+      <c r="M296" s="2" t="n"/>
+      <c r="N296" s="2" t="n"/>
+      <c r="O296" s="2" t="n"/>
+      <c r="P296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -8970,6 +10221,10 @@
       </c>
       <c r="K297" s="2" t="n"/>
       <c r="L297" s="2" t="n"/>
+      <c r="M297" s="2" t="n"/>
+      <c r="N297" s="2" t="n"/>
+      <c r="O297" s="2" t="n"/>
+      <c r="P297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -8998,6 +10253,10 @@
       </c>
       <c r="K298" s="2" t="n"/>
       <c r="L298" s="2" t="n"/>
+      <c r="M298" s="2" t="n"/>
+      <c r="N298" s="2" t="n"/>
+      <c r="O298" s="2" t="n"/>
+      <c r="P298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -9026,6 +10285,10 @@
       </c>
       <c r="K299" s="2" t="n"/>
       <c r="L299" s="2" t="n"/>
+      <c r="M299" s="2" t="n"/>
+      <c r="N299" s="2" t="n"/>
+      <c r="O299" s="2" t="n"/>
+      <c r="P299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -9054,6 +10317,10 @@
       </c>
       <c r="K300" s="2" t="n"/>
       <c r="L300" s="2" t="n"/>
+      <c r="M300" s="2" t="n"/>
+      <c r="N300" s="2" t="n"/>
+      <c r="O300" s="2" t="n"/>
+      <c r="P300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -9082,6 +10349,10 @@
       </c>
       <c r="K301" s="2" t="n"/>
       <c r="L301" s="2" t="n"/>
+      <c r="M301" s="2" t="n"/>
+      <c r="N301" s="2" t="n"/>
+      <c r="O301" s="2" t="n"/>
+      <c r="P301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -9110,6 +10381,10 @@
       </c>
       <c r="K302" s="2" t="n"/>
       <c r="L302" s="2" t="n"/>
+      <c r="M302" s="2" t="n"/>
+      <c r="N302" s="2" t="n"/>
+      <c r="O302" s="2" t="n"/>
+      <c r="P302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -9138,6 +10413,10 @@
       </c>
       <c r="K303" s="2" t="n"/>
       <c r="L303" s="2" t="n"/>
+      <c r="M303" s="2" t="n"/>
+      <c r="N303" s="2" t="n"/>
+      <c r="O303" s="2" t="n"/>
+      <c r="P303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -9166,6 +10445,10 @@
       </c>
       <c r="K304" s="2" t="n"/>
       <c r="L304" s="2" t="n"/>
+      <c r="M304" s="2" t="n"/>
+      <c r="N304" s="2" t="n"/>
+      <c r="O304" s="2" t="n"/>
+      <c r="P304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -9194,6 +10477,10 @@
       </c>
       <c r="K305" s="2" t="n"/>
       <c r="L305" s="2" t="n"/>
+      <c r="M305" s="2" t="n"/>
+      <c r="N305" s="2" t="n"/>
+      <c r="O305" s="2" t="n"/>
+      <c r="P305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -9222,6 +10509,10 @@
       </c>
       <c r="K306" s="2" t="n"/>
       <c r="L306" s="2" t="n"/>
+      <c r="M306" s="2" t="n"/>
+      <c r="N306" s="2" t="n"/>
+      <c r="O306" s="2" t="n"/>
+      <c r="P306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -9250,6 +10541,10 @@
       </c>
       <c r="K307" s="2" t="n"/>
       <c r="L307" s="2" t="n"/>
+      <c r="M307" s="2" t="n"/>
+      <c r="N307" s="2" t="n"/>
+      <c r="O307" s="2" t="n"/>
+      <c r="P307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -9278,6 +10573,10 @@
       </c>
       <c r="K308" s="2" t="n"/>
       <c r="L308" s="2" t="n"/>
+      <c r="M308" s="2" t="n"/>
+      <c r="N308" s="2" t="n"/>
+      <c r="O308" s="2" t="n"/>
+      <c r="P308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -9306,6 +10605,10 @@
       </c>
       <c r="K309" s="2" t="n"/>
       <c r="L309" s="2" t="n"/>
+      <c r="M309" s="2" t="n"/>
+      <c r="N309" s="2" t="n"/>
+      <c r="O309" s="2" t="n"/>
+      <c r="P309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -9334,6 +10637,10 @@
       </c>
       <c r="K310" s="2" t="n"/>
       <c r="L310" s="2" t="n"/>
+      <c r="M310" s="2" t="n"/>
+      <c r="N310" s="2" t="n"/>
+      <c r="O310" s="2" t="n"/>
+      <c r="P310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -9362,6 +10669,10 @@
       </c>
       <c r="K311" s="2" t="n"/>
       <c r="L311" s="2" t="n"/>
+      <c r="M311" s="2" t="n"/>
+      <c r="N311" s="2" t="n"/>
+      <c r="O311" s="2" t="n"/>
+      <c r="P311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -9390,6 +10701,10 @@
       </c>
       <c r="K312" s="2" t="n"/>
       <c r="L312" s="2" t="n"/>
+      <c r="M312" s="2" t="n"/>
+      <c r="N312" s="2" t="n"/>
+      <c r="O312" s="2" t="n"/>
+      <c r="P312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -9418,6 +10733,10 @@
       </c>
       <c r="K313" s="2" t="n"/>
       <c r="L313" s="2" t="n"/>
+      <c r="M313" s="2" t="n"/>
+      <c r="N313" s="2" t="n"/>
+      <c r="O313" s="2" t="n"/>
+      <c r="P313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -9446,6 +10765,10 @@
       </c>
       <c r="K314" s="2" t="n"/>
       <c r="L314" s="2" t="n"/>
+      <c r="M314" s="2" t="n"/>
+      <c r="N314" s="2" t="n"/>
+      <c r="O314" s="2" t="n"/>
+      <c r="P314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -9474,6 +10797,10 @@
       </c>
       <c r="K315" s="2" t="n"/>
       <c r="L315" s="2" t="n"/>
+      <c r="M315" s="2" t="n"/>
+      <c r="N315" s="2" t="n"/>
+      <c r="O315" s="2" t="n"/>
+      <c r="P315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -9502,6 +10829,10 @@
       </c>
       <c r="K316" s="2" t="n"/>
       <c r="L316" s="2" t="n"/>
+      <c r="M316" s="2" t="n"/>
+      <c r="N316" s="2" t="n"/>
+      <c r="O316" s="2" t="n"/>
+      <c r="P316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -9530,6 +10861,10 @@
       </c>
       <c r="K317" s="2" t="n"/>
       <c r="L317" s="2" t="n"/>
+      <c r="M317" s="2" t="n"/>
+      <c r="N317" s="2" t="n"/>
+      <c r="O317" s="2" t="n"/>
+      <c r="P317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -9558,6 +10893,10 @@
       </c>
       <c r="K318" s="2" t="n"/>
       <c r="L318" s="2" t="n"/>
+      <c r="M318" s="2" t="n"/>
+      <c r="N318" s="2" t="n"/>
+      <c r="O318" s="2" t="n"/>
+      <c r="P318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -9586,6 +10925,10 @@
       </c>
       <c r="K319" s="2" t="n"/>
       <c r="L319" s="2" t="n"/>
+      <c r="M319" s="2" t="n"/>
+      <c r="N319" s="2" t="n"/>
+      <c r="O319" s="2" t="n"/>
+      <c r="P319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -9614,6 +10957,10 @@
       </c>
       <c r="K320" s="2" t="n"/>
       <c r="L320" s="2" t="n"/>
+      <c r="M320" s="2" t="n"/>
+      <c r="N320" s="2" t="n"/>
+      <c r="O320" s="2" t="n"/>
+      <c r="P320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -9642,6 +10989,10 @@
       </c>
       <c r="K321" s="2" t="n"/>
       <c r="L321" s="2" t="n"/>
+      <c r="M321" s="2" t="n"/>
+      <c r="N321" s="2" t="n"/>
+      <c r="O321" s="2" t="n"/>
+      <c r="P321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -9670,6 +11021,10 @@
       </c>
       <c r="K322" s="2" t="n"/>
       <c r="L322" s="2" t="n"/>
+      <c r="M322" s="2" t="n"/>
+      <c r="N322" s="2" t="n"/>
+      <c r="O322" s="2" t="n"/>
+      <c r="P322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -9698,6 +11053,10 @@
       </c>
       <c r="K323" s="2" t="n"/>
       <c r="L323" s="2" t="n"/>
+      <c r="M323" s="2" t="n"/>
+      <c r="N323" s="2" t="n"/>
+      <c r="O323" s="2" t="n"/>
+      <c r="P323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -9726,6 +11085,10 @@
       </c>
       <c r="K324" s="2" t="n"/>
       <c r="L324" s="2" t="n"/>
+      <c r="M324" s="2" t="n"/>
+      <c r="N324" s="2" t="n"/>
+      <c r="O324" s="2" t="n"/>
+      <c r="P324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -9754,6 +11117,10 @@
       </c>
       <c r="K325" s="2" t="n"/>
       <c r="L325" s="2" t="n"/>
+      <c r="M325" s="2" t="n"/>
+      <c r="N325" s="2" t="n"/>
+      <c r="O325" s="2" t="n"/>
+      <c r="P325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -9782,6 +11149,10 @@
       </c>
       <c r="K326" s="2" t="n"/>
       <c r="L326" s="2" t="n"/>
+      <c r="M326" s="2" t="n"/>
+      <c r="N326" s="2" t="n"/>
+      <c r="O326" s="2" t="n"/>
+      <c r="P326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -9810,6 +11181,10 @@
       </c>
       <c r="K327" s="2" t="n"/>
       <c r="L327" s="2" t="n"/>
+      <c r="M327" s="2" t="n"/>
+      <c r="N327" s="2" t="n"/>
+      <c r="O327" s="2" t="n"/>
+      <c r="P327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -9838,6 +11213,10 @@
       </c>
       <c r="K328" s="2" t="n"/>
       <c r="L328" s="2" t="n"/>
+      <c r="M328" s="2" t="n"/>
+      <c r="N328" s="2" t="n"/>
+      <c r="O328" s="2" t="n"/>
+      <c r="P328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -9866,6 +11245,10 @@
       </c>
       <c r="K329" s="2" t="n"/>
       <c r="L329" s="2" t="n"/>
+      <c r="M329" s="2" t="n"/>
+      <c r="N329" s="2" t="n"/>
+      <c r="O329" s="2" t="n"/>
+      <c r="P329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -9894,6 +11277,10 @@
       </c>
       <c r="K330" s="2" t="n"/>
       <c r="L330" s="2" t="n"/>
+      <c r="M330" s="2" t="n"/>
+      <c r="N330" s="2" t="n"/>
+      <c r="O330" s="2" t="n"/>
+      <c r="P330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -9922,6 +11309,10 @@
       </c>
       <c r="K331" s="2" t="n"/>
       <c r="L331" s="2" t="n"/>
+      <c r="M331" s="2" t="n"/>
+      <c r="N331" s="2" t="n"/>
+      <c r="O331" s="2" t="n"/>
+      <c r="P331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -9950,6 +11341,10 @@
       </c>
       <c r="K332" s="2" t="n"/>
       <c r="L332" s="2" t="n"/>
+      <c r="M332" s="2" t="n"/>
+      <c r="N332" s="2" t="n"/>
+      <c r="O332" s="2" t="n"/>
+      <c r="P332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -9978,6 +11373,10 @@
       </c>
       <c r="K333" s="2" t="n"/>
       <c r="L333" s="2" t="n"/>
+      <c r="M333" s="2" t="n"/>
+      <c r="N333" s="2" t="n"/>
+      <c r="O333" s="2" t="n"/>
+      <c r="P333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -10006,6 +11405,10 @@
       </c>
       <c r="K334" s="2" t="n"/>
       <c r="L334" s="2" t="n"/>
+      <c r="M334" s="2" t="n"/>
+      <c r="N334" s="2" t="n"/>
+      <c r="O334" s="2" t="n"/>
+      <c r="P334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -10034,6 +11437,10 @@
       </c>
       <c r="K335" s="2" t="n"/>
       <c r="L335" s="2" t="n"/>
+      <c r="M335" s="2" t="n"/>
+      <c r="N335" s="2" t="n"/>
+      <c r="O335" s="2" t="n"/>
+      <c r="P335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -10062,6 +11469,10 @@
       </c>
       <c r="K336" s="2" t="n"/>
       <c r="L336" s="2" t="n"/>
+      <c r="M336" s="2" t="n"/>
+      <c r="N336" s="2" t="n"/>
+      <c r="O336" s="2" t="n"/>
+      <c r="P336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -10090,6 +11501,10 @@
       </c>
       <c r="K337" s="2" t="n"/>
       <c r="L337" s="2" t="n"/>
+      <c r="M337" s="2" t="n"/>
+      <c r="N337" s="2" t="n"/>
+      <c r="O337" s="2" t="n"/>
+      <c r="P337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -10118,6 +11533,10 @@
       </c>
       <c r="K338" s="2" t="n"/>
       <c r="L338" s="2" t="n"/>
+      <c r="M338" s="2" t="n"/>
+      <c r="N338" s="2" t="n"/>
+      <c r="O338" s="2" t="n"/>
+      <c r="P338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -10146,6 +11565,10 @@
       </c>
       <c r="K339" s="2" t="n"/>
       <c r="L339" s="2" t="n"/>
+      <c r="M339" s="2" t="n"/>
+      <c r="N339" s="2" t="n"/>
+      <c r="O339" s="2" t="n"/>
+      <c r="P339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -10174,6 +11597,10 @@
       </c>
       <c r="K340" s="2" t="n"/>
       <c r="L340" s="2" t="n"/>
+      <c r="M340" s="2" t="n"/>
+      <c r="N340" s="2" t="n"/>
+      <c r="O340" s="2" t="n"/>
+      <c r="P340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -10202,6 +11629,10 @@
       </c>
       <c r="K341" s="2" t="n"/>
       <c r="L341" s="2" t="n"/>
+      <c r="M341" s="2" t="n"/>
+      <c r="N341" s="2" t="n"/>
+      <c r="O341" s="2" t="n"/>
+      <c r="P341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -10230,6 +11661,10 @@
       </c>
       <c r="K342" s="2" t="n"/>
       <c r="L342" s="2" t="n"/>
+      <c r="M342" s="2" t="n"/>
+      <c r="N342" s="2" t="n"/>
+      <c r="O342" s="2" t="n"/>
+      <c r="P342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -10258,6 +11693,10 @@
       </c>
       <c r="K343" s="2" t="n"/>
       <c r="L343" s="2" t="n"/>
+      <c r="M343" s="2" t="n"/>
+      <c r="N343" s="2" t="n"/>
+      <c r="O343" s="2" t="n"/>
+      <c r="P343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -10286,6 +11725,10 @@
       </c>
       <c r="K344" s="2" t="n"/>
       <c r="L344" s="2" t="n"/>
+      <c r="M344" s="2" t="n"/>
+      <c r="N344" s="2" t="n"/>
+      <c r="O344" s="2" t="n"/>
+      <c r="P344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -10314,6 +11757,10 @@
       </c>
       <c r="K345" s="2" t="n"/>
       <c r="L345" s="2" t="n"/>
+      <c r="M345" s="2" t="n"/>
+      <c r="N345" s="2" t="n"/>
+      <c r="O345" s="2" t="n"/>
+      <c r="P345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -10342,6 +11789,10 @@
       </c>
       <c r="K346" s="2" t="n"/>
       <c r="L346" s="2" t="n"/>
+      <c r="M346" s="2" t="n"/>
+      <c r="N346" s="2" t="n"/>
+      <c r="O346" s="2" t="n"/>
+      <c r="P346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -10370,6 +11821,10 @@
       </c>
       <c r="K347" s="2" t="n"/>
       <c r="L347" s="2" t="n"/>
+      <c r="M347" s="2" t="n"/>
+      <c r="N347" s="2" t="n"/>
+      <c r="O347" s="2" t="n"/>
+      <c r="P347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -10398,6 +11853,10 @@
       </c>
       <c r="K348" s="2" t="n"/>
       <c r="L348" s="2" t="n"/>
+      <c r="M348" s="2" t="n"/>
+      <c r="N348" s="2" t="n"/>
+      <c r="O348" s="2" t="n"/>
+      <c r="P348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -10426,6 +11885,10 @@
       </c>
       <c r="K349" s="2" t="n"/>
       <c r="L349" s="2" t="n"/>
+      <c r="M349" s="2" t="n"/>
+      <c r="N349" s="2" t="n"/>
+      <c r="O349" s="2" t="n"/>
+      <c r="P349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -10454,6 +11917,10 @@
       </c>
       <c r="K350" s="2" t="n"/>
       <c r="L350" s="2" t="n"/>
+      <c r="M350" s="2" t="n"/>
+      <c r="N350" s="2" t="n"/>
+      <c r="O350" s="2" t="n"/>
+      <c r="P350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -10482,6 +11949,10 @@
       </c>
       <c r="K351" s="2" t="n"/>
       <c r="L351" s="2" t="n"/>
+      <c r="M351" s="2" t="n"/>
+      <c r="N351" s="2" t="n"/>
+      <c r="O351" s="2" t="n"/>
+      <c r="P351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -10510,6 +11981,10 @@
       </c>
       <c r="K352" s="2" t="n"/>
       <c r="L352" s="2" t="n"/>
+      <c r="M352" s="2" t="n"/>
+      <c r="N352" s="2" t="n"/>
+      <c r="O352" s="2" t="n"/>
+      <c r="P352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -10538,6 +12013,10 @@
       </c>
       <c r="K353" s="2" t="n"/>
       <c r="L353" s="2" t="n"/>
+      <c r="M353" s="2" t="n"/>
+      <c r="N353" s="2" t="n"/>
+      <c r="O353" s="2" t="n"/>
+      <c r="P353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -10566,6 +12045,10 @@
       </c>
       <c r="K354" s="2" t="n"/>
       <c r="L354" s="2" t="n"/>
+      <c r="M354" s="2" t="n"/>
+      <c r="N354" s="2" t="n"/>
+      <c r="O354" s="2" t="n"/>
+      <c r="P354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -10594,6 +12077,10 @@
       </c>
       <c r="K355" s="2" t="n"/>
       <c r="L355" s="2" t="n"/>
+      <c r="M355" s="2" t="n"/>
+      <c r="N355" s="2" t="n"/>
+      <c r="O355" s="2" t="n"/>
+      <c r="P355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -10622,6 +12109,10 @@
       </c>
       <c r="K356" s="2" t="n"/>
       <c r="L356" s="2" t="n"/>
+      <c r="M356" s="2" t="n"/>
+      <c r="N356" s="2" t="n"/>
+      <c r="O356" s="2" t="n"/>
+      <c r="P356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -10650,6 +12141,10 @@
       </c>
       <c r="K357" s="2" t="n"/>
       <c r="L357" s="2" t="n"/>
+      <c r="M357" s="2" t="n"/>
+      <c r="N357" s="2" t="n"/>
+      <c r="O357" s="2" t="n"/>
+      <c r="P357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -10678,6 +12173,10 @@
       </c>
       <c r="K358" s="2" t="n"/>
       <c r="L358" s="2" t="n"/>
+      <c r="M358" s="2" t="n"/>
+      <c r="N358" s="2" t="n"/>
+      <c r="O358" s="2" t="n"/>
+      <c r="P358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -10706,6 +12205,10 @@
       </c>
       <c r="K359" s="2" t="n"/>
       <c r="L359" s="2" t="n"/>
+      <c r="M359" s="2" t="n"/>
+      <c r="N359" s="2" t="n"/>
+      <c r="O359" s="2" t="n"/>
+      <c r="P359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -10734,6 +12237,10 @@
       </c>
       <c r="K360" s="2" t="n"/>
       <c r="L360" s="2" t="n"/>
+      <c r="M360" s="2" t="n"/>
+      <c r="N360" s="2" t="n"/>
+      <c r="O360" s="2" t="n"/>
+      <c r="P360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -10762,6 +12269,10 @@
       </c>
       <c r="K361" s="2" t="n"/>
       <c r="L361" s="2" t="n"/>
+      <c r="M361" s="2" t="n"/>
+      <c r="N361" s="2" t="n"/>
+      <c r="O361" s="2" t="n"/>
+      <c r="P361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -10790,6 +12301,10 @@
       </c>
       <c r="K362" s="2" t="n"/>
       <c r="L362" s="2" t="n"/>
+      <c r="M362" s="2" t="n"/>
+      <c r="N362" s="2" t="n"/>
+      <c r="O362" s="2" t="n"/>
+      <c r="P362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -10818,6 +12333,10 @@
       </c>
       <c r="K363" s="2" t="n"/>
       <c r="L363" s="2" t="n"/>
+      <c r="M363" s="2" t="n"/>
+      <c r="N363" s="2" t="n"/>
+      <c r="O363" s="2" t="n"/>
+      <c r="P363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -10846,6 +12365,10 @@
       </c>
       <c r="K364" s="2" t="n"/>
       <c r="L364" s="2" t="n"/>
+      <c r="M364" s="2" t="n"/>
+      <c r="N364" s="2" t="n"/>
+      <c r="O364" s="2" t="n"/>
+      <c r="P364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -10874,6 +12397,10 @@
       </c>
       <c r="K365" s="2" t="n"/>
       <c r="L365" s="2" t="n"/>
+      <c r="M365" s="2" t="n"/>
+      <c r="N365" s="2" t="n"/>
+      <c r="O365" s="2" t="n"/>
+      <c r="P365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -10902,6 +12429,10 @@
       </c>
       <c r="K366" s="2" t="n"/>
       <c r="L366" s="2" t="n"/>
+      <c r="M366" s="2" t="n"/>
+      <c r="N366" s="2" t="n"/>
+      <c r="O366" s="2" t="n"/>
+      <c r="P366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -10930,6 +12461,10 @@
       </c>
       <c r="K367" s="2" t="n"/>
       <c r="L367" s="2" t="n"/>
+      <c r="M367" s="2" t="n"/>
+      <c r="N367" s="2" t="n"/>
+      <c r="O367" s="2" t="n"/>
+      <c r="P367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -10958,6 +12493,10 @@
       </c>
       <c r="K368" s="2" t="n"/>
       <c r="L368" s="2" t="n"/>
+      <c r="M368" s="2" t="n"/>
+      <c r="N368" s="2" t="n"/>
+      <c r="O368" s="2" t="n"/>
+      <c r="P368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -10986,6 +12525,10 @@
       </c>
       <c r="K369" s="2" t="n"/>
       <c r="L369" s="2" t="n"/>
+      <c r="M369" s="2" t="n"/>
+      <c r="N369" s="2" t="n"/>
+      <c r="O369" s="2" t="n"/>
+      <c r="P369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -11014,6 +12557,10 @@
       </c>
       <c r="K370" s="2" t="n"/>
       <c r="L370" s="2" t="n"/>
+      <c r="M370" s="2" t="n"/>
+      <c r="N370" s="2" t="n"/>
+      <c r="O370" s="2" t="n"/>
+      <c r="P370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -11042,6 +12589,10 @@
       </c>
       <c r="K371" s="2" t="n"/>
       <c r="L371" s="2" t="n"/>
+      <c r="M371" s="2" t="n"/>
+      <c r="N371" s="2" t="n"/>
+      <c r="O371" s="2" t="n"/>
+      <c r="P371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -11070,6 +12621,10 @@
       </c>
       <c r="K372" s="2" t="n"/>
       <c r="L372" s="2" t="n"/>
+      <c r="M372" s="2" t="n"/>
+      <c r="N372" s="2" t="n"/>
+      <c r="O372" s="2" t="n"/>
+      <c r="P372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -11098,6 +12653,10 @@
       </c>
       <c r="K373" s="2" t="n"/>
       <c r="L373" s="2" t="n"/>
+      <c r="M373" s="2" t="n"/>
+      <c r="N373" s="2" t="n"/>
+      <c r="O373" s="2" t="n"/>
+      <c r="P373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -11126,6 +12685,10 @@
       </c>
       <c r="K374" s="2" t="n"/>
       <c r="L374" s="2" t="n"/>
+      <c r="M374" s="2" t="n"/>
+      <c r="N374" s="2" t="n"/>
+      <c r="O374" s="2" t="n"/>
+      <c r="P374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -11154,6 +12717,10 @@
       </c>
       <c r="K375" s="2" t="n"/>
       <c r="L375" s="2" t="n"/>
+      <c r="M375" s="2" t="n"/>
+      <c r="N375" s="2" t="n"/>
+      <c r="O375" s="2" t="n"/>
+      <c r="P375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -11182,6 +12749,10 @@
       </c>
       <c r="K376" s="2" t="n"/>
       <c r="L376" s="2" t="n"/>
+      <c r="M376" s="2" t="n"/>
+      <c r="N376" s="2" t="n"/>
+      <c r="O376" s="2" t="n"/>
+      <c r="P376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -11210,6 +12781,10 @@
       </c>
       <c r="K377" s="2" t="n"/>
       <c r="L377" s="2" t="n"/>
+      <c r="M377" s="2" t="n"/>
+      <c r="N377" s="2" t="n"/>
+      <c r="O377" s="2" t="n"/>
+      <c r="P377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -11238,6 +12813,10 @@
       </c>
       <c r="K378" s="2" t="n"/>
       <c r="L378" s="2" t="n"/>
+      <c r="M378" s="2" t="n"/>
+      <c r="N378" s="2" t="n"/>
+      <c r="O378" s="2" t="n"/>
+      <c r="P378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -11266,6 +12845,10 @@
       </c>
       <c r="K379" s="2" t="n"/>
       <c r="L379" s="2" t="n"/>
+      <c r="M379" s="2" t="n"/>
+      <c r="N379" s="2" t="n"/>
+      <c r="O379" s="2" t="n"/>
+      <c r="P379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -11294,6 +12877,10 @@
       </c>
       <c r="K380" s="2" t="n"/>
       <c r="L380" s="2" t="n"/>
+      <c r="M380" s="2" t="n"/>
+      <c r="N380" s="2" t="n"/>
+      <c r="O380" s="2" t="n"/>
+      <c r="P380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -11322,6 +12909,10 @@
       </c>
       <c r="K381" s="2" t="n"/>
       <c r="L381" s="2" t="n"/>
+      <c r="M381" s="2" t="n"/>
+      <c r="N381" s="2" t="n"/>
+      <c r="O381" s="2" t="n"/>
+      <c r="P381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -11350,6 +12941,10 @@
       </c>
       <c r="K382" s="2" t="n"/>
       <c r="L382" s="2" t="n"/>
+      <c r="M382" s="2" t="n"/>
+      <c r="N382" s="2" t="n"/>
+      <c r="O382" s="2" t="n"/>
+      <c r="P382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -11378,6 +12973,10 @@
       </c>
       <c r="K383" s="2" t="n"/>
       <c r="L383" s="2" t="n"/>
+      <c r="M383" s="2" t="n"/>
+      <c r="N383" s="2" t="n"/>
+      <c r="O383" s="2" t="n"/>
+      <c r="P383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -11406,6 +13005,10 @@
       </c>
       <c r="K384" s="2" t="n"/>
       <c r="L384" s="2" t="n"/>
+      <c r="M384" s="2" t="n"/>
+      <c r="N384" s="2" t="n"/>
+      <c r="O384" s="2" t="n"/>
+      <c r="P384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -11434,6 +13037,10 @@
       </c>
       <c r="K385" s="2" t="n"/>
       <c r="L385" s="2" t="n"/>
+      <c r="M385" s="2" t="n"/>
+      <c r="N385" s="2" t="n"/>
+      <c r="O385" s="2" t="n"/>
+      <c r="P385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -11462,6 +13069,10 @@
       </c>
       <c r="K386" s="2" t="n"/>
       <c r="L386" s="2" t="n"/>
+      <c r="M386" s="2" t="n"/>
+      <c r="N386" s="2" t="n"/>
+      <c r="O386" s="2" t="n"/>
+      <c r="P386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -11490,6 +13101,10 @@
       </c>
       <c r="K387" s="2" t="n"/>
       <c r="L387" s="2" t="n"/>
+      <c r="M387" s="2" t="n"/>
+      <c r="N387" s="2" t="n"/>
+      <c r="O387" s="2" t="n"/>
+      <c r="P387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -11518,6 +13133,10 @@
       </c>
       <c r="K388" s="2" t="n"/>
       <c r="L388" s="2" t="n"/>
+      <c r="M388" s="2" t="n"/>
+      <c r="N388" s="2" t="n"/>
+      <c r="O388" s="2" t="n"/>
+      <c r="P388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -11546,6 +13165,10 @@
       </c>
       <c r="K389" s="2" t="n"/>
       <c r="L389" s="2" t="n"/>
+      <c r="M389" s="2" t="n"/>
+      <c r="N389" s="2" t="n"/>
+      <c r="O389" s="2" t="n"/>
+      <c r="P389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -11574,6 +13197,10 @@
       </c>
       <c r="K390" s="2" t="n"/>
       <c r="L390" s="2" t="n"/>
+      <c r="M390" s="2" t="n"/>
+      <c r="N390" s="2" t="n"/>
+      <c r="O390" s="2" t="n"/>
+      <c r="P390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -11602,6 +13229,10 @@
       </c>
       <c r="K391" s="2" t="n"/>
       <c r="L391" s="2" t="n"/>
+      <c r="M391" s="2" t="n"/>
+      <c r="N391" s="2" t="n"/>
+      <c r="O391" s="2" t="n"/>
+      <c r="P391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -11630,6 +13261,10 @@
       </c>
       <c r="K392" s="2" t="n"/>
       <c r="L392" s="2" t="n"/>
+      <c r="M392" s="2" t="n"/>
+      <c r="N392" s="2" t="n"/>
+      <c r="O392" s="2" t="n"/>
+      <c r="P392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -11658,6 +13293,10 @@
       </c>
       <c r="K393" s="2" t="n"/>
       <c r="L393" s="2" t="n"/>
+      <c r="M393" s="2" t="n"/>
+      <c r="N393" s="2" t="n"/>
+      <c r="O393" s="2" t="n"/>
+      <c r="P393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -11686,6 +13325,10 @@
       </c>
       <c r="K394" s="2" t="n"/>
       <c r="L394" s="2" t="n"/>
+      <c r="M394" s="2" t="n"/>
+      <c r="N394" s="2" t="n"/>
+      <c r="O394" s="2" t="n"/>
+      <c r="P394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -11714,6 +13357,10 @@
       </c>
       <c r="K395" s="2" t="n"/>
       <c r="L395" s="2" t="n"/>
+      <c r="M395" s="2" t="n"/>
+      <c r="N395" s="2" t="n"/>
+      <c r="O395" s="2" t="n"/>
+      <c r="P395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -11742,6 +13389,10 @@
       </c>
       <c r="K396" s="2" t="n"/>
       <c r="L396" s="2" t="n"/>
+      <c r="M396" s="2" t="n"/>
+      <c r="N396" s="2" t="n"/>
+      <c r="O396" s="2" t="n"/>
+      <c r="P396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -11770,6 +13421,10 @@
       </c>
       <c r="K397" s="2" t="n"/>
       <c r="L397" s="2" t="n"/>
+      <c r="M397" s="2" t="n"/>
+      <c r="N397" s="2" t="n"/>
+      <c r="O397" s="2" t="n"/>
+      <c r="P397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -11798,6 +13453,10 @@
       </c>
       <c r="K398" s="2" t="n"/>
       <c r="L398" s="2" t="n"/>
+      <c r="M398" s="2" t="n"/>
+      <c r="N398" s="2" t="n"/>
+      <c r="O398" s="2" t="n"/>
+      <c r="P398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -11826,6 +13485,10 @@
       </c>
       <c r="K399" s="2" t="n"/>
       <c r="L399" s="2" t="n"/>
+      <c r="M399" s="2" t="n"/>
+      <c r="N399" s="2" t="n"/>
+      <c r="O399" s="2" t="n"/>
+      <c r="P399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -11854,6 +13517,10 @@
       </c>
       <c r="K400" s="2" t="n"/>
       <c r="L400" s="2" t="n"/>
+      <c r="M400" s="2" t="n"/>
+      <c r="N400" s="2" t="n"/>
+      <c r="O400" s="2" t="n"/>
+      <c r="P400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -11882,6 +13549,10 @@
       </c>
       <c r="K401" s="2" t="n"/>
       <c r="L401" s="2" t="n"/>
+      <c r="M401" s="2" t="n"/>
+      <c r="N401" s="2" t="n"/>
+      <c r="O401" s="2" t="n"/>
+      <c r="P401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -11910,6 +13581,10 @@
       </c>
       <c r="K402" s="2" t="n"/>
       <c r="L402" s="2" t="n"/>
+      <c r="M402" s="2" t="n"/>
+      <c r="N402" s="2" t="n"/>
+      <c r="O402" s="2" t="n"/>
+      <c r="P402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -11938,6 +13613,10 @@
       </c>
       <c r="K403" s="2" t="n"/>
       <c r="L403" s="2" t="n"/>
+      <c r="M403" s="2" t="n"/>
+      <c r="N403" s="2" t="n"/>
+      <c r="O403" s="2" t="n"/>
+      <c r="P403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -11966,6 +13645,10 @@
       </c>
       <c r="K404" s="2" t="n"/>
       <c r="L404" s="2" t="n"/>
+      <c r="M404" s="2" t="n"/>
+      <c r="N404" s="2" t="n"/>
+      <c r="O404" s="2" t="n"/>
+      <c r="P404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -11994,6 +13677,10 @@
       </c>
       <c r="K405" s="2" t="n"/>
       <c r="L405" s="2" t="n"/>
+      <c r="M405" s="2" t="n"/>
+      <c r="N405" s="2" t="n"/>
+      <c r="O405" s="2" t="n"/>
+      <c r="P405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -12022,6 +13709,10 @@
       </c>
       <c r="K406" s="2" t="n"/>
       <c r="L406" s="2" t="n"/>
+      <c r="M406" s="2" t="n"/>
+      <c r="N406" s="2" t="n"/>
+      <c r="O406" s="2" t="n"/>
+      <c r="P406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -12050,6 +13741,10 @@
       </c>
       <c r="K407" s="2" t="n"/>
       <c r="L407" s="2" t="n"/>
+      <c r="M407" s="2" t="n"/>
+      <c r="N407" s="2" t="n"/>
+      <c r="O407" s="2" t="n"/>
+      <c r="P407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -12078,6 +13773,10 @@
       </c>
       <c r="K408" s="2" t="n"/>
       <c r="L408" s="2" t="n"/>
+      <c r="M408" s="2" t="n"/>
+      <c r="N408" s="2" t="n"/>
+      <c r="O408" s="2" t="n"/>
+      <c r="P408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -12106,6 +13805,10 @@
       </c>
       <c r="K409" s="2" t="n"/>
       <c r="L409" s="2" t="n"/>
+      <c r="M409" s="2" t="n"/>
+      <c r="N409" s="2" t="n"/>
+      <c r="O409" s="2" t="n"/>
+      <c r="P409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -12134,6 +13837,10 @@
       </c>
       <c r="K410" s="2" t="n"/>
       <c r="L410" s="2" t="n"/>
+      <c r="M410" s="2" t="n"/>
+      <c r="N410" s="2" t="n"/>
+      <c r="O410" s="2" t="n"/>
+      <c r="P410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -12162,6 +13869,10 @@
       </c>
       <c r="K411" s="2" t="n"/>
       <c r="L411" s="2" t="n"/>
+      <c r="M411" s="2" t="n"/>
+      <c r="N411" s="2" t="n"/>
+      <c r="O411" s="2" t="n"/>
+      <c r="P411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -12190,6 +13901,10 @@
       </c>
       <c r="K412" s="2" t="n"/>
       <c r="L412" s="2" t="n"/>
+      <c r="M412" s="2" t="n"/>
+      <c r="N412" s="2" t="n"/>
+      <c r="O412" s="2" t="n"/>
+      <c r="P412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -12218,6 +13933,10 @@
       </c>
       <c r="K413" s="2" t="n"/>
       <c r="L413" s="2" t="n"/>
+      <c r="M413" s="2" t="n"/>
+      <c r="N413" s="2" t="n"/>
+      <c r="O413" s="2" t="n"/>
+      <c r="P413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -12246,6 +13965,10 @@
       </c>
       <c r="K414" s="2" t="n"/>
       <c r="L414" s="2" t="n"/>
+      <c r="M414" s="2" t="n"/>
+      <c r="N414" s="2" t="n"/>
+      <c r="O414" s="2" t="n"/>
+      <c r="P414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -12274,6 +13997,10 @@
       </c>
       <c r="K415" s="2" t="n"/>
       <c r="L415" s="2" t="n"/>
+      <c r="M415" s="2" t="n"/>
+      <c r="N415" s="2" t="n"/>
+      <c r="O415" s="2" t="n"/>
+      <c r="P415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -12302,6 +14029,10 @@
       </c>
       <c r="K416" s="2" t="n"/>
       <c r="L416" s="2" t="n"/>
+      <c r="M416" s="2" t="n"/>
+      <c r="N416" s="2" t="n"/>
+      <c r="O416" s="2" t="n"/>
+      <c r="P416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -12330,6 +14061,10 @@
       </c>
       <c r="K417" s="2" t="n"/>
       <c r="L417" s="2" t="n"/>
+      <c r="M417" s="2" t="n"/>
+      <c r="N417" s="2" t="n"/>
+      <c r="O417" s="2" t="n"/>
+      <c r="P417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -12358,6 +14093,10 @@
       </c>
       <c r="K418" s="2" t="n"/>
       <c r="L418" s="2" t="n"/>
+      <c r="M418" s="2" t="n"/>
+      <c r="N418" s="2" t="n"/>
+      <c r="O418" s="2" t="n"/>
+      <c r="P418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -12386,6 +14125,10 @@
       </c>
       <c r="K419" s="2" t="n"/>
       <c r="L419" s="2" t="n"/>
+      <c r="M419" s="2" t="n"/>
+      <c r="N419" s="2" t="n"/>
+      <c r="O419" s="2" t="n"/>
+      <c r="P419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -12414,6 +14157,10 @@
       </c>
       <c r="K420" s="2" t="n"/>
       <c r="L420" s="2" t="n"/>
+      <c r="M420" s="2" t="n"/>
+      <c r="N420" s="2" t="n"/>
+      <c r="O420" s="2" t="n"/>
+      <c r="P420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -12442,6 +14189,10 @@
       </c>
       <c r="K421" s="2" t="n"/>
       <c r="L421" s="2" t="n"/>
+      <c r="M421" s="2" t="n"/>
+      <c r="N421" s="2" t="n"/>
+      <c r="O421" s="2" t="n"/>
+      <c r="P421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -12470,6 +14221,10 @@
       </c>
       <c r="K422" s="2" t="n"/>
       <c r="L422" s="2" t="n"/>
+      <c r="M422" s="2" t="n"/>
+      <c r="N422" s="2" t="n"/>
+      <c r="O422" s="2" t="n"/>
+      <c r="P422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -12498,6 +14253,10 @@
       </c>
       <c r="K423" s="2" t="n"/>
       <c r="L423" s="2" t="n"/>
+      <c r="M423" s="2" t="n"/>
+      <c r="N423" s="2" t="n"/>
+      <c r="O423" s="2" t="n"/>
+      <c r="P423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -12526,6 +14285,10 @@
       </c>
       <c r="K424" s="2" t="n"/>
       <c r="L424" s="2" t="n"/>
+      <c r="M424" s="2" t="n"/>
+      <c r="N424" s="2" t="n"/>
+      <c r="O424" s="2" t="n"/>
+      <c r="P424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -12554,6 +14317,10 @@
       </c>
       <c r="K425" s="2" t="n"/>
       <c r="L425" s="2" t="n"/>
+      <c r="M425" s="2" t="n"/>
+      <c r="N425" s="2" t="n"/>
+      <c r="O425" s="2" t="n"/>
+      <c r="P425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -12582,6 +14349,10 @@
       </c>
       <c r="K426" s="2" t="n"/>
       <c r="L426" s="2" t="n"/>
+      <c r="M426" s="2" t="n"/>
+      <c r="N426" s="2" t="n"/>
+      <c r="O426" s="2" t="n"/>
+      <c r="P426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -12610,6 +14381,10 @@
       </c>
       <c r="K427" s="2" t="n"/>
       <c r="L427" s="2" t="n"/>
+      <c r="M427" s="2" t="n"/>
+      <c r="N427" s="2" t="n"/>
+      <c r="O427" s="2" t="n"/>
+      <c r="P427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -12638,6 +14413,10 @@
       </c>
       <c r="K428" s="2" t="n"/>
       <c r="L428" s="2" t="n"/>
+      <c r="M428" s="2" t="n"/>
+      <c r="N428" s="2" t="n"/>
+      <c r="O428" s="2" t="n"/>
+      <c r="P428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -12666,6 +14445,10 @@
       </c>
       <c r="K429" s="2" t="n"/>
       <c r="L429" s="2" t="n"/>
+      <c r="M429" s="2" t="n"/>
+      <c r="N429" s="2" t="n"/>
+      <c r="O429" s="2" t="n"/>
+      <c r="P429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -12694,6 +14477,10 @@
       </c>
       <c r="K430" s="2" t="n"/>
       <c r="L430" s="2" t="n"/>
+      <c r="M430" s="2" t="n"/>
+      <c r="N430" s="2" t="n"/>
+      <c r="O430" s="2" t="n"/>
+      <c r="P430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -12722,6 +14509,10 @@
       </c>
       <c r="K431" s="2" t="n"/>
       <c r="L431" s="2" t="n"/>
+      <c r="M431" s="2" t="n"/>
+      <c r="N431" s="2" t="n"/>
+      <c r="O431" s="2" t="n"/>
+      <c r="P431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -12750,6 +14541,10 @@
       </c>
       <c r="K432" s="2" t="n"/>
       <c r="L432" s="2" t="n"/>
+      <c r="M432" s="2" t="n"/>
+      <c r="N432" s="2" t="n"/>
+      <c r="O432" s="2" t="n"/>
+      <c r="P432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -12778,6 +14573,10 @@
       </c>
       <c r="K433" s="2" t="n"/>
       <c r="L433" s="2" t="n"/>
+      <c r="M433" s="2" t="n"/>
+      <c r="N433" s="2" t="n"/>
+      <c r="O433" s="2" t="n"/>
+      <c r="P433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -12806,6 +14605,10 @@
       </c>
       <c r="K434" s="2" t="n"/>
       <c r="L434" s="2" t="n"/>
+      <c r="M434" s="2" t="n"/>
+      <c r="N434" s="2" t="n"/>
+      <c r="O434" s="2" t="n"/>
+      <c r="P434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -12834,6 +14637,10 @@
       </c>
       <c r="K435" s="2" t="n"/>
       <c r="L435" s="2" t="n"/>
+      <c r="M435" s="2" t="n"/>
+      <c r="N435" s="2" t="n"/>
+      <c r="O435" s="2" t="n"/>
+      <c r="P435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -12862,6 +14669,10 @@
       </c>
       <c r="K436" s="2" t="n"/>
       <c r="L436" s="2" t="n"/>
+      <c r="M436" s="2" t="n"/>
+      <c r="N436" s="2" t="n"/>
+      <c r="O436" s="2" t="n"/>
+      <c r="P436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -12890,6 +14701,10 @@
       </c>
       <c r="K437" s="2" t="n"/>
       <c r="L437" s="2" t="n"/>
+      <c r="M437" s="2" t="n"/>
+      <c r="N437" s="2" t="n"/>
+      <c r="O437" s="2" t="n"/>
+      <c r="P437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -12918,6 +14733,10 @@
       </c>
       <c r="K438" s="2" t="n"/>
       <c r="L438" s="2" t="n"/>
+      <c r="M438" s="2" t="n"/>
+      <c r="N438" s="2" t="n"/>
+      <c r="O438" s="2" t="n"/>
+      <c r="P438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -12946,6 +14765,10 @@
       </c>
       <c r="K439" s="2" t="n"/>
       <c r="L439" s="2" t="n"/>
+      <c r="M439" s="2" t="n"/>
+      <c r="N439" s="2" t="n"/>
+      <c r="O439" s="2" t="n"/>
+      <c r="P439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -12974,6 +14797,10 @@
       </c>
       <c r="K440" s="2" t="n"/>
       <c r="L440" s="2" t="n"/>
+      <c r="M440" s="2" t="n"/>
+      <c r="N440" s="2" t="n"/>
+      <c r="O440" s="2" t="n"/>
+      <c r="P440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -13002,6 +14829,10 @@
       </c>
       <c r="K441" s="2" t="n"/>
       <c r="L441" s="2" t="n"/>
+      <c r="M441" s="2" t="n"/>
+      <c r="N441" s="2" t="n"/>
+      <c r="O441" s="2" t="n"/>
+      <c r="P441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -13030,6 +14861,10 @@
       </c>
       <c r="K442" s="2" t="n"/>
       <c r="L442" s="2" t="n"/>
+      <c r="M442" s="2" t="n"/>
+      <c r="N442" s="2" t="n"/>
+      <c r="O442" s="2" t="n"/>
+      <c r="P442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -13058,6 +14893,10 @@
       </c>
       <c r="K443" s="2" t="n"/>
       <c r="L443" s="2" t="n"/>
+      <c r="M443" s="2" t="n"/>
+      <c r="N443" s="2" t="n"/>
+      <c r="O443" s="2" t="n"/>
+      <c r="P443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -13086,6 +14925,10 @@
       </c>
       <c r="K444" s="2" t="n"/>
       <c r="L444" s="2" t="n"/>
+      <c r="M444" s="2" t="n"/>
+      <c r="N444" s="2" t="n"/>
+      <c r="O444" s="2" t="n"/>
+      <c r="P444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -13114,6 +14957,10 @@
       </c>
       <c r="K445" s="2" t="n"/>
       <c r="L445" s="2" t="n"/>
+      <c r="M445" s="2" t="n"/>
+      <c r="N445" s="2" t="n"/>
+      <c r="O445" s="2" t="n"/>
+      <c r="P445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -13142,6 +14989,10 @@
       </c>
       <c r="K446" s="2" t="n"/>
       <c r="L446" s="2" t="n"/>
+      <c r="M446" s="2" t="n"/>
+      <c r="N446" s="2" t="n"/>
+      <c r="O446" s="2" t="n"/>
+      <c r="P446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -13170,6 +15021,10 @@
       </c>
       <c r="K447" s="2" t="n"/>
       <c r="L447" s="2" t="n"/>
+      <c r="M447" s="2" t="n"/>
+      <c r="N447" s="2" t="n"/>
+      <c r="O447" s="2" t="n"/>
+      <c r="P447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -13198,6 +15053,10 @@
       </c>
       <c r="K448" s="2" t="n"/>
       <c r="L448" s="2" t="n"/>
+      <c r="M448" s="2" t="n"/>
+      <c r="N448" s="2" t="n"/>
+      <c r="O448" s="2" t="n"/>
+      <c r="P448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -13226,6 +15085,10 @@
       </c>
       <c r="K449" s="2" t="n"/>
       <c r="L449" s="2" t="n"/>
+      <c r="M449" s="2" t="n"/>
+      <c r="N449" s="2" t="n"/>
+      <c r="O449" s="2" t="n"/>
+      <c r="P449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -13254,6 +15117,10 @@
       </c>
       <c r="K450" s="2" t="n"/>
       <c r="L450" s="2" t="n"/>
+      <c r="M450" s="2" t="n"/>
+      <c r="N450" s="2" t="n"/>
+      <c r="O450" s="2" t="n"/>
+      <c r="P450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -13282,6 +15149,10 @@
       </c>
       <c r="K451" s="2" t="n"/>
       <c r="L451" s="2" t="n"/>
+      <c r="M451" s="2" t="n"/>
+      <c r="N451" s="2" t="n"/>
+      <c r="O451" s="2" t="n"/>
+      <c r="P451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -13310,6 +15181,10 @@
       </c>
       <c r="K452" s="2" t="n"/>
       <c r="L452" s="2" t="n"/>
+      <c r="M452" s="2" t="n"/>
+      <c r="N452" s="2" t="n"/>
+      <c r="O452" s="2" t="n"/>
+      <c r="P452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -13338,6 +15213,10 @@
       </c>
       <c r="K453" s="2" t="n"/>
       <c r="L453" s="2" t="n"/>
+      <c r="M453" s="2" t="n"/>
+      <c r="N453" s="2" t="n"/>
+      <c r="O453" s="2" t="n"/>
+      <c r="P453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -13366,6 +15245,10 @@
       </c>
       <c r="K454" s="2" t="n"/>
       <c r="L454" s="2" t="n"/>
+      <c r="M454" s="2" t="n"/>
+      <c r="N454" s="2" t="n"/>
+      <c r="O454" s="2" t="n"/>
+      <c r="P454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -13394,6 +15277,10 @@
       </c>
       <c r="K455" s="2" t="n"/>
       <c r="L455" s="2" t="n"/>
+      <c r="M455" s="2" t="n"/>
+      <c r="N455" s="2" t="n"/>
+      <c r="O455" s="2" t="n"/>
+      <c r="P455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -13422,6 +15309,10 @@
       </c>
       <c r="K456" s="2" t="n"/>
       <c r="L456" s="2" t="n"/>
+      <c r="M456" s="2" t="n"/>
+      <c r="N456" s="2" t="n"/>
+      <c r="O456" s="2" t="n"/>
+      <c r="P456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -13450,6 +15341,10 @@
       </c>
       <c r="K457" s="2" t="n"/>
       <c r="L457" s="2" t="n"/>
+      <c r="M457" s="2" t="n"/>
+      <c r="N457" s="2" t="n"/>
+      <c r="O457" s="2" t="n"/>
+      <c r="P457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -13478,6 +15373,10 @@
       </c>
       <c r="K458" s="2" t="n"/>
       <c r="L458" s="2" t="n"/>
+      <c r="M458" s="2" t="n"/>
+      <c r="N458" s="2" t="n"/>
+      <c r="O458" s="2" t="n"/>
+      <c r="P458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -13506,6 +15405,10 @@
       </c>
       <c r="K459" s="2" t="n"/>
       <c r="L459" s="2" t="n"/>
+      <c r="M459" s="2" t="n"/>
+      <c r="N459" s="2" t="n"/>
+      <c r="O459" s="2" t="n"/>
+      <c r="P459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -13534,6 +15437,10 @@
       </c>
       <c r="K460" s="2" t="n"/>
       <c r="L460" s="2" t="n"/>
+      <c r="M460" s="2" t="n"/>
+      <c r="N460" s="2" t="n"/>
+      <c r="O460" s="2" t="n"/>
+      <c r="P460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -13562,6 +15469,10 @@
       </c>
       <c r="K461" s="2" t="n"/>
       <c r="L461" s="2" t="n"/>
+      <c r="M461" s="2" t="n"/>
+      <c r="N461" s="2" t="n"/>
+      <c r="O461" s="2" t="n"/>
+      <c r="P461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -13590,6 +15501,10 @@
       </c>
       <c r="K462" s="2" t="n"/>
       <c r="L462" s="2" t="n"/>
+      <c r="M462" s="2" t="n"/>
+      <c r="N462" s="2" t="n"/>
+      <c r="O462" s="2" t="n"/>
+      <c r="P462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -13618,6 +15533,10 @@
       </c>
       <c r="K463" s="2" t="n"/>
       <c r="L463" s="2" t="n"/>
+      <c r="M463" s="2" t="n"/>
+      <c r="N463" s="2" t="n"/>
+      <c r="O463" s="2" t="n"/>
+      <c r="P463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -13646,6 +15565,10 @@
       </c>
       <c r="K464" s="2" t="n"/>
       <c r="L464" s="2" t="n"/>
+      <c r="M464" s="2" t="n"/>
+      <c r="N464" s="2" t="n"/>
+      <c r="O464" s="2" t="n"/>
+      <c r="P464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -13674,6 +15597,10 @@
       </c>
       <c r="K465" s="2" t="n"/>
       <c r="L465" s="2" t="n"/>
+      <c r="M465" s="2" t="n"/>
+      <c r="N465" s="2" t="n"/>
+      <c r="O465" s="2" t="n"/>
+      <c r="P465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -13702,6 +15629,10 @@
       </c>
       <c r="K466" s="2" t="n"/>
       <c r="L466" s="2" t="n"/>
+      <c r="M466" s="2" t="n"/>
+      <c r="N466" s="2" t="n"/>
+      <c r="O466" s="2" t="n"/>
+      <c r="P466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -13730,6 +15661,10 @@
       </c>
       <c r="K467" s="2" t="n"/>
       <c r="L467" s="2" t="n"/>
+      <c r="M467" s="2" t="n"/>
+      <c r="N467" s="2" t="n"/>
+      <c r="O467" s="2" t="n"/>
+      <c r="P467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -13758,6 +15693,10 @@
       </c>
       <c r="K468" s="2" t="n"/>
       <c r="L468" s="2" t="n"/>
+      <c r="M468" s="2" t="n"/>
+      <c r="N468" s="2" t="n"/>
+      <c r="O468" s="2" t="n"/>
+      <c r="P468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -13786,6 +15725,10 @@
       </c>
       <c r="K469" s="2" t="n"/>
       <c r="L469" s="2" t="n"/>
+      <c r="M469" s="2" t="n"/>
+      <c r="N469" s="2" t="n"/>
+      <c r="O469" s="2" t="n"/>
+      <c r="P469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -13814,6 +15757,10 @@
       </c>
       <c r="K470" s="2" t="n"/>
       <c r="L470" s="2" t="n"/>
+      <c r="M470" s="2" t="n"/>
+      <c r="N470" s="2" t="n"/>
+      <c r="O470" s="2" t="n"/>
+      <c r="P470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -13842,6 +15789,10 @@
       </c>
       <c r="K471" s="2" t="n"/>
       <c r="L471" s="2" t="n"/>
+      <c r="M471" s="2" t="n"/>
+      <c r="N471" s="2" t="n"/>
+      <c r="O471" s="2" t="n"/>
+      <c r="P471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -13870,6 +15821,10 @@
       </c>
       <c r="K472" s="2" t="n"/>
       <c r="L472" s="2" t="n"/>
+      <c r="M472" s="2" t="n"/>
+      <c r="N472" s="2" t="n"/>
+      <c r="O472" s="2" t="n"/>
+      <c r="P472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -13898,6 +15853,10 @@
       </c>
       <c r="K473" s="2" t="n"/>
       <c r="L473" s="2" t="n"/>
+      <c r="M473" s="2" t="n"/>
+      <c r="N473" s="2" t="n"/>
+      <c r="O473" s="2" t="n"/>
+      <c r="P473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -13926,6 +15885,10 @@
       </c>
       <c r="K474" s="2" t="n"/>
       <c r="L474" s="2" t="n"/>
+      <c r="M474" s="2" t="n"/>
+      <c r="N474" s="2" t="n"/>
+      <c r="O474" s="2" t="n"/>
+      <c r="P474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -13954,6 +15917,10 @@
       </c>
       <c r="K475" s="2" t="n"/>
       <c r="L475" s="2" t="n"/>
+      <c r="M475" s="2" t="n"/>
+      <c r="N475" s="2" t="n"/>
+      <c r="O475" s="2" t="n"/>
+      <c r="P475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -13982,6 +15949,10 @@
       </c>
       <c r="K476" s="2" t="n"/>
       <c r="L476" s="2" t="n"/>
+      <c r="M476" s="2" t="n"/>
+      <c r="N476" s="2" t="n"/>
+      <c r="O476" s="2" t="n"/>
+      <c r="P476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -14010,6 +15981,10 @@
       </c>
       <c r="K477" s="2" t="n"/>
       <c r="L477" s="2" t="n"/>
+      <c r="M477" s="2" t="n"/>
+      <c r="N477" s="2" t="n"/>
+      <c r="O477" s="2" t="n"/>
+      <c r="P477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -14038,6 +16013,10 @@
       </c>
       <c r="K478" s="2" t="n"/>
       <c r="L478" s="2" t="n"/>
+      <c r="M478" s="2" t="n"/>
+      <c r="N478" s="2" t="n"/>
+      <c r="O478" s="2" t="n"/>
+      <c r="P478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -14066,6 +16045,10 @@
       </c>
       <c r="K479" s="2" t="n"/>
       <c r="L479" s="2" t="n"/>
+      <c r="M479" s="2" t="n"/>
+      <c r="N479" s="2" t="n"/>
+      <c r="O479" s="2" t="n"/>
+      <c r="P479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -14094,6 +16077,10 @@
       </c>
       <c r="K480" s="2" t="n"/>
       <c r="L480" s="2" t="n"/>
+      <c r="M480" s="2" t="n"/>
+      <c r="N480" s="2" t="n"/>
+      <c r="O480" s="2" t="n"/>
+      <c r="P480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -14122,6 +16109,10 @@
       </c>
       <c r="K481" s="2" t="n"/>
       <c r="L481" s="2" t="n"/>
+      <c r="M481" s="2" t="n"/>
+      <c r="N481" s="2" t="n"/>
+      <c r="O481" s="2" t="n"/>
+      <c r="P481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -14150,6 +16141,10 @@
       </c>
       <c r="K482" s="2" t="n"/>
       <c r="L482" s="2" t="n"/>
+      <c r="M482" s="2" t="n"/>
+      <c r="N482" s="2" t="n"/>
+      <c r="O482" s="2" t="n"/>
+      <c r="P482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -14178,6 +16173,10 @@
       </c>
       <c r="K483" s="2" t="n"/>
       <c r="L483" s="2" t="n"/>
+      <c r="M483" s="2" t="n"/>
+      <c r="N483" s="2" t="n"/>
+      <c r="O483" s="2" t="n"/>
+      <c r="P483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -14206,6 +16205,10 @@
       </c>
       <c r="K484" s="2" t="n"/>
       <c r="L484" s="2" t="n"/>
+      <c r="M484" s="2" t="n"/>
+      <c r="N484" s="2" t="n"/>
+      <c r="O484" s="2" t="n"/>
+      <c r="P484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -14234,6 +16237,10 @@
       </c>
       <c r="K485" s="2" t="n"/>
       <c r="L485" s="2" t="n"/>
+      <c r="M485" s="2" t="n"/>
+      <c r="N485" s="2" t="n"/>
+      <c r="O485" s="2" t="n"/>
+      <c r="P485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -14262,6 +16269,10 @@
       </c>
       <c r="K486" s="2" t="n"/>
       <c r="L486" s="2" t="n"/>
+      <c r="M486" s="2" t="n"/>
+      <c r="N486" s="2" t="n"/>
+      <c r="O486" s="2" t="n"/>
+      <c r="P486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -14290,6 +16301,10 @@
       </c>
       <c r="K487" s="2" t="n"/>
       <c r="L487" s="2" t="n"/>
+      <c r="M487" s="2" t="n"/>
+      <c r="N487" s="2" t="n"/>
+      <c r="O487" s="2" t="n"/>
+      <c r="P487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -14318,6 +16333,10 @@
       </c>
       <c r="K488" s="2" t="n"/>
       <c r="L488" s="2" t="n"/>
+      <c r="M488" s="2" t="n"/>
+      <c r="N488" s="2" t="n"/>
+      <c r="O488" s="2" t="n"/>
+      <c r="P488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -14346,6 +16365,10 @@
       </c>
       <c r="K489" s="2" t="n"/>
       <c r="L489" s="2" t="n"/>
+      <c r="M489" s="2" t="n"/>
+      <c r="N489" s="2" t="n"/>
+      <c r="O489" s="2" t="n"/>
+      <c r="P489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -14374,6 +16397,10 @@
       </c>
       <c r="K490" s="2" t="n"/>
       <c r="L490" s="2" t="n"/>
+      <c r="M490" s="2" t="n"/>
+      <c r="N490" s="2" t="n"/>
+      <c r="O490" s="2" t="n"/>
+      <c r="P490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -14402,6 +16429,10 @@
       </c>
       <c r="K491" s="2" t="n"/>
       <c r="L491" s="2" t="n"/>
+      <c r="M491" s="2" t="n"/>
+      <c r="N491" s="2" t="n"/>
+      <c r="O491" s="2" t="n"/>
+      <c r="P491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -14430,6 +16461,10 @@
       </c>
       <c r="K492" s="2" t="n"/>
       <c r="L492" s="2" t="n"/>
+      <c r="M492" s="2" t="n"/>
+      <c r="N492" s="2" t="n"/>
+      <c r="O492" s="2" t="n"/>
+      <c r="P492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -14458,6 +16493,10 @@
       </c>
       <c r="K493" s="2" t="n"/>
       <c r="L493" s="2" t="n"/>
+      <c r="M493" s="2" t="n"/>
+      <c r="N493" s="2" t="n"/>
+      <c r="O493" s="2" t="n"/>
+      <c r="P493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -14486,6 +16525,10 @@
       </c>
       <c r="K494" s="2" t="n"/>
       <c r="L494" s="2" t="n"/>
+      <c r="M494" s="2" t="n"/>
+      <c r="N494" s="2" t="n"/>
+      <c r="O494" s="2" t="n"/>
+      <c r="P494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -14514,6 +16557,10 @@
       </c>
       <c r="K495" s="2" t="n"/>
       <c r="L495" s="2" t="n"/>
+      <c r="M495" s="2" t="n"/>
+      <c r="N495" s="2" t="n"/>
+      <c r="O495" s="2" t="n"/>
+      <c r="P495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -14542,6 +16589,10 @@
       </c>
       <c r="K496" s="2" t="n"/>
       <c r="L496" s="2" t="n"/>
+      <c r="M496" s="2" t="n"/>
+      <c r="N496" s="2" t="n"/>
+      <c r="O496" s="2" t="n"/>
+      <c r="P496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -14570,6 +16621,10 @@
       </c>
       <c r="K497" s="2" t="n"/>
       <c r="L497" s="2" t="n"/>
+      <c r="M497" s="2" t="n"/>
+      <c r="N497" s="2" t="n"/>
+      <c r="O497" s="2" t="n"/>
+      <c r="P497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -14598,6 +16653,10 @@
       </c>
       <c r="K498" s="2" t="n"/>
       <c r="L498" s="2" t="n"/>
+      <c r="M498" s="2" t="n"/>
+      <c r="N498" s="2" t="n"/>
+      <c r="O498" s="2" t="n"/>
+      <c r="P498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -14626,6 +16685,10 @@
       </c>
       <c r="K499" s="2" t="n"/>
       <c r="L499" s="2" t="n"/>
+      <c r="M499" s="2" t="n"/>
+      <c r="N499" s="2" t="n"/>
+      <c r="O499" s="2" t="n"/>
+      <c r="P499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -14654,6 +16717,10 @@
       </c>
       <c r="K500" s="2" t="n"/>
       <c r="L500" s="2" t="n"/>
+      <c r="M500" s="2" t="n"/>
+      <c r="N500" s="2" t="n"/>
+      <c r="O500" s="2" t="n"/>
+      <c r="P500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -14682,14 +16749,13 @@
       </c>
       <c r="K501" s="2" t="n"/>
       <c r="L501" s="2" t="n"/>
+      <c r="M501" s="2" t="n"/>
+      <c r="N501" s="2" t="n"/>
+      <c r="O501" s="2" t="n"/>
+      <c r="P501" s="2" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F501">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>F2="Dynamic"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="8">
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
       <formula1>=ChallengeStates</formula1>
     </dataValidation>
@@ -14701,6 +16767,18 @@
     </dataValidation>
     <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number greater than or equal to 0." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
+      <formula1>=ScoringFunctions</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Enter a whole number greater than or equal to 0." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Enter a whole number greater than or equal to 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
+      <formula1>=BonusModes</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26878,7 +28956,3063 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D501"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Start Placement</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>End Placement</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n"/>
+      <c r="C201" s="2" t="n"/>
+      <c r="D201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n"/>
+      <c r="C203" s="2" t="n"/>
+      <c r="D203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n"/>
+      <c r="B205" s="2" t="n"/>
+      <c r="C205" s="2" t="n"/>
+      <c r="D205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n"/>
+      <c r="C207" s="2" t="n"/>
+      <c r="D207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="2" t="n"/>
+      <c r="D208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n"/>
+      <c r="C209" s="2" t="n"/>
+      <c r="D209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n"/>
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="2" t="n"/>
+      <c r="D210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="2" t="n"/>
+      <c r="D211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="n"/>
+      <c r="D212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="n"/>
+      <c r="D213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n"/>
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n"/>
+      <c r="B215" s="2" t="n"/>
+      <c r="C215" s="2" t="n"/>
+      <c r="D215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n"/>
+      <c r="B216" s="2" t="n"/>
+      <c r="C216" s="2" t="n"/>
+      <c r="D216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n"/>
+      <c r="B217" s="2" t="n"/>
+      <c r="C217" s="2" t="n"/>
+      <c r="D217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n"/>
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n"/>
+      <c r="B219" s="2" t="n"/>
+      <c r="C219" s="2" t="n"/>
+      <c r="D219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n"/>
+      <c r="B220" s="2" t="n"/>
+      <c r="C220" s="2" t="n"/>
+      <c r="D220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n"/>
+      <c r="B221" s="2" t="n"/>
+      <c r="C221" s="2" t="n"/>
+      <c r="D221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n"/>
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="2" t="n"/>
+      <c r="D222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n"/>
+      <c r="B223" s="2" t="n"/>
+      <c r="C223" s="2" t="n"/>
+      <c r="D223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n"/>
+      <c r="B224" s="2" t="n"/>
+      <c r="C224" s="2" t="n"/>
+      <c r="D224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n"/>
+      <c r="B225" s="2" t="n"/>
+      <c r="C225" s="2" t="n"/>
+      <c r="D225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n"/>
+      <c r="B226" s="2" t="n"/>
+      <c r="C226" s="2" t="n"/>
+      <c r="D226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n"/>
+      <c r="B227" s="2" t="n"/>
+      <c r="C227" s="2" t="n"/>
+      <c r="D227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n"/>
+      <c r="B228" s="2" t="n"/>
+      <c r="C228" s="2" t="n"/>
+      <c r="D228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n"/>
+      <c r="B229" s="2" t="n"/>
+      <c r="C229" s="2" t="n"/>
+      <c r="D229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n"/>
+      <c r="B230" s="2" t="n"/>
+      <c r="C230" s="2" t="n"/>
+      <c r="D230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n"/>
+      <c r="B231" s="2" t="n"/>
+      <c r="C231" s="2" t="n"/>
+      <c r="D231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n"/>
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="2" t="n"/>
+      <c r="D232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n"/>
+      <c r="B233" s="2" t="n"/>
+      <c r="C233" s="2" t="n"/>
+      <c r="D233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n"/>
+      <c r="B234" s="2" t="n"/>
+      <c r="C234" s="2" t="n"/>
+      <c r="D234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n"/>
+      <c r="B235" s="2" t="n"/>
+      <c r="C235" s="2" t="n"/>
+      <c r="D235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n"/>
+      <c r="B236" s="2" t="n"/>
+      <c r="C236" s="2" t="n"/>
+      <c r="D236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n"/>
+      <c r="B237" s="2" t="n"/>
+      <c r="C237" s="2" t="n"/>
+      <c r="D237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n"/>
+      <c r="B238" s="2" t="n"/>
+      <c r="C238" s="2" t="n"/>
+      <c r="D238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n"/>
+      <c r="B239" s="2" t="n"/>
+      <c r="C239" s="2" t="n"/>
+      <c r="D239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n"/>
+      <c r="B240" s="2" t="n"/>
+      <c r="C240" s="2" t="n"/>
+      <c r="D240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n"/>
+      <c r="B241" s="2" t="n"/>
+      <c r="C241" s="2" t="n"/>
+      <c r="D241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n"/>
+      <c r="B242" s="2" t="n"/>
+      <c r="C242" s="2" t="n"/>
+      <c r="D242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n"/>
+      <c r="B243" s="2" t="n"/>
+      <c r="C243" s="2" t="n"/>
+      <c r="D243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n"/>
+      <c r="B244" s="2" t="n"/>
+      <c r="C244" s="2" t="n"/>
+      <c r="D244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n"/>
+      <c r="B245" s="2" t="n"/>
+      <c r="C245" s="2" t="n"/>
+      <c r="D245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n"/>
+      <c r="B246" s="2" t="n"/>
+      <c r="C246" s="2" t="n"/>
+      <c r="D246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n"/>
+      <c r="B247" s="2" t="n"/>
+      <c r="C247" s="2" t="n"/>
+      <c r="D247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n"/>
+      <c r="B248" s="2" t="n"/>
+      <c r="C248" s="2" t="n"/>
+      <c r="D248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n"/>
+      <c r="B249" s="2" t="n"/>
+      <c r="C249" s="2" t="n"/>
+      <c r="D249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n"/>
+      <c r="B250" s="2" t="n"/>
+      <c r="C250" s="2" t="n"/>
+      <c r="D250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n"/>
+      <c r="B251" s="2" t="n"/>
+      <c r="C251" s="2" t="n"/>
+      <c r="D251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n"/>
+      <c r="B252" s="2" t="n"/>
+      <c r="C252" s="2" t="n"/>
+      <c r="D252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n"/>
+      <c r="B253" s="2" t="n"/>
+      <c r="C253" s="2" t="n"/>
+      <c r="D253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n"/>
+      <c r="B254" s="2" t="n"/>
+      <c r="C254" s="2" t="n"/>
+      <c r="D254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n"/>
+      <c r="B255" s="2" t="n"/>
+      <c r="C255" s="2" t="n"/>
+      <c r="D255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n"/>
+      <c r="B256" s="2" t="n"/>
+      <c r="C256" s="2" t="n"/>
+      <c r="D256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n"/>
+      <c r="B257" s="2" t="n"/>
+      <c r="C257" s="2" t="n"/>
+      <c r="D257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n"/>
+      <c r="B258" s="2" t="n"/>
+      <c r="C258" s="2" t="n"/>
+      <c r="D258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n"/>
+      <c r="B259" s="2" t="n"/>
+      <c r="C259" s="2" t="n"/>
+      <c r="D259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n"/>
+      <c r="B260" s="2" t="n"/>
+      <c r="C260" s="2" t="n"/>
+      <c r="D260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n"/>
+      <c r="B261" s="2" t="n"/>
+      <c r="C261" s="2" t="n"/>
+      <c r="D261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n"/>
+      <c r="B262" s="2" t="n"/>
+      <c r="C262" s="2" t="n"/>
+      <c r="D262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n"/>
+      <c r="B263" s="2" t="n"/>
+      <c r="C263" s="2" t="n"/>
+      <c r="D263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n"/>
+      <c r="B264" s="2" t="n"/>
+      <c r="C264" s="2" t="n"/>
+      <c r="D264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n"/>
+      <c r="B265" s="2" t="n"/>
+      <c r="C265" s="2" t="n"/>
+      <c r="D265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n"/>
+      <c r="B266" s="2" t="n"/>
+      <c r="C266" s="2" t="n"/>
+      <c r="D266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n"/>
+      <c r="B267" s="2" t="n"/>
+      <c r="C267" s="2" t="n"/>
+      <c r="D267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n"/>
+      <c r="B268" s="2" t="n"/>
+      <c r="C268" s="2" t="n"/>
+      <c r="D268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n"/>
+      <c r="B269" s="2" t="n"/>
+      <c r="C269" s="2" t="n"/>
+      <c r="D269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n"/>
+      <c r="B270" s="2" t="n"/>
+      <c r="C270" s="2" t="n"/>
+      <c r="D270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n"/>
+      <c r="B271" s="2" t="n"/>
+      <c r="C271" s="2" t="n"/>
+      <c r="D271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n"/>
+      <c r="B272" s="2" t="n"/>
+      <c r="C272" s="2" t="n"/>
+      <c r="D272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n"/>
+      <c r="B273" s="2" t="n"/>
+      <c r="C273" s="2" t="n"/>
+      <c r="D273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n"/>
+      <c r="B274" s="2" t="n"/>
+      <c r="C274" s="2" t="n"/>
+      <c r="D274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n"/>
+      <c r="B275" s="2" t="n"/>
+      <c r="C275" s="2" t="n"/>
+      <c r="D275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n"/>
+      <c r="B276" s="2" t="n"/>
+      <c r="C276" s="2" t="n"/>
+      <c r="D276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n"/>
+      <c r="B277" s="2" t="n"/>
+      <c r="C277" s="2" t="n"/>
+      <c r="D277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n"/>
+      <c r="B278" s="2" t="n"/>
+      <c r="C278" s="2" t="n"/>
+      <c r="D278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n"/>
+      <c r="B279" s="2" t="n"/>
+      <c r="C279" s="2" t="n"/>
+      <c r="D279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n"/>
+      <c r="B280" s="2" t="n"/>
+      <c r="C280" s="2" t="n"/>
+      <c r="D280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n"/>
+      <c r="B281" s="2" t="n"/>
+      <c r="C281" s="2" t="n"/>
+      <c r="D281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n"/>
+      <c r="B282" s="2" t="n"/>
+      <c r="C282" s="2" t="n"/>
+      <c r="D282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n"/>
+      <c r="B283" s="2" t="n"/>
+      <c r="C283" s="2" t="n"/>
+      <c r="D283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n"/>
+      <c r="B284" s="2" t="n"/>
+      <c r="C284" s="2" t="n"/>
+      <c r="D284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n"/>
+      <c r="B285" s="2" t="n"/>
+      <c r="C285" s="2" t="n"/>
+      <c r="D285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n"/>
+      <c r="B286" s="2" t="n"/>
+      <c r="C286" s="2" t="n"/>
+      <c r="D286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n"/>
+      <c r="B287" s="2" t="n"/>
+      <c r="C287" s="2" t="n"/>
+      <c r="D287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n"/>
+      <c r="B288" s="2" t="n"/>
+      <c r="C288" s="2" t="n"/>
+      <c r="D288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n"/>
+      <c r="B289" s="2" t="n"/>
+      <c r="C289" s="2" t="n"/>
+      <c r="D289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n"/>
+      <c r="B290" s="2" t="n"/>
+      <c r="C290" s="2" t="n"/>
+      <c r="D290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n"/>
+      <c r="B291" s="2" t="n"/>
+      <c r="C291" s="2" t="n"/>
+      <c r="D291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n"/>
+      <c r="B292" s="2" t="n"/>
+      <c r="C292" s="2" t="n"/>
+      <c r="D292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n"/>
+      <c r="B293" s="2" t="n"/>
+      <c r="C293" s="2" t="n"/>
+      <c r="D293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n"/>
+      <c r="B294" s="2" t="n"/>
+      <c r="C294" s="2" t="n"/>
+      <c r="D294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n"/>
+      <c r="B295" s="2" t="n"/>
+      <c r="C295" s="2" t="n"/>
+      <c r="D295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n"/>
+      <c r="B296" s="2" t="n"/>
+      <c r="C296" s="2" t="n"/>
+      <c r="D296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n"/>
+      <c r="B297" s="2" t="n"/>
+      <c r="C297" s="2" t="n"/>
+      <c r="D297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n"/>
+      <c r="B298" s="2" t="n"/>
+      <c r="C298" s="2" t="n"/>
+      <c r="D298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n"/>
+      <c r="B299" s="2" t="n"/>
+      <c r="C299" s="2" t="n"/>
+      <c r="D299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n"/>
+      <c r="B300" s="2" t="n"/>
+      <c r="C300" s="2" t="n"/>
+      <c r="D300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n"/>
+      <c r="B301" s="2" t="n"/>
+      <c r="C301" s="2" t="n"/>
+      <c r="D301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n"/>
+      <c r="B302" s="2" t="n"/>
+      <c r="C302" s="2" t="n"/>
+      <c r="D302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n"/>
+      <c r="B303" s="2" t="n"/>
+      <c r="C303" s="2" t="n"/>
+      <c r="D303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n"/>
+      <c r="B304" s="2" t="n"/>
+      <c r="C304" s="2" t="n"/>
+      <c r="D304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n"/>
+      <c r="B305" s="2" t="n"/>
+      <c r="C305" s="2" t="n"/>
+      <c r="D305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n"/>
+      <c r="B306" s="2" t="n"/>
+      <c r="C306" s="2" t="n"/>
+      <c r="D306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n"/>
+      <c r="B307" s="2" t="n"/>
+      <c r="C307" s="2" t="n"/>
+      <c r="D307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n"/>
+      <c r="B308" s="2" t="n"/>
+      <c r="C308" s="2" t="n"/>
+      <c r="D308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n"/>
+      <c r="B309" s="2" t="n"/>
+      <c r="C309" s="2" t="n"/>
+      <c r="D309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n"/>
+      <c r="B310" s="2" t="n"/>
+      <c r="C310" s="2" t="n"/>
+      <c r="D310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n"/>
+      <c r="B311" s="2" t="n"/>
+      <c r="C311" s="2" t="n"/>
+      <c r="D311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n"/>
+      <c r="B312" s="2" t="n"/>
+      <c r="C312" s="2" t="n"/>
+      <c r="D312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n"/>
+      <c r="B313" s="2" t="n"/>
+      <c r="C313" s="2" t="n"/>
+      <c r="D313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n"/>
+      <c r="B314" s="2" t="n"/>
+      <c r="C314" s="2" t="n"/>
+      <c r="D314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n"/>
+      <c r="B315" s="2" t="n"/>
+      <c r="C315" s="2" t="n"/>
+      <c r="D315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n"/>
+      <c r="B316" s="2" t="n"/>
+      <c r="C316" s="2" t="n"/>
+      <c r="D316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n"/>
+      <c r="B317" s="2" t="n"/>
+      <c r="C317" s="2" t="n"/>
+      <c r="D317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n"/>
+      <c r="B318" s="2" t="n"/>
+      <c r="C318" s="2" t="n"/>
+      <c r="D318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n"/>
+      <c r="B319" s="2" t="n"/>
+      <c r="C319" s="2" t="n"/>
+      <c r="D319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n"/>
+      <c r="B320" s="2" t="n"/>
+      <c r="C320" s="2" t="n"/>
+      <c r="D320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n"/>
+      <c r="B321" s="2" t="n"/>
+      <c r="C321" s="2" t="n"/>
+      <c r="D321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n"/>
+      <c r="B322" s="2" t="n"/>
+      <c r="C322" s="2" t="n"/>
+      <c r="D322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n"/>
+      <c r="B323" s="2" t="n"/>
+      <c r="C323" s="2" t="n"/>
+      <c r="D323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n"/>
+      <c r="B324" s="2" t="n"/>
+      <c r="C324" s="2" t="n"/>
+      <c r="D324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n"/>
+      <c r="B325" s="2" t="n"/>
+      <c r="C325" s="2" t="n"/>
+      <c r="D325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n"/>
+      <c r="B326" s="2" t="n"/>
+      <c r="C326" s="2" t="n"/>
+      <c r="D326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n"/>
+      <c r="B327" s="2" t="n"/>
+      <c r="C327" s="2" t="n"/>
+      <c r="D327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n"/>
+      <c r="B328" s="2" t="n"/>
+      <c r="C328" s="2" t="n"/>
+      <c r="D328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n"/>
+      <c r="B329" s="2" t="n"/>
+      <c r="C329" s="2" t="n"/>
+      <c r="D329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n"/>
+      <c r="B330" s="2" t="n"/>
+      <c r="C330" s="2" t="n"/>
+      <c r="D330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n"/>
+      <c r="B331" s="2" t="n"/>
+      <c r="C331" s="2" t="n"/>
+      <c r="D331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n"/>
+      <c r="B332" s="2" t="n"/>
+      <c r="C332" s="2" t="n"/>
+      <c r="D332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n"/>
+      <c r="B333" s="2" t="n"/>
+      <c r="C333" s="2" t="n"/>
+      <c r="D333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n"/>
+      <c r="B334" s="2" t="n"/>
+      <c r="C334" s="2" t="n"/>
+      <c r="D334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n"/>
+      <c r="B335" s="2" t="n"/>
+      <c r="C335" s="2" t="n"/>
+      <c r="D335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n"/>
+      <c r="B336" s="2" t="n"/>
+      <c r="C336" s="2" t="n"/>
+      <c r="D336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n"/>
+      <c r="B337" s="2" t="n"/>
+      <c r="C337" s="2" t="n"/>
+      <c r="D337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n"/>
+      <c r="B338" s="2" t="n"/>
+      <c r="C338" s="2" t="n"/>
+      <c r="D338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n"/>
+      <c r="B339" s="2" t="n"/>
+      <c r="C339" s="2" t="n"/>
+      <c r="D339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n"/>
+      <c r="B340" s="2" t="n"/>
+      <c r="C340" s="2" t="n"/>
+      <c r="D340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n"/>
+      <c r="B341" s="2" t="n"/>
+      <c r="C341" s="2" t="n"/>
+      <c r="D341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n"/>
+      <c r="B342" s="2" t="n"/>
+      <c r="C342" s="2" t="n"/>
+      <c r="D342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n"/>
+      <c r="B343" s="2" t="n"/>
+      <c r="C343" s="2" t="n"/>
+      <c r="D343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n"/>
+      <c r="B344" s="2" t="n"/>
+      <c r="C344" s="2" t="n"/>
+      <c r="D344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n"/>
+      <c r="B345" s="2" t="n"/>
+      <c r="C345" s="2" t="n"/>
+      <c r="D345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n"/>
+      <c r="B346" s="2" t="n"/>
+      <c r="C346" s="2" t="n"/>
+      <c r="D346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n"/>
+      <c r="B347" s="2" t="n"/>
+      <c r="C347" s="2" t="n"/>
+      <c r="D347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n"/>
+      <c r="B348" s="2" t="n"/>
+      <c r="C348" s="2" t="n"/>
+      <c r="D348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n"/>
+      <c r="B349" s="2" t="n"/>
+      <c r="C349" s="2" t="n"/>
+      <c r="D349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n"/>
+      <c r="B350" s="2" t="n"/>
+      <c r="C350" s="2" t="n"/>
+      <c r="D350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n"/>
+      <c r="B351" s="2" t="n"/>
+      <c r="C351" s="2" t="n"/>
+      <c r="D351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n"/>
+      <c r="B352" s="2" t="n"/>
+      <c r="C352" s="2" t="n"/>
+      <c r="D352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n"/>
+      <c r="B353" s="2" t="n"/>
+      <c r="C353" s="2" t="n"/>
+      <c r="D353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n"/>
+      <c r="B354" s="2" t="n"/>
+      <c r="C354" s="2" t="n"/>
+      <c r="D354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n"/>
+      <c r="B355" s="2" t="n"/>
+      <c r="C355" s="2" t="n"/>
+      <c r="D355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n"/>
+      <c r="B356" s="2" t="n"/>
+      <c r="C356" s="2" t="n"/>
+      <c r="D356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n"/>
+      <c r="B357" s="2" t="n"/>
+      <c r="C357" s="2" t="n"/>
+      <c r="D357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n"/>
+      <c r="B358" s="2" t="n"/>
+      <c r="C358" s="2" t="n"/>
+      <c r="D358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n"/>
+      <c r="B359" s="2" t="n"/>
+      <c r="C359" s="2" t="n"/>
+      <c r="D359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n"/>
+      <c r="B360" s="2" t="n"/>
+      <c r="C360" s="2" t="n"/>
+      <c r="D360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n"/>
+      <c r="B361" s="2" t="n"/>
+      <c r="C361" s="2" t="n"/>
+      <c r="D361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n"/>
+      <c r="B362" s="2" t="n"/>
+      <c r="C362" s="2" t="n"/>
+      <c r="D362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n"/>
+      <c r="B363" s="2" t="n"/>
+      <c r="C363" s="2" t="n"/>
+      <c r="D363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n"/>
+      <c r="B364" s="2" t="n"/>
+      <c r="C364" s="2" t="n"/>
+      <c r="D364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n"/>
+      <c r="B365" s="2" t="n"/>
+      <c r="C365" s="2" t="n"/>
+      <c r="D365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="n"/>
+      <c r="B366" s="2" t="n"/>
+      <c r="C366" s="2" t="n"/>
+      <c r="D366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n"/>
+      <c r="B367" s="2" t="n"/>
+      <c r="C367" s="2" t="n"/>
+      <c r="D367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n"/>
+      <c r="B368" s="2" t="n"/>
+      <c r="C368" s="2" t="n"/>
+      <c r="D368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n"/>
+      <c r="B369" s="2" t="n"/>
+      <c r="C369" s="2" t="n"/>
+      <c r="D369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n"/>
+      <c r="B370" s="2" t="n"/>
+      <c r="C370" s="2" t="n"/>
+      <c r="D370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n"/>
+      <c r="B371" s="2" t="n"/>
+      <c r="C371" s="2" t="n"/>
+      <c r="D371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n"/>
+      <c r="B372" s="2" t="n"/>
+      <c r="C372" s="2" t="n"/>
+      <c r="D372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n"/>
+      <c r="B373" s="2" t="n"/>
+      <c r="C373" s="2" t="n"/>
+      <c r="D373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n"/>
+      <c r="B374" s="2" t="n"/>
+      <c r="C374" s="2" t="n"/>
+      <c r="D374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n"/>
+      <c r="B375" s="2" t="n"/>
+      <c r="C375" s="2" t="n"/>
+      <c r="D375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n"/>
+      <c r="B376" s="2" t="n"/>
+      <c r="C376" s="2" t="n"/>
+      <c r="D376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n"/>
+      <c r="B377" s="2" t="n"/>
+      <c r="C377" s="2" t="n"/>
+      <c r="D377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n"/>
+      <c r="B378" s="2" t="n"/>
+      <c r="C378" s="2" t="n"/>
+      <c r="D378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n"/>
+      <c r="B379" s="2" t="n"/>
+      <c r="C379" s="2" t="n"/>
+      <c r="D379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n"/>
+      <c r="B380" s="2" t="n"/>
+      <c r="C380" s="2" t="n"/>
+      <c r="D380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n"/>
+      <c r="B381" s="2" t="n"/>
+      <c r="C381" s="2" t="n"/>
+      <c r="D381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n"/>
+      <c r="B382" s="2" t="n"/>
+      <c r="C382" s="2" t="n"/>
+      <c r="D382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n"/>
+      <c r="B383" s="2" t="n"/>
+      <c r="C383" s="2" t="n"/>
+      <c r="D383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n"/>
+      <c r="B384" s="2" t="n"/>
+      <c r="C384" s="2" t="n"/>
+      <c r="D384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n"/>
+      <c r="B385" s="2" t="n"/>
+      <c r="C385" s="2" t="n"/>
+      <c r="D385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n"/>
+      <c r="B386" s="2" t="n"/>
+      <c r="C386" s="2" t="n"/>
+      <c r="D386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n"/>
+      <c r="B387" s="2" t="n"/>
+      <c r="C387" s="2" t="n"/>
+      <c r="D387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n"/>
+      <c r="B388" s="2" t="n"/>
+      <c r="C388" s="2" t="n"/>
+      <c r="D388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n"/>
+      <c r="B389" s="2" t="n"/>
+      <c r="C389" s="2" t="n"/>
+      <c r="D389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n"/>
+      <c r="B390" s="2" t="n"/>
+      <c r="C390" s="2" t="n"/>
+      <c r="D390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n"/>
+      <c r="B391" s="2" t="n"/>
+      <c r="C391" s="2" t="n"/>
+      <c r="D391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n"/>
+      <c r="B392" s="2" t="n"/>
+      <c r="C392" s="2" t="n"/>
+      <c r="D392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n"/>
+      <c r="B393" s="2" t="n"/>
+      <c r="C393" s="2" t="n"/>
+      <c r="D393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n"/>
+      <c r="B394" s="2" t="n"/>
+      <c r="C394" s="2" t="n"/>
+      <c r="D394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n"/>
+      <c r="B395" s="2" t="n"/>
+      <c r="C395" s="2" t="n"/>
+      <c r="D395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n"/>
+      <c r="B396" s="2" t="n"/>
+      <c r="C396" s="2" t="n"/>
+      <c r="D396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n"/>
+      <c r="B397" s="2" t="n"/>
+      <c r="C397" s="2" t="n"/>
+      <c r="D397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n"/>
+      <c r="B398" s="2" t="n"/>
+      <c r="C398" s="2" t="n"/>
+      <c r="D398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n"/>
+      <c r="B399" s="2" t="n"/>
+      <c r="C399" s="2" t="n"/>
+      <c r="D399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n"/>
+      <c r="B400" s="2" t="n"/>
+      <c r="C400" s="2" t="n"/>
+      <c r="D400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n"/>
+      <c r="B401" s="2" t="n"/>
+      <c r="C401" s="2" t="n"/>
+      <c r="D401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n"/>
+      <c r="B402" s="2" t="n"/>
+      <c r="C402" s="2" t="n"/>
+      <c r="D402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n"/>
+      <c r="B403" s="2" t="n"/>
+      <c r="C403" s="2" t="n"/>
+      <c r="D403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n"/>
+      <c r="B404" s="2" t="n"/>
+      <c r="C404" s="2" t="n"/>
+      <c r="D404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n"/>
+      <c r="B405" s="2" t="n"/>
+      <c r="C405" s="2" t="n"/>
+      <c r="D405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n"/>
+      <c r="B406" s="2" t="n"/>
+      <c r="C406" s="2" t="n"/>
+      <c r="D406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n"/>
+      <c r="B407" s="2" t="n"/>
+      <c r="C407" s="2" t="n"/>
+      <c r="D407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n"/>
+      <c r="B408" s="2" t="n"/>
+      <c r="C408" s="2" t="n"/>
+      <c r="D408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n"/>
+      <c r="B409" s="2" t="n"/>
+      <c r="C409" s="2" t="n"/>
+      <c r="D409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n"/>
+      <c r="B410" s="2" t="n"/>
+      <c r="C410" s="2" t="n"/>
+      <c r="D410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n"/>
+      <c r="B411" s="2" t="n"/>
+      <c r="C411" s="2" t="n"/>
+      <c r="D411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n"/>
+      <c r="B412" s="2" t="n"/>
+      <c r="C412" s="2" t="n"/>
+      <c r="D412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n"/>
+      <c r="B413" s="2" t="n"/>
+      <c r="C413" s="2" t="n"/>
+      <c r="D413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n"/>
+      <c r="B414" s="2" t="n"/>
+      <c r="C414" s="2" t="n"/>
+      <c r="D414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n"/>
+      <c r="B415" s="2" t="n"/>
+      <c r="C415" s="2" t="n"/>
+      <c r="D415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n"/>
+      <c r="B416" s="2" t="n"/>
+      <c r="C416" s="2" t="n"/>
+      <c r="D416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n"/>
+      <c r="B417" s="2" t="n"/>
+      <c r="C417" s="2" t="n"/>
+      <c r="D417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n"/>
+      <c r="B418" s="2" t="n"/>
+      <c r="C418" s="2" t="n"/>
+      <c r="D418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n"/>
+      <c r="B419" s="2" t="n"/>
+      <c r="C419" s="2" t="n"/>
+      <c r="D419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n"/>
+      <c r="B420" s="2" t="n"/>
+      <c r="C420" s="2" t="n"/>
+      <c r="D420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n"/>
+      <c r="B421" s="2" t="n"/>
+      <c r="C421" s="2" t="n"/>
+      <c r="D421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n"/>
+      <c r="B422" s="2" t="n"/>
+      <c r="C422" s="2" t="n"/>
+      <c r="D422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n"/>
+      <c r="B423" s="2" t="n"/>
+      <c r="C423" s="2" t="n"/>
+      <c r="D423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n"/>
+      <c r="B424" s="2" t="n"/>
+      <c r="C424" s="2" t="n"/>
+      <c r="D424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n"/>
+      <c r="B425" s="2" t="n"/>
+      <c r="C425" s="2" t="n"/>
+      <c r="D425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="n"/>
+      <c r="B426" s="2" t="n"/>
+      <c r="C426" s="2" t="n"/>
+      <c r="D426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n"/>
+      <c r="B427" s="2" t="n"/>
+      <c r="C427" s="2" t="n"/>
+      <c r="D427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n"/>
+      <c r="B428" s="2" t="n"/>
+      <c r="C428" s="2" t="n"/>
+      <c r="D428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n"/>
+      <c r="B429" s="2" t="n"/>
+      <c r="C429" s="2" t="n"/>
+      <c r="D429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n"/>
+      <c r="B430" s="2" t="n"/>
+      <c r="C430" s="2" t="n"/>
+      <c r="D430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n"/>
+      <c r="B431" s="2" t="n"/>
+      <c r="C431" s="2" t="n"/>
+      <c r="D431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n"/>
+      <c r="B432" s="2" t="n"/>
+      <c r="C432" s="2" t="n"/>
+      <c r="D432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n"/>
+      <c r="B433" s="2" t="n"/>
+      <c r="C433" s="2" t="n"/>
+      <c r="D433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n"/>
+      <c r="B434" s="2" t="n"/>
+      <c r="C434" s="2" t="n"/>
+      <c r="D434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n"/>
+      <c r="B435" s="2" t="n"/>
+      <c r="C435" s="2" t="n"/>
+      <c r="D435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n"/>
+      <c r="B436" s="2" t="n"/>
+      <c r="C436" s="2" t="n"/>
+      <c r="D436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n"/>
+      <c r="B437" s="2" t="n"/>
+      <c r="C437" s="2" t="n"/>
+      <c r="D437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n"/>
+      <c r="B438" s="2" t="n"/>
+      <c r="C438" s="2" t="n"/>
+      <c r="D438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n"/>
+      <c r="B439" s="2" t="n"/>
+      <c r="C439" s="2" t="n"/>
+      <c r="D439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n"/>
+      <c r="B440" s="2" t="n"/>
+      <c r="C440" s="2" t="n"/>
+      <c r="D440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n"/>
+      <c r="B441" s="2" t="n"/>
+      <c r="C441" s="2" t="n"/>
+      <c r="D441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n"/>
+      <c r="B442" s="2" t="n"/>
+      <c r="C442" s="2" t="n"/>
+      <c r="D442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n"/>
+      <c r="B443" s="2" t="n"/>
+      <c r="C443" s="2" t="n"/>
+      <c r="D443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n"/>
+      <c r="B444" s="2" t="n"/>
+      <c r="C444" s="2" t="n"/>
+      <c r="D444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n"/>
+      <c r="B445" s="2" t="n"/>
+      <c r="C445" s="2" t="n"/>
+      <c r="D445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n"/>
+      <c r="B446" s="2" t="n"/>
+      <c r="C446" s="2" t="n"/>
+      <c r="D446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n"/>
+      <c r="B447" s="2" t="n"/>
+      <c r="C447" s="2" t="n"/>
+      <c r="D447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n"/>
+      <c r="B448" s="2" t="n"/>
+      <c r="C448" s="2" t="n"/>
+      <c r="D448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n"/>
+      <c r="B449" s="2" t="n"/>
+      <c r="C449" s="2" t="n"/>
+      <c r="D449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n"/>
+      <c r="B450" s="2" t="n"/>
+      <c r="C450" s="2" t="n"/>
+      <c r="D450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n"/>
+      <c r="B451" s="2" t="n"/>
+      <c r="C451" s="2" t="n"/>
+      <c r="D451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n"/>
+      <c r="B452" s="2" t="n"/>
+      <c r="C452" s="2" t="n"/>
+      <c r="D452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n"/>
+      <c r="B453" s="2" t="n"/>
+      <c r="C453" s="2" t="n"/>
+      <c r="D453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n"/>
+      <c r="B454" s="2" t="n"/>
+      <c r="C454" s="2" t="n"/>
+      <c r="D454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n"/>
+      <c r="B455" s="2" t="n"/>
+      <c r="C455" s="2" t="n"/>
+      <c r="D455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n"/>
+      <c r="B456" s="2" t="n"/>
+      <c r="C456" s="2" t="n"/>
+      <c r="D456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n"/>
+      <c r="B457" s="2" t="n"/>
+      <c r="C457" s="2" t="n"/>
+      <c r="D457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n"/>
+      <c r="B458" s="2" t="n"/>
+      <c r="C458" s="2" t="n"/>
+      <c r="D458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n"/>
+      <c r="B459" s="2" t="n"/>
+      <c r="C459" s="2" t="n"/>
+      <c r="D459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n"/>
+      <c r="B460" s="2" t="n"/>
+      <c r="C460" s="2" t="n"/>
+      <c r="D460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n"/>
+      <c r="B461" s="2" t="n"/>
+      <c r="C461" s="2" t="n"/>
+      <c r="D461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n"/>
+      <c r="B462" s="2" t="n"/>
+      <c r="C462" s="2" t="n"/>
+      <c r="D462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n"/>
+      <c r="B463" s="2" t="n"/>
+      <c r="C463" s="2" t="n"/>
+      <c r="D463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n"/>
+      <c r="B464" s="2" t="n"/>
+      <c r="C464" s="2" t="n"/>
+      <c r="D464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n"/>
+      <c r="B465" s="2" t="n"/>
+      <c r="C465" s="2" t="n"/>
+      <c r="D465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n"/>
+      <c r="B466" s="2" t="n"/>
+      <c r="C466" s="2" t="n"/>
+      <c r="D466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n"/>
+      <c r="B467" s="2" t="n"/>
+      <c r="C467" s="2" t="n"/>
+      <c r="D467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n"/>
+      <c r="B468" s="2" t="n"/>
+      <c r="C468" s="2" t="n"/>
+      <c r="D468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n"/>
+      <c r="B469" s="2" t="n"/>
+      <c r="C469" s="2" t="n"/>
+      <c r="D469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n"/>
+      <c r="B470" s="2" t="n"/>
+      <c r="C470" s="2" t="n"/>
+      <c r="D470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n"/>
+      <c r="B471" s="2" t="n"/>
+      <c r="C471" s="2" t="n"/>
+      <c r="D471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n"/>
+      <c r="B472" s="2" t="n"/>
+      <c r="C472" s="2" t="n"/>
+      <c r="D472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n"/>
+      <c r="B473" s="2" t="n"/>
+      <c r="C473" s="2" t="n"/>
+      <c r="D473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n"/>
+      <c r="B474" s="2" t="n"/>
+      <c r="C474" s="2" t="n"/>
+      <c r="D474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n"/>
+      <c r="B475" s="2" t="n"/>
+      <c r="C475" s="2" t="n"/>
+      <c r="D475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n"/>
+      <c r="B476" s="2" t="n"/>
+      <c r="C476" s="2" t="n"/>
+      <c r="D476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n"/>
+      <c r="B477" s="2" t="n"/>
+      <c r="C477" s="2" t="n"/>
+      <c r="D477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n"/>
+      <c r="B478" s="2" t="n"/>
+      <c r="C478" s="2" t="n"/>
+      <c r="D478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n"/>
+      <c r="B479" s="2" t="n"/>
+      <c r="C479" s="2" t="n"/>
+      <c r="D479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n"/>
+      <c r="B480" s="2" t="n"/>
+      <c r="C480" s="2" t="n"/>
+      <c r="D480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n"/>
+      <c r="B481" s="2" t="n"/>
+      <c r="C481" s="2" t="n"/>
+      <c r="D481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n"/>
+      <c r="B482" s="2" t="n"/>
+      <c r="C482" s="2" t="n"/>
+      <c r="D482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n"/>
+      <c r="B483" s="2" t="n"/>
+      <c r="C483" s="2" t="n"/>
+      <c r="D483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n"/>
+      <c r="B484" s="2" t="n"/>
+      <c r="C484" s="2" t="n"/>
+      <c r="D484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n"/>
+      <c r="B485" s="2" t="n"/>
+      <c r="C485" s="2" t="n"/>
+      <c r="D485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n"/>
+      <c r="B486" s="2" t="n"/>
+      <c r="C486" s="2" t="n"/>
+      <c r="D486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n"/>
+      <c r="B487" s="2" t="n"/>
+      <c r="C487" s="2" t="n"/>
+      <c r="D487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n"/>
+      <c r="B488" s="2" t="n"/>
+      <c r="C488" s="2" t="n"/>
+      <c r="D488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n"/>
+      <c r="B489" s="2" t="n"/>
+      <c r="C489" s="2" t="n"/>
+      <c r="D489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n"/>
+      <c r="B490" s="2" t="n"/>
+      <c r="C490" s="2" t="n"/>
+      <c r="D490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n"/>
+      <c r="B491" s="2" t="n"/>
+      <c r="C491" s="2" t="n"/>
+      <c r="D491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n"/>
+      <c r="B492" s="2" t="n"/>
+      <c r="C492" s="2" t="n"/>
+      <c r="D492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n"/>
+      <c r="B493" s="2" t="n"/>
+      <c r="C493" s="2" t="n"/>
+      <c r="D493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n"/>
+      <c r="B494" s="2" t="n"/>
+      <c r="C494" s="2" t="n"/>
+      <c r="D494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n"/>
+      <c r="B495" s="2" t="n"/>
+      <c r="C495" s="2" t="n"/>
+      <c r="D495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n"/>
+      <c r="B496" s="2" t="n"/>
+      <c r="C496" s="2" t="n"/>
+      <c r="D496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n"/>
+      <c r="B497" s="2" t="n"/>
+      <c r="C497" s="2" t="n"/>
+      <c r="D497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n"/>
+      <c r="B498" s="2" t="n"/>
+      <c r="C498" s="2" t="n"/>
+      <c r="D498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n"/>
+      <c r="B499" s="2" t="n"/>
+      <c r="C499" s="2" t="n"/>
+      <c r="D499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n"/>
+      <c r="B500" s="2" t="n"/>
+      <c r="C500" s="2" t="n"/>
+      <c r="D500" s="2" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n"/>
+      <c r="B501" s="2" t="n"/>
+      <c r="C501" s="2" t="n"/>
+      <c r="D501" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
+      <formula1>=ChallengeNames</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number greater than or equal to 1." type="whole" operator="greaterThanOrEqual">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a nonnegative number." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26912,6 +32046,16 @@
           <t>Solution States</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Scoring Functions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bonus Modes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26944,6 +32088,16 @@
           <t>Hidden</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Disabled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26976,6 +32130,16 @@
           <t>Visible</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Logarithmic</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Absolute</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26986,6 +32150,11 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Solved</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Percentage</t>
         </is>
       </c>
     </row>

--- a/tools/push-challenges-template.xlsx
+++ b/tools/push-challenges-template.xlsx
@@ -160,9 +160,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChallengesTable" displayName="ChallengesTable" ref="A1:P501" headerRowCount="1">
-  <autoFilter ref="A1:P501"/>
-  <tableColumns count="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ChallengesTable" displayName="ChallengesTable" ref="A1:Q501" headerRowCount="1">
+  <autoFilter ref="A1:Q501"/>
+  <tableColumns count="17">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Description"/>
     <tableColumn id="3" name="Value"/>
@@ -179,6 +179,7 @@
     <tableColumn id="14" name="Minimum Value"/>
     <tableColumn id="15" name="Decay"/>
     <tableColumn id="16" name="Bonus Mode"/>
+    <tableColumn id="17" name="Position"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -525,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -637,6 +638,18 @@
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Existing Standard/Dynamic type mismatches skip only that challenge. Review MANUAL ACTION REQUIRED at the end of every import. Change types manually in CTFd and rerun. Files remain manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Optional display order: positive whole numbers sort lowest first. 0 uses CTFd automatic point ordering. Blank preserves an existing position or leaves a new challenge at 0. Next is navigation, not order.</t>
         </is>
       </c>
     </row>
@@ -651,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P501"/>
+  <dimension ref="A1:Q501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -670,6 +683,7 @@
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,6 +765,11 @@
       <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Bonus Mode</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Position</t>
         </is>
       </c>
     </row>
@@ -785,6 +804,7 @@
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -817,6 +837,7 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -849,6 +870,7 @@
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -881,6 +903,7 @@
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -913,6 +936,7 @@
       <c r="N6" s="2" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -945,6 +969,7 @@
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -977,6 +1002,7 @@
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1009,6 +1035,7 @@
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1041,6 +1068,7 @@
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1073,6 +1101,7 @@
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1105,6 +1134,7 @@
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1137,6 +1167,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1169,6 +1200,7 @@
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1201,6 +1233,7 @@
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1233,6 +1266,7 @@
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1265,6 +1299,7 @@
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1297,6 +1332,7 @@
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1329,6 +1365,7 @@
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1361,6 +1398,7 @@
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1393,6 +1431,7 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1425,6 +1464,7 @@
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1457,6 +1497,7 @@
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1489,6 +1530,7 @@
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1521,6 +1563,7 @@
       <c r="N25" s="2" t="n"/>
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1553,6 +1596,7 @@
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1585,6 +1629,7 @@
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1617,6 +1662,7 @@
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1649,6 +1695,7 @@
       <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1681,6 +1728,7 @@
       <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1713,6 +1761,7 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1745,6 +1794,7 @@
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -1777,6 +1827,7 @@
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1809,6 +1860,7 @@
       <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -1841,6 +1893,7 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1873,6 +1926,7 @@
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1905,6 +1959,7 @@
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1937,6 +1992,7 @@
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -1969,6 +2025,7 @@
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2001,6 +2058,7 @@
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2033,6 +2091,7 @@
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2065,6 +2124,7 @@
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2097,6 +2157,7 @@
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2129,6 +2190,7 @@
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2161,6 +2223,7 @@
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2193,6 +2256,7 @@
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2225,6 +2289,7 @@
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2257,6 +2322,7 @@
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="n"/>
+      <c r="Q48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -2289,6 +2355,7 @@
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2321,6 +2388,7 @@
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -2353,6 +2421,7 @@
       <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2385,6 +2454,7 @@
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -2417,6 +2487,7 @@
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -2449,6 +2520,7 @@
       <c r="N54" s="2" t="n"/>
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -2481,6 +2553,7 @@
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -2513,6 +2586,7 @@
       <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -2545,6 +2619,7 @@
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -2577,6 +2652,7 @@
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -2609,6 +2685,7 @@
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="n"/>
+      <c r="Q59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -2641,6 +2718,7 @@
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -2673,6 +2751,7 @@
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="n"/>
+      <c r="Q61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -2705,6 +2784,7 @@
       <c r="N62" s="2" t="n"/>
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="n"/>
+      <c r="Q62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -2737,6 +2817,7 @@
       <c r="N63" s="2" t="n"/>
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="n"/>
+      <c r="Q63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -2769,6 +2850,7 @@
       <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -2801,6 +2883,7 @@
       <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="n"/>
+      <c r="Q65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -2833,6 +2916,7 @@
       <c r="N66" s="2" t="n"/>
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="n"/>
+      <c r="Q66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -2865,6 +2949,7 @@
       <c r="N67" s="2" t="n"/>
       <c r="O67" s="2" t="n"/>
       <c r="P67" s="2" t="n"/>
+      <c r="Q67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -2897,6 +2982,7 @@
       <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="n"/>
+      <c r="Q68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -2929,6 +3015,7 @@
       <c r="N69" s="2" t="n"/>
       <c r="O69" s="2" t="n"/>
       <c r="P69" s="2" t="n"/>
+      <c r="Q69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -2961,6 +3048,7 @@
       <c r="N70" s="2" t="n"/>
       <c r="O70" s="2" t="n"/>
       <c r="P70" s="2" t="n"/>
+      <c r="Q70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -2993,6 +3081,7 @@
       <c r="N71" s="2" t="n"/>
       <c r="O71" s="2" t="n"/>
       <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -3025,6 +3114,7 @@
       <c r="N72" s="2" t="n"/>
       <c r="O72" s="2" t="n"/>
       <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -3057,6 +3147,7 @@
       <c r="N73" s="2" t="n"/>
       <c r="O73" s="2" t="n"/>
       <c r="P73" s="2" t="n"/>
+      <c r="Q73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -3089,6 +3180,7 @@
       <c r="N74" s="2" t="n"/>
       <c r="O74" s="2" t="n"/>
       <c r="P74" s="2" t="n"/>
+      <c r="Q74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -3121,6 +3213,7 @@
       <c r="N75" s="2" t="n"/>
       <c r="O75" s="2" t="n"/>
       <c r="P75" s="2" t="n"/>
+      <c r="Q75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -3153,6 +3246,7 @@
       <c r="N76" s="2" t="n"/>
       <c r="O76" s="2" t="n"/>
       <c r="P76" s="2" t="n"/>
+      <c r="Q76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -3185,6 +3279,7 @@
       <c r="N77" s="2" t="n"/>
       <c r="O77" s="2" t="n"/>
       <c r="P77" s="2" t="n"/>
+      <c r="Q77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -3217,6 +3312,7 @@
       <c r="N78" s="2" t="n"/>
       <c r="O78" s="2" t="n"/>
       <c r="P78" s="2" t="n"/>
+      <c r="Q78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -3249,6 +3345,7 @@
       <c r="N79" s="2" t="n"/>
       <c r="O79" s="2" t="n"/>
       <c r="P79" s="2" t="n"/>
+      <c r="Q79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -3281,6 +3378,7 @@
       <c r="N80" s="2" t="n"/>
       <c r="O80" s="2" t="n"/>
       <c r="P80" s="2" t="n"/>
+      <c r="Q80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -3313,6 +3411,7 @@
       <c r="N81" s="2" t="n"/>
       <c r="O81" s="2" t="n"/>
       <c r="P81" s="2" t="n"/>
+      <c r="Q81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -3345,6 +3444,7 @@
       <c r="N82" s="2" t="n"/>
       <c r="O82" s="2" t="n"/>
       <c r="P82" s="2" t="n"/>
+      <c r="Q82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -3377,6 +3477,7 @@
       <c r="N83" s="2" t="n"/>
       <c r="O83" s="2" t="n"/>
       <c r="P83" s="2" t="n"/>
+      <c r="Q83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -3409,6 +3510,7 @@
       <c r="N84" s="2" t="n"/>
       <c r="O84" s="2" t="n"/>
       <c r="P84" s="2" t="n"/>
+      <c r="Q84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -3441,6 +3543,7 @@
       <c r="N85" s="2" t="n"/>
       <c r="O85" s="2" t="n"/>
       <c r="P85" s="2" t="n"/>
+      <c r="Q85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -3473,6 +3576,7 @@
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="n"/>
+      <c r="Q86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -3505,6 +3609,7 @@
       <c r="N87" s="2" t="n"/>
       <c r="O87" s="2" t="n"/>
       <c r="P87" s="2" t="n"/>
+      <c r="Q87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -3537,6 +3642,7 @@
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="2" t="n"/>
       <c r="P88" s="2" t="n"/>
+      <c r="Q88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -3569,6 +3675,7 @@
       <c r="N89" s="2" t="n"/>
       <c r="O89" s="2" t="n"/>
       <c r="P89" s="2" t="n"/>
+      <c r="Q89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -3601,6 +3708,7 @@
       <c r="N90" s="2" t="n"/>
       <c r="O90" s="2" t="n"/>
       <c r="P90" s="2" t="n"/>
+      <c r="Q90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -3633,6 +3741,7 @@
       <c r="N91" s="2" t="n"/>
       <c r="O91" s="2" t="n"/>
       <c r="P91" s="2" t="n"/>
+      <c r="Q91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -3665,6 +3774,7 @@
       <c r="N92" s="2" t="n"/>
       <c r="O92" s="2" t="n"/>
       <c r="P92" s="2" t="n"/>
+      <c r="Q92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -3697,6 +3807,7 @@
       <c r="N93" s="2" t="n"/>
       <c r="O93" s="2" t="n"/>
       <c r="P93" s="2" t="n"/>
+      <c r="Q93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -3729,6 +3840,7 @@
       <c r="N94" s="2" t="n"/>
       <c r="O94" s="2" t="n"/>
       <c r="P94" s="2" t="n"/>
+      <c r="Q94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -3761,6 +3873,7 @@
       <c r="N95" s="2" t="n"/>
       <c r="O95" s="2" t="n"/>
       <c r="P95" s="2" t="n"/>
+      <c r="Q95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -3793,6 +3906,7 @@
       <c r="N96" s="2" t="n"/>
       <c r="O96" s="2" t="n"/>
       <c r="P96" s="2" t="n"/>
+      <c r="Q96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -3825,6 +3939,7 @@
       <c r="N97" s="2" t="n"/>
       <c r="O97" s="2" t="n"/>
       <c r="P97" s="2" t="n"/>
+      <c r="Q97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -3857,6 +3972,7 @@
       <c r="N98" s="2" t="n"/>
       <c r="O98" s="2" t="n"/>
       <c r="P98" s="2" t="n"/>
+      <c r="Q98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -3889,6 +4005,7 @@
       <c r="N99" s="2" t="n"/>
       <c r="O99" s="2" t="n"/>
       <c r="P99" s="2" t="n"/>
+      <c r="Q99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -3921,6 +4038,7 @@
       <c r="N100" s="2" t="n"/>
       <c r="O100" s="2" t="n"/>
       <c r="P100" s="2" t="n"/>
+      <c r="Q100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -3953,6 +4071,7 @@
       <c r="N101" s="2" t="n"/>
       <c r="O101" s="2" t="n"/>
       <c r="P101" s="2" t="n"/>
+      <c r="Q101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -3985,6 +4104,7 @@
       <c r="N102" s="2" t="n"/>
       <c r="O102" s="2" t="n"/>
       <c r="P102" s="2" t="n"/>
+      <c r="Q102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -4017,6 +4137,7 @@
       <c r="N103" s="2" t="n"/>
       <c r="O103" s="2" t="n"/>
       <c r="P103" s="2" t="n"/>
+      <c r="Q103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -4049,6 +4170,7 @@
       <c r="N104" s="2" t="n"/>
       <c r="O104" s="2" t="n"/>
       <c r="P104" s="2" t="n"/>
+      <c r="Q104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -4081,6 +4203,7 @@
       <c r="N105" s="2" t="n"/>
       <c r="O105" s="2" t="n"/>
       <c r="P105" s="2" t="n"/>
+      <c r="Q105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -4113,6 +4236,7 @@
       <c r="N106" s="2" t="n"/>
       <c r="O106" s="2" t="n"/>
       <c r="P106" s="2" t="n"/>
+      <c r="Q106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -4145,6 +4269,7 @@
       <c r="N107" s="2" t="n"/>
       <c r="O107" s="2" t="n"/>
       <c r="P107" s="2" t="n"/>
+      <c r="Q107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -4177,6 +4302,7 @@
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="n"/>
       <c r="P108" s="2" t="n"/>
+      <c r="Q108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -4209,6 +4335,7 @@
       <c r="N109" s="2" t="n"/>
       <c r="O109" s="2" t="n"/>
       <c r="P109" s="2" t="n"/>
+      <c r="Q109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -4241,6 +4368,7 @@
       <c r="N110" s="2" t="n"/>
       <c r="O110" s="2" t="n"/>
       <c r="P110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -4273,6 +4401,7 @@
       <c r="N111" s="2" t="n"/>
       <c r="O111" s="2" t="n"/>
       <c r="P111" s="2" t="n"/>
+      <c r="Q111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -4305,6 +4434,7 @@
       <c r="N112" s="2" t="n"/>
       <c r="O112" s="2" t="n"/>
       <c r="P112" s="2" t="n"/>
+      <c r="Q112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -4337,6 +4467,7 @@
       <c r="N113" s="2" t="n"/>
       <c r="O113" s="2" t="n"/>
       <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -4369,6 +4500,7 @@
       <c r="N114" s="2" t="n"/>
       <c r="O114" s="2" t="n"/>
       <c r="P114" s="2" t="n"/>
+      <c r="Q114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -4401,6 +4533,7 @@
       <c r="N115" s="2" t="n"/>
       <c r="O115" s="2" t="n"/>
       <c r="P115" s="2" t="n"/>
+      <c r="Q115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -4433,6 +4566,7 @@
       <c r="N116" s="2" t="n"/>
       <c r="O116" s="2" t="n"/>
       <c r="P116" s="2" t="n"/>
+      <c r="Q116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -4465,6 +4599,7 @@
       <c r="N117" s="2" t="n"/>
       <c r="O117" s="2" t="n"/>
       <c r="P117" s="2" t="n"/>
+      <c r="Q117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -4497,6 +4632,7 @@
       <c r="N118" s="2" t="n"/>
       <c r="O118" s="2" t="n"/>
       <c r="P118" s="2" t="n"/>
+      <c r="Q118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -4529,6 +4665,7 @@
       <c r="N119" s="2" t="n"/>
       <c r="O119" s="2" t="n"/>
       <c r="P119" s="2" t="n"/>
+      <c r="Q119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -4561,6 +4698,7 @@
       <c r="N120" s="2" t="n"/>
       <c r="O120" s="2" t="n"/>
       <c r="P120" s="2" t="n"/>
+      <c r="Q120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -4593,6 +4731,7 @@
       <c r="N121" s="2" t="n"/>
       <c r="O121" s="2" t="n"/>
       <c r="P121" s="2" t="n"/>
+      <c r="Q121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -4625,6 +4764,7 @@
       <c r="N122" s="2" t="n"/>
       <c r="O122" s="2" t="n"/>
       <c r="P122" s="2" t="n"/>
+      <c r="Q122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -4657,6 +4797,7 @@
       <c r="N123" s="2" t="n"/>
       <c r="O123" s="2" t="n"/>
       <c r="P123" s="2" t="n"/>
+      <c r="Q123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -4689,6 +4830,7 @@
       <c r="N124" s="2" t="n"/>
       <c r="O124" s="2" t="n"/>
       <c r="P124" s="2" t="n"/>
+      <c r="Q124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -4721,6 +4863,7 @@
       <c r="N125" s="2" t="n"/>
       <c r="O125" s="2" t="n"/>
       <c r="P125" s="2" t="n"/>
+      <c r="Q125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -4753,6 +4896,7 @@
       <c r="N126" s="2" t="n"/>
       <c r="O126" s="2" t="n"/>
       <c r="P126" s="2" t="n"/>
+      <c r="Q126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -4785,6 +4929,7 @@
       <c r="N127" s="2" t="n"/>
       <c r="O127" s="2" t="n"/>
       <c r="P127" s="2" t="n"/>
+      <c r="Q127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -4817,6 +4962,7 @@
       <c r="N128" s="2" t="n"/>
       <c r="O128" s="2" t="n"/>
       <c r="P128" s="2" t="n"/>
+      <c r="Q128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -4849,6 +4995,7 @@
       <c r="N129" s="2" t="n"/>
       <c r="O129" s="2" t="n"/>
       <c r="P129" s="2" t="n"/>
+      <c r="Q129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -4881,6 +5028,7 @@
       <c r="N130" s="2" t="n"/>
       <c r="O130" s="2" t="n"/>
       <c r="P130" s="2" t="n"/>
+      <c r="Q130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -4913,6 +5061,7 @@
       <c r="N131" s="2" t="n"/>
       <c r="O131" s="2" t="n"/>
       <c r="P131" s="2" t="n"/>
+      <c r="Q131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -4945,6 +5094,7 @@
       <c r="N132" s="2" t="n"/>
       <c r="O132" s="2" t="n"/>
       <c r="P132" s="2" t="n"/>
+      <c r="Q132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -4977,6 +5127,7 @@
       <c r="N133" s="2" t="n"/>
       <c r="O133" s="2" t="n"/>
       <c r="P133" s="2" t="n"/>
+      <c r="Q133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -5009,6 +5160,7 @@
       <c r="N134" s="2" t="n"/>
       <c r="O134" s="2" t="n"/>
       <c r="P134" s="2" t="n"/>
+      <c r="Q134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -5041,6 +5193,7 @@
       <c r="N135" s="2" t="n"/>
       <c r="O135" s="2" t="n"/>
       <c r="P135" s="2" t="n"/>
+      <c r="Q135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -5073,6 +5226,7 @@
       <c r="N136" s="2" t="n"/>
       <c r="O136" s="2" t="n"/>
       <c r="P136" s="2" t="n"/>
+      <c r="Q136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -5105,6 +5259,7 @@
       <c r="N137" s="2" t="n"/>
       <c r="O137" s="2" t="n"/>
       <c r="P137" s="2" t="n"/>
+      <c r="Q137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -5137,6 +5292,7 @@
       <c r="N138" s="2" t="n"/>
       <c r="O138" s="2" t="n"/>
       <c r="P138" s="2" t="n"/>
+      <c r="Q138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -5169,6 +5325,7 @@
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="n"/>
       <c r="P139" s="2" t="n"/>
+      <c r="Q139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -5201,6 +5358,7 @@
       <c r="N140" s="2" t="n"/>
       <c r="O140" s="2" t="n"/>
       <c r="P140" s="2" t="n"/>
+      <c r="Q140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -5233,6 +5391,7 @@
       <c r="N141" s="2" t="n"/>
       <c r="O141" s="2" t="n"/>
       <c r="P141" s="2" t="n"/>
+      <c r="Q141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -5265,6 +5424,7 @@
       <c r="N142" s="2" t="n"/>
       <c r="O142" s="2" t="n"/>
       <c r="P142" s="2" t="n"/>
+      <c r="Q142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -5297,6 +5457,7 @@
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="2" t="n"/>
       <c r="P143" s="2" t="n"/>
+      <c r="Q143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -5329,6 +5490,7 @@
       <c r="N144" s="2" t="n"/>
       <c r="O144" s="2" t="n"/>
       <c r="P144" s="2" t="n"/>
+      <c r="Q144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -5361,6 +5523,7 @@
       <c r="N145" s="2" t="n"/>
       <c r="O145" s="2" t="n"/>
       <c r="P145" s="2" t="n"/>
+      <c r="Q145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -5393,6 +5556,7 @@
       <c r="N146" s="2" t="n"/>
       <c r="O146" s="2" t="n"/>
       <c r="P146" s="2" t="n"/>
+      <c r="Q146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -5425,6 +5589,7 @@
       <c r="N147" s="2" t="n"/>
       <c r="O147" s="2" t="n"/>
       <c r="P147" s="2" t="n"/>
+      <c r="Q147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -5457,6 +5622,7 @@
       <c r="N148" s="2" t="n"/>
       <c r="O148" s="2" t="n"/>
       <c r="P148" s="2" t="n"/>
+      <c r="Q148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -5489,6 +5655,7 @@
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="2" t="n"/>
       <c r="P149" s="2" t="n"/>
+      <c r="Q149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -5521,6 +5688,7 @@
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="2" t="n"/>
       <c r="P150" s="2" t="n"/>
+      <c r="Q150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -5553,6 +5721,7 @@
       <c r="N151" s="2" t="n"/>
       <c r="O151" s="2" t="n"/>
       <c r="P151" s="2" t="n"/>
+      <c r="Q151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -5585,6 +5754,7 @@
       <c r="N152" s="2" t="n"/>
       <c r="O152" s="2" t="n"/>
       <c r="P152" s="2" t="n"/>
+      <c r="Q152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -5617,6 +5787,7 @@
       <c r="N153" s="2" t="n"/>
       <c r="O153" s="2" t="n"/>
       <c r="P153" s="2" t="n"/>
+      <c r="Q153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -5649,6 +5820,7 @@
       <c r="N154" s="2" t="n"/>
       <c r="O154" s="2" t="n"/>
       <c r="P154" s="2" t="n"/>
+      <c r="Q154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -5681,6 +5853,7 @@
       <c r="N155" s="2" t="n"/>
       <c r="O155" s="2" t="n"/>
       <c r="P155" s="2" t="n"/>
+      <c r="Q155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -5713,6 +5886,7 @@
       <c r="N156" s="2" t="n"/>
       <c r="O156" s="2" t="n"/>
       <c r="P156" s="2" t="n"/>
+      <c r="Q156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -5745,6 +5919,7 @@
       <c r="N157" s="2" t="n"/>
       <c r="O157" s="2" t="n"/>
       <c r="P157" s="2" t="n"/>
+      <c r="Q157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -5777,6 +5952,7 @@
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="2" t="n"/>
       <c r="P158" s="2" t="n"/>
+      <c r="Q158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -5809,6 +5985,7 @@
       <c r="N159" s="2" t="n"/>
       <c r="O159" s="2" t="n"/>
       <c r="P159" s="2" t="n"/>
+      <c r="Q159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -5841,6 +6018,7 @@
       <c r="N160" s="2" t="n"/>
       <c r="O160" s="2" t="n"/>
       <c r="P160" s="2" t="n"/>
+      <c r="Q160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -5873,6 +6051,7 @@
       <c r="N161" s="2" t="n"/>
       <c r="O161" s="2" t="n"/>
       <c r="P161" s="2" t="n"/>
+      <c r="Q161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -5905,6 +6084,7 @@
       <c r="N162" s="2" t="n"/>
       <c r="O162" s="2" t="n"/>
       <c r="P162" s="2" t="n"/>
+      <c r="Q162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -5937,6 +6117,7 @@
       <c r="N163" s="2" t="n"/>
       <c r="O163" s="2" t="n"/>
       <c r="P163" s="2" t="n"/>
+      <c r="Q163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -5969,6 +6150,7 @@
       <c r="N164" s="2" t="n"/>
       <c r="O164" s="2" t="n"/>
       <c r="P164" s="2" t="n"/>
+      <c r="Q164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -6001,6 +6183,7 @@
       <c r="N165" s="2" t="n"/>
       <c r="O165" s="2" t="n"/>
       <c r="P165" s="2" t="n"/>
+      <c r="Q165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -6033,6 +6216,7 @@
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="2" t="n"/>
       <c r="P166" s="2" t="n"/>
+      <c r="Q166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -6065,6 +6249,7 @@
       <c r="N167" s="2" t="n"/>
       <c r="O167" s="2" t="n"/>
       <c r="P167" s="2" t="n"/>
+      <c r="Q167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -6097,6 +6282,7 @@
       <c r="N168" s="2" t="n"/>
       <c r="O168" s="2" t="n"/>
       <c r="P168" s="2" t="n"/>
+      <c r="Q168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -6129,6 +6315,7 @@
       <c r="N169" s="2" t="n"/>
       <c r="O169" s="2" t="n"/>
       <c r="P169" s="2" t="n"/>
+      <c r="Q169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -6161,6 +6348,7 @@
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="2" t="n"/>
       <c r="P170" s="2" t="n"/>
+      <c r="Q170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -6193,6 +6381,7 @@
       <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="n"/>
       <c r="P171" s="2" t="n"/>
+      <c r="Q171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -6225,6 +6414,7 @@
       <c r="N172" s="2" t="n"/>
       <c r="O172" s="2" t="n"/>
       <c r="P172" s="2" t="n"/>
+      <c r="Q172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -6257,6 +6447,7 @@
       <c r="N173" s="2" t="n"/>
       <c r="O173" s="2" t="n"/>
       <c r="P173" s="2" t="n"/>
+      <c r="Q173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -6289,6 +6480,7 @@
       <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="n"/>
       <c r="P174" s="2" t="n"/>
+      <c r="Q174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -6321,6 +6513,7 @@
       <c r="N175" s="2" t="n"/>
       <c r="O175" s="2" t="n"/>
       <c r="P175" s="2" t="n"/>
+      <c r="Q175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -6353,6 +6546,7 @@
       <c r="N176" s="2" t="n"/>
       <c r="O176" s="2" t="n"/>
       <c r="P176" s="2" t="n"/>
+      <c r="Q176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -6385,6 +6579,7 @@
       <c r="N177" s="2" t="n"/>
       <c r="O177" s="2" t="n"/>
       <c r="P177" s="2" t="n"/>
+      <c r="Q177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -6417,6 +6612,7 @@
       <c r="N178" s="2" t="n"/>
       <c r="O178" s="2" t="n"/>
       <c r="P178" s="2" t="n"/>
+      <c r="Q178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -6449,6 +6645,7 @@
       <c r="N179" s="2" t="n"/>
       <c r="O179" s="2" t="n"/>
       <c r="P179" s="2" t="n"/>
+      <c r="Q179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -6481,6 +6678,7 @@
       <c r="N180" s="2" t="n"/>
       <c r="O180" s="2" t="n"/>
       <c r="P180" s="2" t="n"/>
+      <c r="Q180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -6513,6 +6711,7 @@
       <c r="N181" s="2" t="n"/>
       <c r="O181" s="2" t="n"/>
       <c r="P181" s="2" t="n"/>
+      <c r="Q181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -6545,6 +6744,7 @@
       <c r="N182" s="2" t="n"/>
       <c r="O182" s="2" t="n"/>
       <c r="P182" s="2" t="n"/>
+      <c r="Q182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -6577,6 +6777,7 @@
       <c r="N183" s="2" t="n"/>
       <c r="O183" s="2" t="n"/>
       <c r="P183" s="2" t="n"/>
+      <c r="Q183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -6609,6 +6810,7 @@
       <c r="N184" s="2" t="n"/>
       <c r="O184" s="2" t="n"/>
       <c r="P184" s="2" t="n"/>
+      <c r="Q184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -6641,6 +6843,7 @@
       <c r="N185" s="2" t="n"/>
       <c r="O185" s="2" t="n"/>
       <c r="P185" s="2" t="n"/>
+      <c r="Q185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -6673,6 +6876,7 @@
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="2" t="n"/>
       <c r="P186" s="2" t="n"/>
+      <c r="Q186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -6705,6 +6909,7 @@
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="2" t="n"/>
       <c r="P187" s="2" t="n"/>
+      <c r="Q187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -6737,6 +6942,7 @@
       <c r="N188" s="2" t="n"/>
       <c r="O188" s="2" t="n"/>
       <c r="P188" s="2" t="n"/>
+      <c r="Q188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -6769,6 +6975,7 @@
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="2" t="n"/>
       <c r="P189" s="2" t="n"/>
+      <c r="Q189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -6801,6 +7008,7 @@
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="2" t="n"/>
       <c r="P190" s="2" t="n"/>
+      <c r="Q190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -6833,6 +7041,7 @@
       <c r="N191" s="2" t="n"/>
       <c r="O191" s="2" t="n"/>
       <c r="P191" s="2" t="n"/>
+      <c r="Q191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -6865,6 +7074,7 @@
       <c r="N192" s="2" t="n"/>
       <c r="O192" s="2" t="n"/>
       <c r="P192" s="2" t="n"/>
+      <c r="Q192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -6897,6 +7107,7 @@
       <c r="N193" s="2" t="n"/>
       <c r="O193" s="2" t="n"/>
       <c r="P193" s="2" t="n"/>
+      <c r="Q193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -6929,6 +7140,7 @@
       <c r="N194" s="2" t="n"/>
       <c r="O194" s="2" t="n"/>
       <c r="P194" s="2" t="n"/>
+      <c r="Q194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -6961,6 +7173,7 @@
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="2" t="n"/>
       <c r="P195" s="2" t="n"/>
+      <c r="Q195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -6993,6 +7206,7 @@
       <c r="N196" s="2" t="n"/>
       <c r="O196" s="2" t="n"/>
       <c r="P196" s="2" t="n"/>
+      <c r="Q196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -7025,6 +7239,7 @@
       <c r="N197" s="2" t="n"/>
       <c r="O197" s="2" t="n"/>
       <c r="P197" s="2" t="n"/>
+      <c r="Q197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -7057,6 +7272,7 @@
       <c r="N198" s="2" t="n"/>
       <c r="O198" s="2" t="n"/>
       <c r="P198" s="2" t="n"/>
+      <c r="Q198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -7089,6 +7305,7 @@
       <c r="N199" s="2" t="n"/>
       <c r="O199" s="2" t="n"/>
       <c r="P199" s="2" t="n"/>
+      <c r="Q199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -7121,6 +7338,7 @@
       <c r="N200" s="2" t="n"/>
       <c r="O200" s="2" t="n"/>
       <c r="P200" s="2" t="n"/>
+      <c r="Q200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -7153,6 +7371,7 @@
       <c r="N201" s="2" t="n"/>
       <c r="O201" s="2" t="n"/>
       <c r="P201" s="2" t="n"/>
+      <c r="Q201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -7185,6 +7404,7 @@
       <c r="N202" s="2" t="n"/>
       <c r="O202" s="2" t="n"/>
       <c r="P202" s="2" t="n"/>
+      <c r="Q202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -7217,6 +7437,7 @@
       <c r="N203" s="2" t="n"/>
       <c r="O203" s="2" t="n"/>
       <c r="P203" s="2" t="n"/>
+      <c r="Q203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -7249,6 +7470,7 @@
       <c r="N204" s="2" t="n"/>
       <c r="O204" s="2" t="n"/>
       <c r="P204" s="2" t="n"/>
+      <c r="Q204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -7281,6 +7503,7 @@
       <c r="N205" s="2" t="n"/>
       <c r="O205" s="2" t="n"/>
       <c r="P205" s="2" t="n"/>
+      <c r="Q205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -7313,6 +7536,7 @@
       <c r="N206" s="2" t="n"/>
       <c r="O206" s="2" t="n"/>
       <c r="P206" s="2" t="n"/>
+      <c r="Q206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -7345,6 +7569,7 @@
       <c r="N207" s="2" t="n"/>
       <c r="O207" s="2" t="n"/>
       <c r="P207" s="2" t="n"/>
+      <c r="Q207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -7377,6 +7602,7 @@
       <c r="N208" s="2" t="n"/>
       <c r="O208" s="2" t="n"/>
       <c r="P208" s="2" t="n"/>
+      <c r="Q208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -7409,6 +7635,7 @@
       <c r="N209" s="2" t="n"/>
       <c r="O209" s="2" t="n"/>
       <c r="P209" s="2" t="n"/>
+      <c r="Q209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -7441,6 +7668,7 @@
       <c r="N210" s="2" t="n"/>
       <c r="O210" s="2" t="n"/>
       <c r="P210" s="2" t="n"/>
+      <c r="Q210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -7473,6 +7701,7 @@
       <c r="N211" s="2" t="n"/>
       <c r="O211" s="2" t="n"/>
       <c r="P211" s="2" t="n"/>
+      <c r="Q211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -7505,6 +7734,7 @@
       <c r="N212" s="2" t="n"/>
       <c r="O212" s="2" t="n"/>
       <c r="P212" s="2" t="n"/>
+      <c r="Q212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -7537,6 +7767,7 @@
       <c r="N213" s="2" t="n"/>
       <c r="O213" s="2" t="n"/>
       <c r="P213" s="2" t="n"/>
+      <c r="Q213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -7569,6 +7800,7 @@
       <c r="N214" s="2" t="n"/>
       <c r="O214" s="2" t="n"/>
       <c r="P214" s="2" t="n"/>
+      <c r="Q214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -7601,6 +7833,7 @@
       <c r="N215" s="2" t="n"/>
       <c r="O215" s="2" t="n"/>
       <c r="P215" s="2" t="n"/>
+      <c r="Q215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -7633,6 +7866,7 @@
       <c r="N216" s="2" t="n"/>
       <c r="O216" s="2" t="n"/>
       <c r="P216" s="2" t="n"/>
+      <c r="Q216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -7665,6 +7899,7 @@
       <c r="N217" s="2" t="n"/>
       <c r="O217" s="2" t="n"/>
       <c r="P217" s="2" t="n"/>
+      <c r="Q217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -7697,6 +7932,7 @@
       <c r="N218" s="2" t="n"/>
       <c r="O218" s="2" t="n"/>
       <c r="P218" s="2" t="n"/>
+      <c r="Q218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -7729,6 +7965,7 @@
       <c r="N219" s="2" t="n"/>
       <c r="O219" s="2" t="n"/>
       <c r="P219" s="2" t="n"/>
+      <c r="Q219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -7761,6 +7998,7 @@
       <c r="N220" s="2" t="n"/>
       <c r="O220" s="2" t="n"/>
       <c r="P220" s="2" t="n"/>
+      <c r="Q220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -7793,6 +8031,7 @@
       <c r="N221" s="2" t="n"/>
       <c r="O221" s="2" t="n"/>
       <c r="P221" s="2" t="n"/>
+      <c r="Q221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -7825,6 +8064,7 @@
       <c r="N222" s="2" t="n"/>
       <c r="O222" s="2" t="n"/>
       <c r="P222" s="2" t="n"/>
+      <c r="Q222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -7857,6 +8097,7 @@
       <c r="N223" s="2" t="n"/>
       <c r="O223" s="2" t="n"/>
       <c r="P223" s="2" t="n"/>
+      <c r="Q223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -7889,6 +8130,7 @@
       <c r="N224" s="2" t="n"/>
       <c r="O224" s="2" t="n"/>
       <c r="P224" s="2" t="n"/>
+      <c r="Q224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -7921,6 +8163,7 @@
       <c r="N225" s="2" t="n"/>
       <c r="O225" s="2" t="n"/>
       <c r="P225" s="2" t="n"/>
+      <c r="Q225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -7953,6 +8196,7 @@
       <c r="N226" s="2" t="n"/>
       <c r="O226" s="2" t="n"/>
       <c r="P226" s="2" t="n"/>
+      <c r="Q226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -7985,6 +8229,7 @@
       <c r="N227" s="2" t="n"/>
       <c r="O227" s="2" t="n"/>
       <c r="P227" s="2" t="n"/>
+      <c r="Q227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -8017,6 +8262,7 @@
       <c r="N228" s="2" t="n"/>
       <c r="O228" s="2" t="n"/>
       <c r="P228" s="2" t="n"/>
+      <c r="Q228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -8049,6 +8295,7 @@
       <c r="N229" s="2" t="n"/>
       <c r="O229" s="2" t="n"/>
       <c r="P229" s="2" t="n"/>
+      <c r="Q229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -8081,6 +8328,7 @@
       <c r="N230" s="2" t="n"/>
       <c r="O230" s="2" t="n"/>
       <c r="P230" s="2" t="n"/>
+      <c r="Q230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -8113,6 +8361,7 @@
       <c r="N231" s="2" t="n"/>
       <c r="O231" s="2" t="n"/>
       <c r="P231" s="2" t="n"/>
+      <c r="Q231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -8145,6 +8394,7 @@
       <c r="N232" s="2" t="n"/>
       <c r="O232" s="2" t="n"/>
       <c r="P232" s="2" t="n"/>
+      <c r="Q232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -8177,6 +8427,7 @@
       <c r="N233" s="2" t="n"/>
       <c r="O233" s="2" t="n"/>
       <c r="P233" s="2" t="n"/>
+      <c r="Q233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -8209,6 +8460,7 @@
       <c r="N234" s="2" t="n"/>
       <c r="O234" s="2" t="n"/>
       <c r="P234" s="2" t="n"/>
+      <c r="Q234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -8241,6 +8493,7 @@
       <c r="N235" s="2" t="n"/>
       <c r="O235" s="2" t="n"/>
       <c r="P235" s="2" t="n"/>
+      <c r="Q235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -8273,6 +8526,7 @@
       <c r="N236" s="2" t="n"/>
       <c r="O236" s="2" t="n"/>
       <c r="P236" s="2" t="n"/>
+      <c r="Q236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -8305,6 +8559,7 @@
       <c r="N237" s="2" t="n"/>
       <c r="O237" s="2" t="n"/>
       <c r="P237" s="2" t="n"/>
+      <c r="Q237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -8337,6 +8592,7 @@
       <c r="N238" s="2" t="n"/>
       <c r="O238" s="2" t="n"/>
       <c r="P238" s="2" t="n"/>
+      <c r="Q238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -8369,6 +8625,7 @@
       <c r="N239" s="2" t="n"/>
       <c r="O239" s="2" t="n"/>
       <c r="P239" s="2" t="n"/>
+      <c r="Q239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -8401,6 +8658,7 @@
       <c r="N240" s="2" t="n"/>
       <c r="O240" s="2" t="n"/>
       <c r="P240" s="2" t="n"/>
+      <c r="Q240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -8433,6 +8691,7 @@
       <c r="N241" s="2" t="n"/>
       <c r="O241" s="2" t="n"/>
       <c r="P241" s="2" t="n"/>
+      <c r="Q241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -8465,6 +8724,7 @@
       <c r="N242" s="2" t="n"/>
       <c r="O242" s="2" t="n"/>
       <c r="P242" s="2" t="n"/>
+      <c r="Q242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -8497,6 +8757,7 @@
       <c r="N243" s="2" t="n"/>
       <c r="O243" s="2" t="n"/>
       <c r="P243" s="2" t="n"/>
+      <c r="Q243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -8529,6 +8790,7 @@
       <c r="N244" s="2" t="n"/>
       <c r="O244" s="2" t="n"/>
       <c r="P244" s="2" t="n"/>
+      <c r="Q244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -8561,6 +8823,7 @@
       <c r="N245" s="2" t="n"/>
       <c r="O245" s="2" t="n"/>
       <c r="P245" s="2" t="n"/>
+      <c r="Q245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -8593,6 +8856,7 @@
       <c r="N246" s="2" t="n"/>
       <c r="O246" s="2" t="n"/>
       <c r="P246" s="2" t="n"/>
+      <c r="Q246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -8625,6 +8889,7 @@
       <c r="N247" s="2" t="n"/>
       <c r="O247" s="2" t="n"/>
       <c r="P247" s="2" t="n"/>
+      <c r="Q247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -8657,6 +8922,7 @@
       <c r="N248" s="2" t="n"/>
       <c r="O248" s="2" t="n"/>
       <c r="P248" s="2" t="n"/>
+      <c r="Q248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -8689,6 +8955,7 @@
       <c r="N249" s="2" t="n"/>
       <c r="O249" s="2" t="n"/>
       <c r="P249" s="2" t="n"/>
+      <c r="Q249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -8721,6 +8988,7 @@
       <c r="N250" s="2" t="n"/>
       <c r="O250" s="2" t="n"/>
       <c r="P250" s="2" t="n"/>
+      <c r="Q250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -8753,6 +9021,7 @@
       <c r="N251" s="2" t="n"/>
       <c r="O251" s="2" t="n"/>
       <c r="P251" s="2" t="n"/>
+      <c r="Q251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -8785,6 +9054,7 @@
       <c r="N252" s="2" t="n"/>
       <c r="O252" s="2" t="n"/>
       <c r="P252" s="2" t="n"/>
+      <c r="Q252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -8817,6 +9087,7 @@
       <c r="N253" s="2" t="n"/>
       <c r="O253" s="2" t="n"/>
       <c r="P253" s="2" t="n"/>
+      <c r="Q253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -8849,6 +9120,7 @@
       <c r="N254" s="2" t="n"/>
       <c r="O254" s="2" t="n"/>
       <c r="P254" s="2" t="n"/>
+      <c r="Q254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -8881,6 +9153,7 @@
       <c r="N255" s="2" t="n"/>
       <c r="O255" s="2" t="n"/>
       <c r="P255" s="2" t="n"/>
+      <c r="Q255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -8913,6 +9186,7 @@
       <c r="N256" s="2" t="n"/>
       <c r="O256" s="2" t="n"/>
       <c r="P256" s="2" t="n"/>
+      <c r="Q256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -8945,6 +9219,7 @@
       <c r="N257" s="2" t="n"/>
       <c r="O257" s="2" t="n"/>
       <c r="P257" s="2" t="n"/>
+      <c r="Q257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -8977,6 +9252,7 @@
       <c r="N258" s="2" t="n"/>
       <c r="O258" s="2" t="n"/>
       <c r="P258" s="2" t="n"/>
+      <c r="Q258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -9009,6 +9285,7 @@
       <c r="N259" s="2" t="n"/>
       <c r="O259" s="2" t="n"/>
       <c r="P259" s="2" t="n"/>
+      <c r="Q259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -9041,6 +9318,7 @@
       <c r="N260" s="2" t="n"/>
       <c r="O260" s="2" t="n"/>
       <c r="P260" s="2" t="n"/>
+      <c r="Q260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -9073,6 +9351,7 @@
       <c r="N261" s="2" t="n"/>
       <c r="O261" s="2" t="n"/>
       <c r="P261" s="2" t="n"/>
+      <c r="Q261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -9105,6 +9384,7 @@
       <c r="N262" s="2" t="n"/>
       <c r="O262" s="2" t="n"/>
       <c r="P262" s="2" t="n"/>
+      <c r="Q262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -9137,6 +9417,7 @@
       <c r="N263" s="2" t="n"/>
       <c r="O263" s="2" t="n"/>
       <c r="P263" s="2" t="n"/>
+      <c r="Q263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -9169,6 +9450,7 @@
       <c r="N264" s="2" t="n"/>
       <c r="O264" s="2" t="n"/>
       <c r="P264" s="2" t="n"/>
+      <c r="Q264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -9201,6 +9483,7 @@
       <c r="N265" s="2" t="n"/>
       <c r="O265" s="2" t="n"/>
       <c r="P265" s="2" t="n"/>
+      <c r="Q265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -9233,6 +9516,7 @@
       <c r="N266" s="2" t="n"/>
       <c r="O266" s="2" t="n"/>
       <c r="P266" s="2" t="n"/>
+      <c r="Q266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -9265,6 +9549,7 @@
       <c r="N267" s="2" t="n"/>
       <c r="O267" s="2" t="n"/>
       <c r="P267" s="2" t="n"/>
+      <c r="Q267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -9297,6 +9582,7 @@
       <c r="N268" s="2" t="n"/>
       <c r="O268" s="2" t="n"/>
       <c r="P268" s="2" t="n"/>
+      <c r="Q268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -9329,6 +9615,7 @@
       <c r="N269" s="2" t="n"/>
       <c r="O269" s="2" t="n"/>
       <c r="P269" s="2" t="n"/>
+      <c r="Q269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -9361,6 +9648,7 @@
       <c r="N270" s="2" t="n"/>
       <c r="O270" s="2" t="n"/>
       <c r="P270" s="2" t="n"/>
+      <c r="Q270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -9393,6 +9681,7 @@
       <c r="N271" s="2" t="n"/>
       <c r="O271" s="2" t="n"/>
       <c r="P271" s="2" t="n"/>
+      <c r="Q271" s="2" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -9425,6 +9714,7 @@
       <c r="N272" s="2" t="n"/>
       <c r="O272" s="2" t="n"/>
       <c r="P272" s="2" t="n"/>
+      <c r="Q272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -9457,6 +9747,7 @@
       <c r="N273" s="2" t="n"/>
       <c r="O273" s="2" t="n"/>
       <c r="P273" s="2" t="n"/>
+      <c r="Q273" s="2" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -9489,6 +9780,7 @@
       <c r="N274" s="2" t="n"/>
       <c r="O274" s="2" t="n"/>
       <c r="P274" s="2" t="n"/>
+      <c r="Q274" s="2" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -9521,6 +9813,7 @@
       <c r="N275" s="2" t="n"/>
       <c r="O275" s="2" t="n"/>
       <c r="P275" s="2" t="n"/>
+      <c r="Q275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -9553,6 +9846,7 @@
       <c r="N276" s="2" t="n"/>
       <c r="O276" s="2" t="n"/>
       <c r="P276" s="2" t="n"/>
+      <c r="Q276" s="2" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -9585,6 +9879,7 @@
       <c r="N277" s="2" t="n"/>
       <c r="O277" s="2" t="n"/>
       <c r="P277" s="2" t="n"/>
+      <c r="Q277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -9617,6 +9912,7 @@
       <c r="N278" s="2" t="n"/>
       <c r="O278" s="2" t="n"/>
       <c r="P278" s="2" t="n"/>
+      <c r="Q278" s="2" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -9649,6 +9945,7 @@
       <c r="N279" s="2" t="n"/>
       <c r="O279" s="2" t="n"/>
       <c r="P279" s="2" t="n"/>
+      <c r="Q279" s="2" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -9681,6 +9978,7 @@
       <c r="N280" s="2" t="n"/>
       <c r="O280" s="2" t="n"/>
       <c r="P280" s="2" t="n"/>
+      <c r="Q280" s="2" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -9713,6 +10011,7 @@
       <c r="N281" s="2" t="n"/>
       <c r="O281" s="2" t="n"/>
       <c r="P281" s="2" t="n"/>
+      <c r="Q281" s="2" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -9745,6 +10044,7 @@
       <c r="N282" s="2" t="n"/>
       <c r="O282" s="2" t="n"/>
       <c r="P282" s="2" t="n"/>
+      <c r="Q282" s="2" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -9777,6 +10077,7 @@
       <c r="N283" s="2" t="n"/>
       <c r="O283" s="2" t="n"/>
       <c r="P283" s="2" t="n"/>
+      <c r="Q283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -9809,6 +10110,7 @@
       <c r="N284" s="2" t="n"/>
       <c r="O284" s="2" t="n"/>
       <c r="P284" s="2" t="n"/>
+      <c r="Q284" s="2" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -9841,6 +10143,7 @@
       <c r="N285" s="2" t="n"/>
       <c r="O285" s="2" t="n"/>
       <c r="P285" s="2" t="n"/>
+      <c r="Q285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -9873,6 +10176,7 @@
       <c r="N286" s="2" t="n"/>
       <c r="O286" s="2" t="n"/>
       <c r="P286" s="2" t="n"/>
+      <c r="Q286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -9905,6 +10209,7 @@
       <c r="N287" s="2" t="n"/>
       <c r="O287" s="2" t="n"/>
       <c r="P287" s="2" t="n"/>
+      <c r="Q287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -9937,6 +10242,7 @@
       <c r="N288" s="2" t="n"/>
       <c r="O288" s="2" t="n"/>
       <c r="P288" s="2" t="n"/>
+      <c r="Q288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -9969,6 +10275,7 @@
       <c r="N289" s="2" t="n"/>
       <c r="O289" s="2" t="n"/>
       <c r="P289" s="2" t="n"/>
+      <c r="Q289" s="2" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -10001,6 +10308,7 @@
       <c r="N290" s="2" t="n"/>
       <c r="O290" s="2" t="n"/>
       <c r="P290" s="2" t="n"/>
+      <c r="Q290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -10033,6 +10341,7 @@
       <c r="N291" s="2" t="n"/>
       <c r="O291" s="2" t="n"/>
       <c r="P291" s="2" t="n"/>
+      <c r="Q291" s="2" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -10065,6 +10374,7 @@
       <c r="N292" s="2" t="n"/>
       <c r="O292" s="2" t="n"/>
       <c r="P292" s="2" t="n"/>
+      <c r="Q292" s="2" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -10097,6 +10407,7 @@
       <c r="N293" s="2" t="n"/>
       <c r="O293" s="2" t="n"/>
       <c r="P293" s="2" t="n"/>
+      <c r="Q293" s="2" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -10129,6 +10440,7 @@
       <c r="N294" s="2" t="n"/>
       <c r="O294" s="2" t="n"/>
       <c r="P294" s="2" t="n"/>
+      <c r="Q294" s="2" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -10161,6 +10473,7 @@
       <c r="N295" s="2" t="n"/>
       <c r="O295" s="2" t="n"/>
       <c r="P295" s="2" t="n"/>
+      <c r="Q295" s="2" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -10193,6 +10506,7 @@
       <c r="N296" s="2" t="n"/>
       <c r="O296" s="2" t="n"/>
       <c r="P296" s="2" t="n"/>
+      <c r="Q296" s="2" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -10225,6 +10539,7 @@
       <c r="N297" s="2" t="n"/>
       <c r="O297" s="2" t="n"/>
       <c r="P297" s="2" t="n"/>
+      <c r="Q297" s="2" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -10257,6 +10572,7 @@
       <c r="N298" s="2" t="n"/>
       <c r="O298" s="2" t="n"/>
       <c r="P298" s="2" t="n"/>
+      <c r="Q298" s="2" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -10289,6 +10605,7 @@
       <c r="N299" s="2" t="n"/>
       <c r="O299" s="2" t="n"/>
       <c r="P299" s="2" t="n"/>
+      <c r="Q299" s="2" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -10321,6 +10638,7 @@
       <c r="N300" s="2" t="n"/>
       <c r="O300" s="2" t="n"/>
       <c r="P300" s="2" t="n"/>
+      <c r="Q300" s="2" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -10353,6 +10671,7 @@
       <c r="N301" s="2" t="n"/>
       <c r="O301" s="2" t="n"/>
       <c r="P301" s="2" t="n"/>
+      <c r="Q301" s="2" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n"/>
@@ -10385,6 +10704,7 @@
       <c r="N302" s="2" t="n"/>
       <c r="O302" s="2" t="n"/>
       <c r="P302" s="2" t="n"/>
+      <c r="Q302" s="2" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n"/>
@@ -10417,6 +10737,7 @@
       <c r="N303" s="2" t="n"/>
       <c r="O303" s="2" t="n"/>
       <c r="P303" s="2" t="n"/>
+      <c r="Q303" s="2" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n"/>
@@ -10449,6 +10770,7 @@
       <c r="N304" s="2" t="n"/>
       <c r="O304" s="2" t="n"/>
       <c r="P304" s="2" t="n"/>
+      <c r="Q304" s="2" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="n"/>
@@ -10481,6 +10803,7 @@
       <c r="N305" s="2" t="n"/>
       <c r="O305" s="2" t="n"/>
       <c r="P305" s="2" t="n"/>
+      <c r="Q305" s="2" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="n"/>
@@ -10513,6 +10836,7 @@
       <c r="N306" s="2" t="n"/>
       <c r="O306" s="2" t="n"/>
       <c r="P306" s="2" t="n"/>
+      <c r="Q306" s="2" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n"/>
@@ -10545,6 +10869,7 @@
       <c r="N307" s="2" t="n"/>
       <c r="O307" s="2" t="n"/>
       <c r="P307" s="2" t="n"/>
+      <c r="Q307" s="2" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n"/>
@@ -10577,6 +10902,7 @@
       <c r="N308" s="2" t="n"/>
       <c r="O308" s="2" t="n"/>
       <c r="P308" s="2" t="n"/>
+      <c r="Q308" s="2" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="n"/>
@@ -10609,6 +10935,7 @@
       <c r="N309" s="2" t="n"/>
       <c r="O309" s="2" t="n"/>
       <c r="P309" s="2" t="n"/>
+      <c r="Q309" s="2" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n"/>
@@ -10641,6 +10968,7 @@
       <c r="N310" s="2" t="n"/>
       <c r="O310" s="2" t="n"/>
       <c r="P310" s="2" t="n"/>
+      <c r="Q310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="n"/>
@@ -10673,6 +11001,7 @@
       <c r="N311" s="2" t="n"/>
       <c r="O311" s="2" t="n"/>
       <c r="P311" s="2" t="n"/>
+      <c r="Q311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="n"/>
@@ -10705,6 +11034,7 @@
       <c r="N312" s="2" t="n"/>
       <c r="O312" s="2" t="n"/>
       <c r="P312" s="2" t="n"/>
+      <c r="Q312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="n"/>
@@ -10737,6 +11067,7 @@
       <c r="N313" s="2" t="n"/>
       <c r="O313" s="2" t="n"/>
       <c r="P313" s="2" t="n"/>
+      <c r="Q313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="n"/>
@@ -10769,6 +11100,7 @@
       <c r="N314" s="2" t="n"/>
       <c r="O314" s="2" t="n"/>
       <c r="P314" s="2" t="n"/>
+      <c r="Q314" s="2" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="n"/>
@@ -10801,6 +11133,7 @@
       <c r="N315" s="2" t="n"/>
       <c r="O315" s="2" t="n"/>
       <c r="P315" s="2" t="n"/>
+      <c r="Q315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="n"/>
@@ -10833,6 +11166,7 @@
       <c r="N316" s="2" t="n"/>
       <c r="O316" s="2" t="n"/>
       <c r="P316" s="2" t="n"/>
+      <c r="Q316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="n"/>
@@ -10865,6 +11199,7 @@
       <c r="N317" s="2" t="n"/>
       <c r="O317" s="2" t="n"/>
       <c r="P317" s="2" t="n"/>
+      <c r="Q317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="n"/>
@@ -10897,6 +11232,7 @@
       <c r="N318" s="2" t="n"/>
       <c r="O318" s="2" t="n"/>
       <c r="P318" s="2" t="n"/>
+      <c r="Q318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="n"/>
@@ -10929,6 +11265,7 @@
       <c r="N319" s="2" t="n"/>
       <c r="O319" s="2" t="n"/>
       <c r="P319" s="2" t="n"/>
+      <c r="Q319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="n"/>
@@ -10961,6 +11298,7 @@
       <c r="N320" s="2" t="n"/>
       <c r="O320" s="2" t="n"/>
       <c r="P320" s="2" t="n"/>
+      <c r="Q320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="n"/>
@@ -10993,6 +11331,7 @@
       <c r="N321" s="2" t="n"/>
       <c r="O321" s="2" t="n"/>
       <c r="P321" s="2" t="n"/>
+      <c r="Q321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="n"/>
@@ -11025,6 +11364,7 @@
       <c r="N322" s="2" t="n"/>
       <c r="O322" s="2" t="n"/>
       <c r="P322" s="2" t="n"/>
+      <c r="Q322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="n"/>
@@ -11057,6 +11397,7 @@
       <c r="N323" s="2" t="n"/>
       <c r="O323" s="2" t="n"/>
       <c r="P323" s="2" t="n"/>
+      <c r="Q323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="n"/>
@@ -11089,6 +11430,7 @@
       <c r="N324" s="2" t="n"/>
       <c r="O324" s="2" t="n"/>
       <c r="P324" s="2" t="n"/>
+      <c r="Q324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="n"/>
@@ -11121,6 +11463,7 @@
       <c r="N325" s="2" t="n"/>
       <c r="O325" s="2" t="n"/>
       <c r="P325" s="2" t="n"/>
+      <c r="Q325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="n"/>
@@ -11153,6 +11496,7 @@
       <c r="N326" s="2" t="n"/>
       <c r="O326" s="2" t="n"/>
       <c r="P326" s="2" t="n"/>
+      <c r="Q326" s="2" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="n"/>
@@ -11185,6 +11529,7 @@
       <c r="N327" s="2" t="n"/>
       <c r="O327" s="2" t="n"/>
       <c r="P327" s="2" t="n"/>
+      <c r="Q327" s="2" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="n"/>
@@ -11217,6 +11562,7 @@
       <c r="N328" s="2" t="n"/>
       <c r="O328" s="2" t="n"/>
       <c r="P328" s="2" t="n"/>
+      <c r="Q328" s="2" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="n"/>
@@ -11249,6 +11595,7 @@
       <c r="N329" s="2" t="n"/>
       <c r="O329" s="2" t="n"/>
       <c r="P329" s="2" t="n"/>
+      <c r="Q329" s="2" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="n"/>
@@ -11281,6 +11628,7 @@
       <c r="N330" s="2" t="n"/>
       <c r="O330" s="2" t="n"/>
       <c r="P330" s="2" t="n"/>
+      <c r="Q330" s="2" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="n"/>
@@ -11313,6 +11661,7 @@
       <c r="N331" s="2" t="n"/>
       <c r="O331" s="2" t="n"/>
       <c r="P331" s="2" t="n"/>
+      <c r="Q331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="n"/>
@@ -11345,6 +11694,7 @@
       <c r="N332" s="2" t="n"/>
       <c r="O332" s="2" t="n"/>
       <c r="P332" s="2" t="n"/>
+      <c r="Q332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="n"/>
@@ -11377,6 +11727,7 @@
       <c r="N333" s="2" t="n"/>
       <c r="O333" s="2" t="n"/>
       <c r="P333" s="2" t="n"/>
+      <c r="Q333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="n"/>
@@ -11409,6 +11760,7 @@
       <c r="N334" s="2" t="n"/>
       <c r="O334" s="2" t="n"/>
       <c r="P334" s="2" t="n"/>
+      <c r="Q334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n"/>
@@ -11441,6 +11793,7 @@
       <c r="N335" s="2" t="n"/>
       <c r="O335" s="2" t="n"/>
       <c r="P335" s="2" t="n"/>
+      <c r="Q335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n"/>
@@ -11473,6 +11826,7 @@
       <c r="N336" s="2" t="n"/>
       <c r="O336" s="2" t="n"/>
       <c r="P336" s="2" t="n"/>
+      <c r="Q336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n"/>
@@ -11505,6 +11859,7 @@
       <c r="N337" s="2" t="n"/>
       <c r="O337" s="2" t="n"/>
       <c r="P337" s="2" t="n"/>
+      <c r="Q337" s="2" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n"/>
@@ -11537,6 +11892,7 @@
       <c r="N338" s="2" t="n"/>
       <c r="O338" s="2" t="n"/>
       <c r="P338" s="2" t="n"/>
+      <c r="Q338" s="2" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n"/>
@@ -11569,6 +11925,7 @@
       <c r="N339" s="2" t="n"/>
       <c r="O339" s="2" t="n"/>
       <c r="P339" s="2" t="n"/>
+      <c r="Q339" s="2" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n"/>
@@ -11601,6 +11958,7 @@
       <c r="N340" s="2" t="n"/>
       <c r="O340" s="2" t="n"/>
       <c r="P340" s="2" t="n"/>
+      <c r="Q340" s="2" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n"/>
@@ -11633,6 +11991,7 @@
       <c r="N341" s="2" t="n"/>
       <c r="O341" s="2" t="n"/>
       <c r="P341" s="2" t="n"/>
+      <c r="Q341" s="2" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n"/>
@@ -11665,6 +12024,7 @@
       <c r="N342" s="2" t="n"/>
       <c r="O342" s="2" t="n"/>
       <c r="P342" s="2" t="n"/>
+      <c r="Q342" s="2" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n"/>
@@ -11697,6 +12057,7 @@
       <c r="N343" s="2" t="n"/>
       <c r="O343" s="2" t="n"/>
       <c r="P343" s="2" t="n"/>
+      <c r="Q343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n"/>
@@ -11729,6 +12090,7 @@
       <c r="N344" s="2" t="n"/>
       <c r="O344" s="2" t="n"/>
       <c r="P344" s="2" t="n"/>
+      <c r="Q344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n"/>
@@ -11761,6 +12123,7 @@
       <c r="N345" s="2" t="n"/>
       <c r="O345" s="2" t="n"/>
       <c r="P345" s="2" t="n"/>
+      <c r="Q345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n"/>
@@ -11793,6 +12156,7 @@
       <c r="N346" s="2" t="n"/>
       <c r="O346" s="2" t="n"/>
       <c r="P346" s="2" t="n"/>
+      <c r="Q346" s="2" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n"/>
@@ -11825,6 +12189,7 @@
       <c r="N347" s="2" t="n"/>
       <c r="O347" s="2" t="n"/>
       <c r="P347" s="2" t="n"/>
+      <c r="Q347" s="2" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n"/>
@@ -11857,6 +12222,7 @@
       <c r="N348" s="2" t="n"/>
       <c r="O348" s="2" t="n"/>
       <c r="P348" s="2" t="n"/>
+      <c r="Q348" s="2" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n"/>
@@ -11889,6 +12255,7 @@
       <c r="N349" s="2" t="n"/>
       <c r="O349" s="2" t="n"/>
       <c r="P349" s="2" t="n"/>
+      <c r="Q349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n"/>
@@ -11921,6 +12288,7 @@
       <c r="N350" s="2" t="n"/>
       <c r="O350" s="2" t="n"/>
       <c r="P350" s="2" t="n"/>
+      <c r="Q350" s="2" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n"/>
@@ -11953,6 +12321,7 @@
       <c r="N351" s="2" t="n"/>
       <c r="O351" s="2" t="n"/>
       <c r="P351" s="2" t="n"/>
+      <c r="Q351" s="2" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n"/>
@@ -11985,6 +12354,7 @@
       <c r="N352" s="2" t="n"/>
       <c r="O352" s="2" t="n"/>
       <c r="P352" s="2" t="n"/>
+      <c r="Q352" s="2" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n"/>
@@ -12017,6 +12387,7 @@
       <c r="N353" s="2" t="n"/>
       <c r="O353" s="2" t="n"/>
       <c r="P353" s="2" t="n"/>
+      <c r="Q353" s="2" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n"/>
@@ -12049,6 +12420,7 @@
       <c r="N354" s="2" t="n"/>
       <c r="O354" s="2" t="n"/>
       <c r="P354" s="2" t="n"/>
+      <c r="Q354" s="2" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n"/>
@@ -12081,6 +12453,7 @@
       <c r="N355" s="2" t="n"/>
       <c r="O355" s="2" t="n"/>
       <c r="P355" s="2" t="n"/>
+      <c r="Q355" s="2" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n"/>
@@ -12113,6 +12486,7 @@
       <c r="N356" s="2" t="n"/>
       <c r="O356" s="2" t="n"/>
       <c r="P356" s="2" t="n"/>
+      <c r="Q356" s="2" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n"/>
@@ -12145,6 +12519,7 @@
       <c r="N357" s="2" t="n"/>
       <c r="O357" s="2" t="n"/>
       <c r="P357" s="2" t="n"/>
+      <c r="Q357" s="2" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n"/>
@@ -12177,6 +12552,7 @@
       <c r="N358" s="2" t="n"/>
       <c r="O358" s="2" t="n"/>
       <c r="P358" s="2" t="n"/>
+      <c r="Q358" s="2" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n"/>
@@ -12209,6 +12585,7 @@
       <c r="N359" s="2" t="n"/>
       <c r="O359" s="2" t="n"/>
       <c r="P359" s="2" t="n"/>
+      <c r="Q359" s="2" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n"/>
@@ -12241,6 +12618,7 @@
       <c r="N360" s="2" t="n"/>
       <c r="O360" s="2" t="n"/>
       <c r="P360" s="2" t="n"/>
+      <c r="Q360" s="2" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n"/>
@@ -12273,6 +12651,7 @@
       <c r="N361" s="2" t="n"/>
       <c r="O361" s="2" t="n"/>
       <c r="P361" s="2" t="n"/>
+      <c r="Q361" s="2" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n"/>
@@ -12305,6 +12684,7 @@
       <c r="N362" s="2" t="n"/>
       <c r="O362" s="2" t="n"/>
       <c r="P362" s="2" t="n"/>
+      <c r="Q362" s="2" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n"/>
@@ -12337,6 +12717,7 @@
       <c r="N363" s="2" t="n"/>
       <c r="O363" s="2" t="n"/>
       <c r="P363" s="2" t="n"/>
+      <c r="Q363" s="2" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n"/>
@@ -12369,6 +12750,7 @@
       <c r="N364" s="2" t="n"/>
       <c r="O364" s="2" t="n"/>
       <c r="P364" s="2" t="n"/>
+      <c r="Q364" s="2" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n"/>
@@ -12401,6 +12783,7 @@
       <c r="N365" s="2" t="n"/>
       <c r="O365" s="2" t="n"/>
       <c r="P365" s="2" t="n"/>
+      <c r="Q365" s="2" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n"/>
@@ -12433,6 +12816,7 @@
       <c r="N366" s="2" t="n"/>
       <c r="O366" s="2" t="n"/>
       <c r="P366" s="2" t="n"/>
+      <c r="Q366" s="2" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n"/>
@@ -12465,6 +12849,7 @@
       <c r="N367" s="2" t="n"/>
       <c r="O367" s="2" t="n"/>
       <c r="P367" s="2" t="n"/>
+      <c r="Q367" s="2" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n"/>
@@ -12497,6 +12882,7 @@
       <c r="N368" s="2" t="n"/>
       <c r="O368" s="2" t="n"/>
       <c r="P368" s="2" t="n"/>
+      <c r="Q368" s="2" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n"/>
@@ -12529,6 +12915,7 @@
       <c r="N369" s="2" t="n"/>
       <c r="O369" s="2" t="n"/>
       <c r="P369" s="2" t="n"/>
+      <c r="Q369" s="2" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n"/>
@@ -12561,6 +12948,7 @@
       <c r="N370" s="2" t="n"/>
       <c r="O370" s="2" t="n"/>
       <c r="P370" s="2" t="n"/>
+      <c r="Q370" s="2" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n"/>
@@ -12593,6 +12981,7 @@
       <c r="N371" s="2" t="n"/>
       <c r="O371" s="2" t="n"/>
       <c r="P371" s="2" t="n"/>
+      <c r="Q371" s="2" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n"/>
@@ -12625,6 +13014,7 @@
       <c r="N372" s="2" t="n"/>
       <c r="O372" s="2" t="n"/>
       <c r="P372" s="2" t="n"/>
+      <c r="Q372" s="2" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n"/>
@@ -12657,6 +13047,7 @@
       <c r="N373" s="2" t="n"/>
       <c r="O373" s="2" t="n"/>
       <c r="P373" s="2" t="n"/>
+      <c r="Q373" s="2" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n"/>
@@ -12689,6 +13080,7 @@
       <c r="N374" s="2" t="n"/>
       <c r="O374" s="2" t="n"/>
       <c r="P374" s="2" t="n"/>
+      <c r="Q374" s="2" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n"/>
@@ -12721,6 +13113,7 @@
       <c r="N375" s="2" t="n"/>
       <c r="O375" s="2" t="n"/>
       <c r="P375" s="2" t="n"/>
+      <c r="Q375" s="2" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n"/>
@@ -12753,6 +13146,7 @@
       <c r="N376" s="2" t="n"/>
       <c r="O376" s="2" t="n"/>
       <c r="P376" s="2" t="n"/>
+      <c r="Q376" s="2" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n"/>
@@ -12785,6 +13179,7 @@
       <c r="N377" s="2" t="n"/>
       <c r="O377" s="2" t="n"/>
       <c r="P377" s="2" t="n"/>
+      <c r="Q377" s="2" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n"/>
@@ -12817,6 +13212,7 @@
       <c r="N378" s="2" t="n"/>
       <c r="O378" s="2" t="n"/>
       <c r="P378" s="2" t="n"/>
+      <c r="Q378" s="2" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n"/>
@@ -12849,6 +13245,7 @@
       <c r="N379" s="2" t="n"/>
       <c r="O379" s="2" t="n"/>
       <c r="P379" s="2" t="n"/>
+      <c r="Q379" s="2" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n"/>
@@ -12881,6 +13278,7 @@
       <c r="N380" s="2" t="n"/>
       <c r="O380" s="2" t="n"/>
       <c r="P380" s="2" t="n"/>
+      <c r="Q380" s="2" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n"/>
@@ -12913,6 +13311,7 @@
       <c r="N381" s="2" t="n"/>
       <c r="O381" s="2" t="n"/>
       <c r="P381" s="2" t="n"/>
+      <c r="Q381" s="2" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n"/>
@@ -12945,6 +13344,7 @@
       <c r="N382" s="2" t="n"/>
       <c r="O382" s="2" t="n"/>
       <c r="P382" s="2" t="n"/>
+      <c r="Q382" s="2" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n"/>
@@ -12977,6 +13377,7 @@
       <c r="N383" s="2" t="n"/>
       <c r="O383" s="2" t="n"/>
       <c r="P383" s="2" t="n"/>
+      <c r="Q383" s="2" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n"/>
@@ -13009,6 +13410,7 @@
       <c r="N384" s="2" t="n"/>
       <c r="O384" s="2" t="n"/>
       <c r="P384" s="2" t="n"/>
+      <c r="Q384" s="2" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n"/>
@@ -13041,6 +13443,7 @@
       <c r="N385" s="2" t="n"/>
       <c r="O385" s="2" t="n"/>
       <c r="P385" s="2" t="n"/>
+      <c r="Q385" s="2" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n"/>
@@ -13073,6 +13476,7 @@
       <c r="N386" s="2" t="n"/>
       <c r="O386" s="2" t="n"/>
       <c r="P386" s="2" t="n"/>
+      <c r="Q386" s="2" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n"/>
@@ -13105,6 +13509,7 @@
       <c r="N387" s="2" t="n"/>
       <c r="O387" s="2" t="n"/>
       <c r="P387" s="2" t="n"/>
+      <c r="Q387" s="2" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n"/>
@@ -13137,6 +13542,7 @@
       <c r="N388" s="2" t="n"/>
       <c r="O388" s="2" t="n"/>
       <c r="P388" s="2" t="n"/>
+      <c r="Q388" s="2" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -13169,6 +13575,7 @@
       <c r="N389" s="2" t="n"/>
       <c r="O389" s="2" t="n"/>
       <c r="P389" s="2" t="n"/>
+      <c r="Q389" s="2" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -13201,6 +13608,7 @@
       <c r="N390" s="2" t="n"/>
       <c r="O390" s="2" t="n"/>
       <c r="P390" s="2" t="n"/>
+      <c r="Q390" s="2" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -13233,6 +13641,7 @@
       <c r="N391" s="2" t="n"/>
       <c r="O391" s="2" t="n"/>
       <c r="P391" s="2" t="n"/>
+      <c r="Q391" s="2" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -13265,6 +13674,7 @@
       <c r="N392" s="2" t="n"/>
       <c r="O392" s="2" t="n"/>
       <c r="P392" s="2" t="n"/>
+      <c r="Q392" s="2" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -13297,6 +13707,7 @@
       <c r="N393" s="2" t="n"/>
       <c r="O393" s="2" t="n"/>
       <c r="P393" s="2" t="n"/>
+      <c r="Q393" s="2" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -13329,6 +13740,7 @@
       <c r="N394" s="2" t="n"/>
       <c r="O394" s="2" t="n"/>
       <c r="P394" s="2" t="n"/>
+      <c r="Q394" s="2" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n"/>
@@ -13361,6 +13773,7 @@
       <c r="N395" s="2" t="n"/>
       <c r="O395" s="2" t="n"/>
       <c r="P395" s="2" t="n"/>
+      <c r="Q395" s="2" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n"/>
@@ -13393,6 +13806,7 @@
       <c r="N396" s="2" t="n"/>
       <c r="O396" s="2" t="n"/>
       <c r="P396" s="2" t="n"/>
+      <c r="Q396" s="2" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n"/>
@@ -13425,6 +13839,7 @@
       <c r="N397" s="2" t="n"/>
       <c r="O397" s="2" t="n"/>
       <c r="P397" s="2" t="n"/>
+      <c r="Q397" s="2" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n"/>
@@ -13457,6 +13872,7 @@
       <c r="N398" s="2" t="n"/>
       <c r="O398" s="2" t="n"/>
       <c r="P398" s="2" t="n"/>
+      <c r="Q398" s="2" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n"/>
@@ -13489,6 +13905,7 @@
       <c r="N399" s="2" t="n"/>
       <c r="O399" s="2" t="n"/>
       <c r="P399" s="2" t="n"/>
+      <c r="Q399" s="2" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n"/>
@@ -13521,6 +13938,7 @@
       <c r="N400" s="2" t="n"/>
       <c r="O400" s="2" t="n"/>
       <c r="P400" s="2" t="n"/>
+      <c r="Q400" s="2" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n"/>
@@ -13553,6 +13971,7 @@
       <c r="N401" s="2" t="n"/>
       <c r="O401" s="2" t="n"/>
       <c r="P401" s="2" t="n"/>
+      <c r="Q401" s="2" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n"/>
@@ -13585,6 +14004,7 @@
       <c r="N402" s="2" t="n"/>
       <c r="O402" s="2" t="n"/>
       <c r="P402" s="2" t="n"/>
+      <c r="Q402" s="2" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n"/>
@@ -13617,6 +14037,7 @@
       <c r="N403" s="2" t="n"/>
       <c r="O403" s="2" t="n"/>
       <c r="P403" s="2" t="n"/>
+      <c r="Q403" s="2" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n"/>
@@ -13649,6 +14070,7 @@
       <c r="N404" s="2" t="n"/>
       <c r="O404" s="2" t="n"/>
       <c r="P404" s="2" t="n"/>
+      <c r="Q404" s="2" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n"/>
@@ -13681,6 +14103,7 @@
       <c r="N405" s="2" t="n"/>
       <c r="O405" s="2" t="n"/>
       <c r="P405" s="2" t="n"/>
+      <c r="Q405" s="2" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n"/>
@@ -13713,6 +14136,7 @@
       <c r="N406" s="2" t="n"/>
       <c r="O406" s="2" t="n"/>
       <c r="P406" s="2" t="n"/>
+      <c r="Q406" s="2" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n"/>
@@ -13745,6 +14169,7 @@
       <c r="N407" s="2" t="n"/>
       <c r="O407" s="2" t="n"/>
       <c r="P407" s="2" t="n"/>
+      <c r="Q407" s="2" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n"/>
@@ -13777,6 +14202,7 @@
       <c r="N408" s="2" t="n"/>
       <c r="O408" s="2" t="n"/>
       <c r="P408" s="2" t="n"/>
+      <c r="Q408" s="2" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n"/>
@@ -13809,6 +14235,7 @@
       <c r="N409" s="2" t="n"/>
       <c r="O409" s="2" t="n"/>
       <c r="P409" s="2" t="n"/>
+      <c r="Q409" s="2" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n"/>
@@ -13841,6 +14268,7 @@
       <c r="N410" s="2" t="n"/>
       <c r="O410" s="2" t="n"/>
       <c r="P410" s="2" t="n"/>
+      <c r="Q410" s="2" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n"/>
@@ -13873,6 +14301,7 @@
       <c r="N411" s="2" t="n"/>
       <c r="O411" s="2" t="n"/>
       <c r="P411" s="2" t="n"/>
+      <c r="Q411" s="2" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n"/>
@@ -13905,6 +14334,7 @@
       <c r="N412" s="2" t="n"/>
       <c r="O412" s="2" t="n"/>
       <c r="P412" s="2" t="n"/>
+      <c r="Q412" s="2" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n"/>
@@ -13937,6 +14367,7 @@
       <c r="N413" s="2" t="n"/>
       <c r="O413" s="2" t="n"/>
       <c r="P413" s="2" t="n"/>
+      <c r="Q413" s="2" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n"/>
@@ -13969,6 +14400,7 @@
       <c r="N414" s="2" t="n"/>
       <c r="O414" s="2" t="n"/>
       <c r="P414" s="2" t="n"/>
+      <c r="Q414" s="2" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n"/>
@@ -14001,6 +14433,7 @@
       <c r="N415" s="2" t="n"/>
       <c r="O415" s="2" t="n"/>
       <c r="P415" s="2" t="n"/>
+      <c r="Q415" s="2" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n"/>
@@ -14033,6 +14466,7 @@
       <c r="N416" s="2" t="n"/>
       <c r="O416" s="2" t="n"/>
       <c r="P416" s="2" t="n"/>
+      <c r="Q416" s="2" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n"/>
@@ -14065,6 +14499,7 @@
       <c r="N417" s="2" t="n"/>
       <c r="O417" s="2" t="n"/>
       <c r="P417" s="2" t="n"/>
+      <c r="Q417" s="2" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n"/>
@@ -14097,6 +14532,7 @@
       <c r="N418" s="2" t="n"/>
       <c r="O418" s="2" t="n"/>
       <c r="P418" s="2" t="n"/>
+      <c r="Q418" s="2" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n"/>
@@ -14129,6 +14565,7 @@
       <c r="N419" s="2" t="n"/>
       <c r="O419" s="2" t="n"/>
       <c r="P419" s="2" t="n"/>
+      <c r="Q419" s="2" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n"/>
@@ -14161,6 +14598,7 @@
       <c r="N420" s="2" t="n"/>
       <c r="O420" s="2" t="n"/>
       <c r="P420" s="2" t="n"/>
+      <c r="Q420" s="2" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n"/>
@@ -14193,6 +14631,7 @@
       <c r="N421" s="2" t="n"/>
       <c r="O421" s="2" t="n"/>
       <c r="P421" s="2" t="n"/>
+      <c r="Q421" s="2" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n"/>
@@ -14225,6 +14664,7 @@
       <c r="N422" s="2" t="n"/>
       <c r="O422" s="2" t="n"/>
       <c r="P422" s="2" t="n"/>
+      <c r="Q422" s="2" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n"/>
@@ -14257,6 +14697,7 @@
       <c r="N423" s="2" t="n"/>
       <c r="O423" s="2" t="n"/>
       <c r="P423" s="2" t="n"/>
+      <c r="Q423" s="2" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n"/>
@@ -14289,6 +14730,7 @@
       <c r="N424" s="2" t="n"/>
       <c r="O424" s="2" t="n"/>
       <c r="P424" s="2" t="n"/>
+      <c r="Q424" s="2" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n"/>
@@ -14321,6 +14763,7 @@
       <c r="N425" s="2" t="n"/>
       <c r="O425" s="2" t="n"/>
       <c r="P425" s="2" t="n"/>
+      <c r="Q425" s="2" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n"/>
@@ -14353,6 +14796,7 @@
       <c r="N426" s="2" t="n"/>
       <c r="O426" s="2" t="n"/>
       <c r="P426" s="2" t="n"/>
+      <c r="Q426" s="2" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n"/>
@@ -14385,6 +14829,7 @@
       <c r="N427" s="2" t="n"/>
       <c r="O427" s="2" t="n"/>
       <c r="P427" s="2" t="n"/>
+      <c r="Q427" s="2" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n"/>
@@ -14417,6 +14862,7 @@
       <c r="N428" s="2" t="n"/>
       <c r="O428" s="2" t="n"/>
       <c r="P428" s="2" t="n"/>
+      <c r="Q428" s="2" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n"/>
@@ -14449,6 +14895,7 @@
       <c r="N429" s="2" t="n"/>
       <c r="O429" s="2" t="n"/>
       <c r="P429" s="2" t="n"/>
+      <c r="Q429" s="2" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n"/>
@@ -14481,6 +14928,7 @@
       <c r="N430" s="2" t="n"/>
       <c r="O430" s="2" t="n"/>
       <c r="P430" s="2" t="n"/>
+      <c r="Q430" s="2" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n"/>
@@ -14513,6 +14961,7 @@
       <c r="N431" s="2" t="n"/>
       <c r="O431" s="2" t="n"/>
       <c r="P431" s="2" t="n"/>
+      <c r="Q431" s="2" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n"/>
@@ -14545,6 +14994,7 @@
       <c r="N432" s="2" t="n"/>
       <c r="O432" s="2" t="n"/>
       <c r="P432" s="2" t="n"/>
+      <c r="Q432" s="2" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n"/>
@@ -14577,6 +15027,7 @@
       <c r="N433" s="2" t="n"/>
       <c r="O433" s="2" t="n"/>
       <c r="P433" s="2" t="n"/>
+      <c r="Q433" s="2" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n"/>
@@ -14609,6 +15060,7 @@
       <c r="N434" s="2" t="n"/>
       <c r="O434" s="2" t="n"/>
       <c r="P434" s="2" t="n"/>
+      <c r="Q434" s="2" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n"/>
@@ -14641,6 +15093,7 @@
       <c r="N435" s="2" t="n"/>
       <c r="O435" s="2" t="n"/>
       <c r="P435" s="2" t="n"/>
+      <c r="Q435" s="2" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n"/>
@@ -14673,6 +15126,7 @@
       <c r="N436" s="2" t="n"/>
       <c r="O436" s="2" t="n"/>
       <c r="P436" s="2" t="n"/>
+      <c r="Q436" s="2" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n"/>
@@ -14705,6 +15159,7 @@
       <c r="N437" s="2" t="n"/>
       <c r="O437" s="2" t="n"/>
       <c r="P437" s="2" t="n"/>
+      <c r="Q437" s="2" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n"/>
@@ -14737,6 +15192,7 @@
       <c r="N438" s="2" t="n"/>
       <c r="O438" s="2" t="n"/>
       <c r="P438" s="2" t="n"/>
+      <c r="Q438" s="2" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n"/>
@@ -14769,6 +15225,7 @@
       <c r="N439" s="2" t="n"/>
       <c r="O439" s="2" t="n"/>
       <c r="P439" s="2" t="n"/>
+      <c r="Q439" s="2" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n"/>
@@ -14801,6 +15258,7 @@
       <c r="N440" s="2" t="n"/>
       <c r="O440" s="2" t="n"/>
       <c r="P440" s="2" t="n"/>
+      <c r="Q440" s="2" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n"/>
@@ -14833,6 +15291,7 @@
       <c r="N441" s="2" t="n"/>
       <c r="O441" s="2" t="n"/>
       <c r="P441" s="2" t="n"/>
+      <c r="Q441" s="2" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n"/>
@@ -14865,6 +15324,7 @@
       <c r="N442" s="2" t="n"/>
       <c r="O442" s="2" t="n"/>
       <c r="P442" s="2" t="n"/>
+      <c r="Q442" s="2" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n"/>
@@ -14897,6 +15357,7 @@
       <c r="N443" s="2" t="n"/>
       <c r="O443" s="2" t="n"/>
       <c r="P443" s="2" t="n"/>
+      <c r="Q443" s="2" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n"/>
@@ -14929,6 +15390,7 @@
       <c r="N444" s="2" t="n"/>
       <c r="O444" s="2" t="n"/>
       <c r="P444" s="2" t="n"/>
+      <c r="Q444" s="2" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n"/>
@@ -14961,6 +15423,7 @@
       <c r="N445" s="2" t="n"/>
       <c r="O445" s="2" t="n"/>
       <c r="P445" s="2" t="n"/>
+      <c r="Q445" s="2" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n"/>
@@ -14993,6 +15456,7 @@
       <c r="N446" s="2" t="n"/>
       <c r="O446" s="2" t="n"/>
       <c r="P446" s="2" t="n"/>
+      <c r="Q446" s="2" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n"/>
@@ -15025,6 +15489,7 @@
       <c r="N447" s="2" t="n"/>
       <c r="O447" s="2" t="n"/>
       <c r="P447" s="2" t="n"/>
+      <c r="Q447" s="2" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n"/>
@@ -15057,6 +15522,7 @@
       <c r="N448" s="2" t="n"/>
       <c r="O448" s="2" t="n"/>
       <c r="P448" s="2" t="n"/>
+      <c r="Q448" s="2" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n"/>
@@ -15089,6 +15555,7 @@
       <c r="N449" s="2" t="n"/>
       <c r="O449" s="2" t="n"/>
       <c r="P449" s="2" t="n"/>
+      <c r="Q449" s="2" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n"/>
@@ -15121,6 +15588,7 @@
       <c r="N450" s="2" t="n"/>
       <c r="O450" s="2" t="n"/>
       <c r="P450" s="2" t="n"/>
+      <c r="Q450" s="2" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n"/>
@@ -15153,6 +15621,7 @@
       <c r="N451" s="2" t="n"/>
       <c r="O451" s="2" t="n"/>
       <c r="P451" s="2" t="n"/>
+      <c r="Q451" s="2" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n"/>
@@ -15185,6 +15654,7 @@
       <c r="N452" s="2" t="n"/>
       <c r="O452" s="2" t="n"/>
       <c r="P452" s="2" t="n"/>
+      <c r="Q452" s="2" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n"/>
@@ -15217,6 +15687,7 @@
       <c r="N453" s="2" t="n"/>
       <c r="O453" s="2" t="n"/>
       <c r="P453" s="2" t="n"/>
+      <c r="Q453" s="2" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n"/>
@@ -15249,6 +15720,7 @@
       <c r="N454" s="2" t="n"/>
       <c r="O454" s="2" t="n"/>
       <c r="P454" s="2" t="n"/>
+      <c r="Q454" s="2" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n"/>
@@ -15281,6 +15753,7 @@
       <c r="N455" s="2" t="n"/>
       <c r="O455" s="2" t="n"/>
       <c r="P455" s="2" t="n"/>
+      <c r="Q455" s="2" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n"/>
@@ -15313,6 +15786,7 @@
       <c r="N456" s="2" t="n"/>
       <c r="O456" s="2" t="n"/>
       <c r="P456" s="2" t="n"/>
+      <c r="Q456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n"/>
@@ -15345,6 +15819,7 @@
       <c r="N457" s="2" t="n"/>
       <c r="O457" s="2" t="n"/>
       <c r="P457" s="2" t="n"/>
+      <c r="Q457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n"/>
@@ -15377,6 +15852,7 @@
       <c r="N458" s="2" t="n"/>
       <c r="O458" s="2" t="n"/>
       <c r="P458" s="2" t="n"/>
+      <c r="Q458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n"/>
@@ -15409,6 +15885,7 @@
       <c r="N459" s="2" t="n"/>
       <c r="O459" s="2" t="n"/>
       <c r="P459" s="2" t="n"/>
+      <c r="Q459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n"/>
@@ -15441,6 +15918,7 @@
       <c r="N460" s="2" t="n"/>
       <c r="O460" s="2" t="n"/>
       <c r="P460" s="2" t="n"/>
+      <c r="Q460" s="2" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n"/>
@@ -15473,6 +15951,7 @@
       <c r="N461" s="2" t="n"/>
       <c r="O461" s="2" t="n"/>
       <c r="P461" s="2" t="n"/>
+      <c r="Q461" s="2" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n"/>
@@ -15505,6 +15984,7 @@
       <c r="N462" s="2" t="n"/>
       <c r="O462" s="2" t="n"/>
       <c r="P462" s="2" t="n"/>
+      <c r="Q462" s="2" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n"/>
@@ -15537,6 +16017,7 @@
       <c r="N463" s="2" t="n"/>
       <c r="O463" s="2" t="n"/>
       <c r="P463" s="2" t="n"/>
+      <c r="Q463" s="2" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n"/>
@@ -15569,6 +16050,7 @@
       <c r="N464" s="2" t="n"/>
       <c r="O464" s="2" t="n"/>
       <c r="P464" s="2" t="n"/>
+      <c r="Q464" s="2" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n"/>
@@ -15601,6 +16083,7 @@
       <c r="N465" s="2" t="n"/>
       <c r="O465" s="2" t="n"/>
       <c r="P465" s="2" t="n"/>
+      <c r="Q465" s="2" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n"/>
@@ -15633,6 +16116,7 @@
       <c r="N466" s="2" t="n"/>
       <c r="O466" s="2" t="n"/>
       <c r="P466" s="2" t="n"/>
+      <c r="Q466" s="2" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n"/>
@@ -15665,6 +16149,7 @@
       <c r="N467" s="2" t="n"/>
       <c r="O467" s="2" t="n"/>
       <c r="P467" s="2" t="n"/>
+      <c r="Q467" s="2" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n"/>
@@ -15697,6 +16182,7 @@
       <c r="N468" s="2" t="n"/>
       <c r="O468" s="2" t="n"/>
       <c r="P468" s="2" t="n"/>
+      <c r="Q468" s="2" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n"/>
@@ -15729,6 +16215,7 @@
       <c r="N469" s="2" t="n"/>
       <c r="O469" s="2" t="n"/>
       <c r="P469" s="2" t="n"/>
+      <c r="Q469" s="2" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n"/>
@@ -15761,6 +16248,7 @@
       <c r="N470" s="2" t="n"/>
       <c r="O470" s="2" t="n"/>
       <c r="P470" s="2" t="n"/>
+      <c r="Q470" s="2" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n"/>
@@ -15793,6 +16281,7 @@
       <c r="N471" s="2" t="n"/>
       <c r="O471" s="2" t="n"/>
       <c r="P471" s="2" t="n"/>
+      <c r="Q471" s="2" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n"/>
@@ -15825,6 +16314,7 @@
       <c r="N472" s="2" t="n"/>
       <c r="O472" s="2" t="n"/>
       <c r="P472" s="2" t="n"/>
+      <c r="Q472" s="2" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n"/>
@@ -15857,6 +16347,7 @@
       <c r="N473" s="2" t="n"/>
       <c r="O473" s="2" t="n"/>
       <c r="P473" s="2" t="n"/>
+      <c r="Q473" s="2" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n"/>
@@ -15889,6 +16380,7 @@
       <c r="N474" s="2" t="n"/>
       <c r="O474" s="2" t="n"/>
       <c r="P474" s="2" t="n"/>
+      <c r="Q474" s="2" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n"/>
@@ -15921,6 +16413,7 @@
       <c r="N475" s="2" t="n"/>
       <c r="O475" s="2" t="n"/>
       <c r="P475" s="2" t="n"/>
+      <c r="Q475" s="2" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n"/>
@@ -15953,6 +16446,7 @@
       <c r="N476" s="2" t="n"/>
       <c r="O476" s="2" t="n"/>
       <c r="P476" s="2" t="n"/>
+      <c r="Q476" s="2" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n"/>
@@ -15985,6 +16479,7 @@
       <c r="N477" s="2" t="n"/>
       <c r="O477" s="2" t="n"/>
       <c r="P477" s="2" t="n"/>
+      <c r="Q477" s="2" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n"/>
@@ -16017,6 +16512,7 @@
       <c r="N478" s="2" t="n"/>
       <c r="O478" s="2" t="n"/>
       <c r="P478" s="2" t="n"/>
+      <c r="Q478" s="2" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n"/>
@@ -16049,6 +16545,7 @@
       <c r="N479" s="2" t="n"/>
       <c r="O479" s="2" t="n"/>
       <c r="P479" s="2" t="n"/>
+      <c r="Q479" s="2" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n"/>
@@ -16081,6 +16578,7 @@
       <c r="N480" s="2" t="n"/>
       <c r="O480" s="2" t="n"/>
       <c r="P480" s="2" t="n"/>
+      <c r="Q480" s="2" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n"/>
@@ -16113,6 +16611,7 @@
       <c r="N481" s="2" t="n"/>
       <c r="O481" s="2" t="n"/>
       <c r="P481" s="2" t="n"/>
+      <c r="Q481" s="2" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n"/>
@@ -16145,6 +16644,7 @@
       <c r="N482" s="2" t="n"/>
       <c r="O482" s="2" t="n"/>
       <c r="P482" s="2" t="n"/>
+      <c r="Q482" s="2" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n"/>
@@ -16177,6 +16677,7 @@
       <c r="N483" s="2" t="n"/>
       <c r="O483" s="2" t="n"/>
       <c r="P483" s="2" t="n"/>
+      <c r="Q483" s="2" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n"/>
@@ -16209,6 +16710,7 @@
       <c r="N484" s="2" t="n"/>
       <c r="O484" s="2" t="n"/>
       <c r="P484" s="2" t="n"/>
+      <c r="Q484" s="2" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n"/>
@@ -16241,6 +16743,7 @@
       <c r="N485" s="2" t="n"/>
       <c r="O485" s="2" t="n"/>
       <c r="P485" s="2" t="n"/>
+      <c r="Q485" s="2" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n"/>
@@ -16273,6 +16776,7 @@
       <c r="N486" s="2" t="n"/>
       <c r="O486" s="2" t="n"/>
       <c r="P486" s="2" t="n"/>
+      <c r="Q486" s="2" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n"/>
@@ -16305,6 +16809,7 @@
       <c r="N487" s="2" t="n"/>
       <c r="O487" s="2" t="n"/>
       <c r="P487" s="2" t="n"/>
+      <c r="Q487" s="2" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n"/>
@@ -16337,6 +16842,7 @@
       <c r="N488" s="2" t="n"/>
       <c r="O488" s="2" t="n"/>
       <c r="P488" s="2" t="n"/>
+      <c r="Q488" s="2" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n"/>
@@ -16369,6 +16875,7 @@
       <c r="N489" s="2" t="n"/>
       <c r="O489" s="2" t="n"/>
       <c r="P489" s="2" t="n"/>
+      <c r="Q489" s="2" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n"/>
@@ -16401,6 +16908,7 @@
       <c r="N490" s="2" t="n"/>
       <c r="O490" s="2" t="n"/>
       <c r="P490" s="2" t="n"/>
+      <c r="Q490" s="2" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n"/>
@@ -16433,6 +16941,7 @@
       <c r="N491" s="2" t="n"/>
       <c r="O491" s="2" t="n"/>
       <c r="P491" s="2" t="n"/>
+      <c r="Q491" s="2" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n"/>
@@ -16465,6 +16974,7 @@
       <c r="N492" s="2" t="n"/>
       <c r="O492" s="2" t="n"/>
       <c r="P492" s="2" t="n"/>
+      <c r="Q492" s="2" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n"/>
@@ -16497,6 +17007,7 @@
       <c r="N493" s="2" t="n"/>
       <c r="O493" s="2" t="n"/>
       <c r="P493" s="2" t="n"/>
+      <c r="Q493" s="2" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n"/>
@@ -16529,6 +17040,7 @@
       <c r="N494" s="2" t="n"/>
       <c r="O494" s="2" t="n"/>
       <c r="P494" s="2" t="n"/>
+      <c r="Q494" s="2" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n"/>
@@ -16561,6 +17073,7 @@
       <c r="N495" s="2" t="n"/>
       <c r="O495" s="2" t="n"/>
       <c r="P495" s="2" t="n"/>
+      <c r="Q495" s="2" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n"/>
@@ -16593,6 +17106,7 @@
       <c r="N496" s="2" t="n"/>
       <c r="O496" s="2" t="n"/>
       <c r="P496" s="2" t="n"/>
+      <c r="Q496" s="2" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n"/>
@@ -16625,6 +17139,7 @@
       <c r="N497" s="2" t="n"/>
       <c r="O497" s="2" t="n"/>
       <c r="P497" s="2" t="n"/>
+      <c r="Q497" s="2" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n"/>
@@ -16657,6 +17172,7 @@
       <c r="N498" s="2" t="n"/>
       <c r="O498" s="2" t="n"/>
       <c r="P498" s="2" t="n"/>
+      <c r="Q498" s="2" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n"/>
@@ -16689,6 +17205,7 @@
       <c r="N499" s="2" t="n"/>
       <c r="O499" s="2" t="n"/>
       <c r="P499" s="2" t="n"/>
+      <c r="Q499" s="2" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n"/>
@@ -16721,6 +17238,7 @@
       <c r="N500" s="2" t="n"/>
       <c r="O500" s="2" t="n"/>
       <c r="P500" s="2" t="n"/>
+      <c r="Q500" s="2" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n"/>
@@ -16753,9 +17271,10 @@
       <c r="N501" s="2" t="n"/>
       <c r="O501" s="2" t="n"/>
       <c r="P501" s="2" t="n"/>
+      <c r="Q501" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
       <formula1>=ChallengeStates</formula1>
     </dataValidation>
@@ -16779,6 +17298,9 @@
     </dataValidation>
     <dataValidation sqref="P2:P501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the dropdown." type="list">
       <formula1>=BonusModes</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Enter a whole number greater than or equal to 0." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
